--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -7,16 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -530,7 +532,7 @@
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>情報管理規程</t>
+          <t>就業規則</t>
         </is>
       </c>
     </row>
@@ -569,7 +571,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における情報資産を適正に管理し、秘密情報及び個人情報の漏えい、不正使用、毀損を防止し、事業活動の信頼性と従業員の職務上の責務を明確にすることを目的とする。</t>
+          <t>第1条　本規則は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）に勤務する従業員の就業に関する基本事項を定め、労務管理の適正化、従業員の生活の安定および業務の円滑な運営を図ることを目的とする。</t>
         </is>
       </c>
     </row>
@@ -577,44 +579,50 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。役員、派遣社員、業務委託先等の関係者についても、会社が必要と認める場合は適用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="7" t="inlineStr"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="10" customHeight="1"/>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>第2章　情報の取扱い</t>
-        </is>
-      </c>
-    </row>
+          <t>第2条　本規則における用語の定義は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>1　「従業員」とは、会社に雇用される者をいう（有期・無期、所定労働時間の長短を問わない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2　「管理監督者」とは、労働基準法第41条に定める者をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>3　その他の用語の詳細は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>（秘密情報の範囲）</t>
+          <t>（適用範囲）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>第3条　秘密情報とは、会社の業務に関し公知でない情報をいう。営業情報、技術情報、顧客情報、従業員の人事・給与情報、財務情報等を含む。</t>
+          <t>第3条　本規則は、会社に雇用されるすべての従業員に適用する。管理監督者等の一部については法令に従い適用除外とし、詳細は「人事管理規程」による。</t>
         </is>
       </c>
     </row>
@@ -622,44 +630,44 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>（個人情報の範囲）</t>
+          <t>（周知・改廃）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>第4条　個人情報とは、個人を識別できる情報（氏名、住所、電話番号、メールアドレス、健康情報等）をいう。</t>
+          <t>第4条　本規則および各規程は、社内掲示・イントラネット等により周知する。改廃は労働基準法に基づく手続（意見聴取・届出等）を経て行う。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>（利用目的の限定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>第5条　従業員は、秘密情報及び個人情報を、業務遂行の目的の範囲内でのみ利用しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>第2章　勤務</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>（持ち出し・複製の制限）</t>
+          <t>（勤務体制：1か月単位の変形労働時間制）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>第6条　従業員は、会社の承認なく情報資産を持ち出し、複製し、または外部に提供してはならない。やむを得ず持ち出す場合は、上長の承認を受けるものとする。</t>
+          <t>第5条　会社は一か月単位の変形労働時間制を採用する。対象者、計算期間、各日・各週の所定労働時間の決定方法、勤務割表の作成・通知方法その他の詳細は「勤務管理規程」による。</t>
         </is>
       </c>
     </row>
@@ -667,44 +675,44 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>（電子機器・通信利用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="48" customHeight="1">
+          <t>（所定労働時間・休憩）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>第7条　従業員は、会社支給のPC、スマートフォン、メールアカウント等を業務目的以外に利用してはならない。私的利用、違法・不適切なサイト閲覧、外部クラウドサービスへの無断保存は禁止する。</t>
+          <t>第6条　所定労働時間は1日8時間とする。休憩は原則として6時間を超える勤務の場合1時間、夜勤勤務の場合2時間とし、取得方法は「勤務管理規程」による。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="8" customHeight="1">
-      <c r="A51" s="7" t="inlineStr"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-    </row>
-    <row r="52" ht="10" customHeight="1"/>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>第3章　管理体制</t>
-        </is>
-      </c>
-    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>（休日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>第7条　休日は月10日を原則とし、このうち法定休日は会社の定める日とする（4週間を通じ少なくとも4日）。振替休日・代休の取扱いは「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>（管理責任者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
+          <t>（時間外・休日・深夜労働）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>第8条　会社は、情報管理責任者を置き、情報資産の保護・管理を統括させる。</t>
+          <t>第8条　業務上必要がある場合、会社は36協定に基づき時間外労働および休日労働を命じることがある。22時から翌5時までの労働については法定割増賃金を支給する。手当の区分・額等は「賃金規程」による。</t>
         </is>
       </c>
     </row>
@@ -712,14 +720,14 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>（アクセス管理）</t>
+          <t>（出退勤記録）</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>第9条　会社は、情報システムへのアクセス権限を職務に応じて付与し、不要となった場合は速やかに停止する。従業員は、他人のID・パスワードを使用してはならない。</t>
+          <t>第9条　従業員は会社の指定する方法により出退勤を記録しなければならない。記録方法、訂正手続等は「勤務管理規程」による。</t>
         </is>
       </c>
     </row>
@@ -727,59 +735,59 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>（媒体管理）</t>
+          <t>（配置転換・出向・転勤）</t>
         </is>
       </c>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>第10条　USBメモリ、外付HDD、紙媒体等の外部記録媒体の利用は会社の許可を要する。利用後は速やかに返却・廃棄しなければならない。</t>
+          <t>第10条　会社は業務上の必要により配置転換、出向、転勤等を命ずることがある。手続・配慮事項は「人事管理規程」による。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>（廃棄時の管理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>第11条　秘密情報及び個人情報を含む文書、媒体を廃棄する場合は、会社所定の方法（シュレッダー、専用廃棄サービス等）に従わなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="8" customHeight="1"/>
-    <row r="66" ht="8" customHeight="1">
-      <c r="A66" s="7" t="inlineStr"/>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
-    </row>
-    <row r="67" ht="10" customHeight="1"/>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>第4章　従業員の義務</t>
-        </is>
-      </c>
-    </row>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="7" t="inlineStr"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>第3章　服務</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>（服務規律）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>第11条　従業員は、法令、本規則および各種規程並びに会社の指示に従い、誠実かつ公正に職務を遂行し、職場秩序を維持しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>（秘密保持義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
+          <t>（ハラスメントの禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>第12条　従業員は、在職中及び退職後においても、秘密情報及び個人情報を漏らしてはならない。</t>
+          <t>第12条　従業員は、セクシュアルハラスメント、パワーハラスメントその他一切のハラスメント行為を行ってはならない。防止体制、相談・調査・再発防止等は「ハラスメント防止規程」による。</t>
         </is>
       </c>
     </row>
@@ -787,14 +795,14 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>（退職時の返還）</t>
+          <t>（秘密情報・個人情報の保護）</t>
         </is>
       </c>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>第13条　従業員は、退職時に会社から貸与された機器、資料、データ等をすべて返還し、社内システムへのアクセス権を消去しなければならない。</t>
+          <t>第13条　従業員は、在職中および退職後において、業務上知り得た秘密情報・個人情報を漏えいしてはならない。範囲、管理措置、違反時の取扱いは「情報管理規程」による。</t>
         </is>
       </c>
     </row>
@@ -802,207 +810,361 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>（事故報告義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
+          <t>（競業避止・利益相反）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="48" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>第14条　従業員は、情報の漏えい、紛失、改ざん、マルウェア感染等の事故を知ったときは、直ちに会社に報告しなければならない。</t>
+          <t>第14条　会社が指定する者は、在職中および退職後一定期間、会社の指定する地域において競業行為を行ってはならない。兼業・副業、利益相反の管理は「競業避止規程」および「人事管理規程」による。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="8" customHeight="1"/>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>（ソーシャルメディア利用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>第15条　従業員は、SNS、掲示板、ブログ等を利用する際に、会社や取引先の秘密情報・個人情報を投稿・公開してはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="8" customHeight="1"/>
-    <row r="81" ht="8" customHeight="1">
-      <c r="A81" s="7" t="inlineStr"/>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="10" customHeight="1"/>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>第5章　教育・監査</t>
-        </is>
-      </c>
-    </row>
+    <row r="78" ht="8" customHeight="1">
+      <c r="A78" s="7" t="inlineStr"/>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+    </row>
+    <row r="79" ht="10" customHeight="1"/>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>第4章　休暇・休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>（年次有給休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>第15条　従業員には労働基準法に基づく年次有給休暇を付与する。付与日、計画的付与、時季変更、半日・時間単位付与等は「休暇規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>（教育）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
+          <t>（特別休暇・法定休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>第16条　会社は、従業員に対して情報管理及び個人情報保護に関する教育を定期的に実施する。</t>
+          <t>第16条　慶弔休暇、病気休暇、産前産後休暇、育児休業、介護休業、子の看護等休暇等の付与・手続は「休暇規程」および「育児・介護休業規程」による。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>（監査）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>第17条　会社は、必要に応じて情報管理状況の監査を行い、改善を指示できる。従業員は監査に協力しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="8" customHeight="1"/>
-    <row r="90" ht="8" customHeight="1">
-      <c r="A90" s="7" t="inlineStr"/>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="8" t="n"/>
-    </row>
-    <row r="91" ht="10" customHeight="1"/>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>第6章　罰則</t>
-        </is>
-      </c>
-    </row>
+    <row r="87" ht="8" customHeight="1">
+      <c r="A87" s="7" t="inlineStr"/>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
+    </row>
+    <row r="88" ht="10" customHeight="1"/>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>第5章　賃金</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>（賃金の構成・決定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>第17条　賃金は、基本給、諸手当、賞与その他会社の定めるものから構成する。種類、額、計算・支給方法、欠勤・遅刻等の控除、割増賃金の算定は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>（懲戒）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
+          <t>（締切日・支払日・支払方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>第18条　従業員が本規程に違反した場合は、「懲戒規程」に基づき懲戒処分の対象とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>2　会社に損害が生じた場合は、法令に基づき賠償責任を負うことがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="8" customHeight="1">
-      <c r="A97" s="7" t="inlineStr"/>
-      <c r="B97" s="8" t="n"/>
-      <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="8" t="n"/>
-    </row>
-    <row r="98" ht="10" customHeight="1"/>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+          <t>第18条　賃金の締切日は毎月末日とし、翌月27日に支払う。支払日が土曜日、日曜日または祝日に当たるときは、直前の平日に繰り上げて支払う。支払方法は、従業員の同意を得て、従業員が指定する銀行口座への振込による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>（賃金控除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>第19条　法令に基づく控除のほか、会社と労使協定を締結した場合に限り賃金控除を行う。控除項目等は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="8" customHeight="1">
+      <c r="A99" s="7" t="inlineStr"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
+    </row>
+    <row r="100" ht="10" customHeight="1"/>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>第6章　安全衛生</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>（安全衛生管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="48" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>第20条　会社は労働安全衛生法その他関係法令に基づき、従業員の安全と健康の確保に努める。従業員は会社の措置に協力しなければならない。体制、健康診断、就業上の措置等は「安全衛生規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="8" customHeight="1"/>
+    <row r="105" ht="8" customHeight="1">
+      <c r="A105" s="7" t="inlineStr"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+    </row>
+    <row r="106" ht="10" customHeight="1"/>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>第7章　懲戒</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>（懲戒の基本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>第21条　従業員が服務規律に違反した場合、情状に応じて懲戒処分を行うことがある。懲戒の種類、事由、手続、弁明の機会付与等は「懲戒規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2　懲戒により減給を命ずる場合、1回の額は平均賃金の1日分の半額を超えず、総額は1賃金支払期における賃金総額の1/10を超えない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="8" customHeight="1">
+      <c r="A112" s="7" t="inlineStr"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+    </row>
+    <row r="113" ht="10" customHeight="1"/>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>第8章　退職・解雇</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>（退職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="48" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>第22条　従業員が自己都合により退職する場合は、円滑な引継ぎのため、原則として30日前までに、書面（電磁的方法を含む）にて会社に届け出るよう努めなければならない。定年、退職時の有給休暇の取扱い、業務引継、貸与物の返還等は「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="8" customHeight="1"/>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>（解雇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>第23条　会社は、業務遂行困難、職務不良、服務規律違反その他やむを得ない事由がある場合に解雇を行うことがある。解雇事由、手続、予告・予告手当、整理解雇の要件等は「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>（退職時証明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>第24条　従業員が退職に際し、在職期間・業務の種類・地位・賃金・事由等の退職証明書の交付を請求したときは、法令に従い遅滞なく交付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="8" customHeight="1">
+      <c r="A124" s="7" t="inlineStr"/>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+    </row>
+    <row r="125" ht="10" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>附則</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>2　本規程は令和8年2月1日から施行する。</t>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>第25条　本規則に定めのない事項は、労働基準法その他関係法令および会社の各規程による。制定・改廃の履歴は「規程管理台帳」に記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>第26条　本規則は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="74">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A103:E103"/>
     <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A128:E128"/>
     <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A118:E118"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="A66:E66"/>
     <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A127:E127"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A101:E101"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
     <mergeCell ref="A93:E93"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　情報管理規程</oddHeader>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　就業規則</oddHeader>
     <oddFooter>&amp;C&amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1016,6 +1178,1178 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>競業避止規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の事業上の正当な利益を保護し、従業員による競業行為を防止するとともに、従業員の職業選択の自由との調和を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用される従業員のうち、経営管理、営業、研究開発その他会社が特に指定する者に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2　派遣社員、業務委託契約者等については、個別契約に基づき適用することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>第3条　本規程における「競業行為」とは、会社と同一または類似の事業を営む行為、会社と競合する他社への就業、または会社の取引先を利用して自己または第三者の利益を図る行為をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="8" customHeight="1">
+      <c r="A37" s="7" t="inlineStr"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="10" customHeight="1"/>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>第2章　在職中の義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>（競業禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>第4条　従業員は、在職中、会社の承認なく競業行為を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>（副業・兼業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>第5条　従業員は、副業・兼業を行う場合であっても、会社の業務に支障を及ぼさず、かつ競業行為に該当しない範囲に限り許可される。詳細は「人事管理規程」及び「副業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>（秘密情報の利用禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>第6条　従業員は、在職中に知り得た会社の秘密情報を利用して競業行為を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="8" customHeight="1">
+      <c r="A49" s="7" t="inlineStr"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="10" customHeight="1"/>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>第3章　退職後の義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>（競業避止義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>第7条　管理職、営業担当その他会社が特に指定した従業員は、退職後1年間、会社が営業する地域（大阪府・兵庫県・京都府・奈良県）において、会社と競合する事業に従事してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>（合理的範囲の限定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>第8条　前条の地域・期間は、会社の事業規模、従業員の職務内容、社会通念を考慮し、合理的な範囲に限定される。過度に広範な競業禁止は適用しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>（補償）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>第9条　会社は、退職後競業避止義務を個別合意で課す場合、社会通念上相当と認められる補償を行う。補償の内容は合意時に明示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="8" customHeight="1">
+      <c r="A61" s="7" t="inlineStr"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+    </row>
+    <row r="62" ht="10" customHeight="1"/>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>第4章　管理・措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>（特別合意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>第10条　会社は、必要に応じ、従業員との間で退職後競業避止に関する特別合意を締結することができる。その場合、地域、期間、業務範囲及び補償内容を明示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>（違反時の措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>第11条　従業員が在職中に本規程に違反した場合は「懲戒規程」に基づき懲戒処分の対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2　従業員が退職後に本規程に違反し会社に損害を与えた場合は、会社は法令に基づき損害賠償を請求することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="8" customHeight="1">
+      <c r="A71" s="7" t="inlineStr"/>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+    </row>
+    <row r="72" ht="10" customHeight="1"/>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>第5章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>（他規程との関係）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>第12条　本規程に定めのない事項は、就業規則、情報管理規程、秘密保持契約その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="8" customHeight="1">
+      <c r="A77" s="7" t="inlineStr"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+    </row>
+    <row r="78" ht="10" customHeight="1"/>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程施行前に締結された労働契約その他の合意についても、本規程に反しない範囲で適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="42">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　競業避止規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E137"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>育児・介護休業規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員が、育児・介護休業法その他関係法令に基づき、仕事と育児・介護を両立できるよう育児休業、介護休業等の制度を定め、従業員の職業生活の安定と充実を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用される全ての正社員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2　契約社員、嘱託社員、パートタイマー等については、労働契約書において別段の定めがある場合を除き、本規程を準用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>第3条　本規程における用語の定義は、育児・介護休業法に準拠し、次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>1　「育児休業」：満1歳に満たない子を養育するために取得する休業をいう。ただし、一定の場合は1歳6か月、さらに2歳まで延長できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2　「介護休業」：要介護状態にある家族（法令に定める範囲）を介護するために取得する休業をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>3　「子の看護等休暇」：小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のために取得できる休暇をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>5　「出生時育児休業」：子の出生後8週間以内に4週間（28日）まで取得できる休業をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>4　「介護休暇」：要介護状態にある家族の介護や通院付添のために取得できる休暇をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>第2章　育児休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>（育児休業の取得要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>第4条　従業員は、1歳に満たない子を養育する場合、会社に申し出ることにより育児休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2　育児休業は、子1人につき原則2回まで分割して取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>3　労使協定により、次の者を育児休業の対象から除外することがある。（1）継続雇用期間が1年未満の者　（2）申出の日から1年以内に雇用関係が終了することが明らかな者　（3）1週間の所定労働日数が2日以下の者</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>4　有期雇用の従業員は、子が1歳6か月に達する日までに労働契約が満了し更新されないことが明らかでない場合に取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>（育児休業の期間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>（育児休業の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>（出生時育児休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>第6条の2　従業員は、子の出生後8週間以内に、4週間（28日）を限度として、2回まで分割して出生時育児休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2　出生時育児休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>（育児休業中の処遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="8" customHeight="1">
+      <c r="A65" s="7" t="inlineStr"/>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="8" t="n"/>
+    </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>第3章　介護休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>（介護休業の取得要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>第8条　従業員は、要介護状態にある家族を介護する場合、会社に申し出ることにより介護休業を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>（介護休業の期間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>第9条　介護休業は、対象家族1人につき通算93日まで取得できる。分割して3回まで分けて取得することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>（介護休業の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>第10条　介護休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに、所定の書式により会社へ申し出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>（介護休業中の処遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>第11条　介護休業中は無給とする。ただし、雇用保険法に基づき介護休業給付金の受給が可能である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="8" customHeight="1">
+      <c r="A80" s="7" t="inlineStr"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+    </row>
+    <row r="81" ht="10" customHeight="1"/>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>第4章　子の看護等休暇・介護休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のため、年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2　子の看護等休暇は、1日または時間単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>（介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2　介護休暇は、1日または時間単位で取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="8" customHeight="1"/>
+    <row r="91" ht="8" customHeight="1">
+      <c r="A91" s="7" t="inlineStr"/>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+    </row>
+    <row r="92" ht="10" customHeight="1"/>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>第4章の2　働き方の制限・措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>（所定外労働の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>第13条の2　小学校就学前の子を養育する従業員、または要介護状態にある家族を介護する従業員が請求した場合、事業の正常な運営を妨げる場合を除き、所定労働時間を超えて労働させない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>（時間外労働・深夜業の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>第13条の3　前条の従業員が請求した場合、時間外労働は1か月24時間、1年150時間を超えないものとし、深夜（午後10時から午前5時まで）に労働させない。ただし、法令に定める除外者はこの限りでない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>（短時間勤務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>第13条の4　3歳に満たない子を養育する従業員、または要介護状態にある家族を介護する従業員は、申し出により、所定労働時間を1日6時間とする短時間勤務を利用できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>（柔軟な働き方を実現するための措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>第13条の5　3歳から小学校就学前の子を養育する従業員に対し、会社は次の措置を講じ、従業員はいずれか1つを選択して利用できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>1　始業・終業時刻の変更（時差出勤）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2　養育両立支援休暇（年10日、時間単位で取得可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>（個別周知・意向確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>第13条の6　会社は、従業員から本人または配偶者の妊娠・出産の申出があったとき、及び子が3歳になる前の適切な時期に、育児休業等の制度を個別に周知し、取得や働き方の意向を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、従業員から家族の介護に直面した旨の申出があったとき、介護休業等の制度を個別に周知し、意向を確認する。また、40歳に達した従業員に対し、介護両立支援制度の情報を提供する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>（ハラスメントの防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>第13条の7　会社は、妊娠・出産、育児休業・介護休業等の利用に関する言動により従業員の就業環境が害されることのないよう、相談体制の整備その他必要な措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="8" customHeight="1">
+      <c r="A115" s="7" t="inlineStr"/>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+    </row>
+    <row r="116" ht="10" customHeight="1"/>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>第5章　復職・不利益取扱い禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>（復職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="48" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>第15条　会社は、従業員が育児休業・出生時育児休業・介護休業・子の看護等休暇・介護休暇その他本規程の制度を利用したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="8" customHeight="1">
+      <c r="A124" s="7" t="inlineStr"/>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+    </row>
+    <row r="125" ht="10" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>第6章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>（制度の周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="8" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>（個人情報保護）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="7" t="inlineStr"/>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="84">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A117:E117"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　育児・介護休業規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1731,6 +3065,528 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>情報管理規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における情報資産を適正に管理し、秘密情報及び個人情報の漏えい、不正使用、毀損を防止し、事業活動の信頼性と従業員の職務上の責務を明確にすることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。役員、派遣社員、業務委託先等の関係者についても、会社が必要と認める場合は適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>第2章　情報の取扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>（秘密情報の範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>第3条　秘密情報とは、会社の業務に関し公知でない情報をいう。営業情報、技術情報、顧客情報、従業員の人事・給与情報、財務情報等を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>（個人情報の範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>第4条　個人情報とは、個人を識別できる情報（氏名、住所、電話番号、メールアドレス、健康情報等）をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>（利用目的の限定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>第5条　従業員は、秘密情報及び個人情報を、業務遂行の目的の範囲内でのみ利用しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>（持ち出し・複製の制限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>第6条　従業員は、会社の承認なく情報資産を持ち出し、複製し、または外部に提供してはならない。やむを得ず持ち出す場合は、上長の承認を受けるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>（電子機器・通信利用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>第7条　従業員は、会社支給のPC、スマートフォン、メールアカウント等を業務目的以外に利用してはならない。私的利用、違法・不適切なサイト閲覧、外部クラウドサービスへの無断保存は禁止する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="8" customHeight="1">
+      <c r="A51" s="7" t="inlineStr"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+    </row>
+    <row r="52" ht="10" customHeight="1"/>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>第3章　管理体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>（管理責任者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>第8条　会社は、情報管理責任者を置き、情報資産の保護・管理を統括させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>（アクセス管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>第9条　会社は、情報システムへのアクセス権限を職務に応じて付与し、不要となった場合は速やかに停止する。従業員は、他人のID・パスワードを使用してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>（媒体管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>第10条　USBメモリ、外付HDD、紙媒体等の外部記録媒体の利用は会社の許可を要する。利用後は速やかに返却・廃棄しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>（廃棄時の管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>第11条　秘密情報及び個人情報を含む文書、媒体を廃棄する場合は、会社所定の方法（シュレッダー、専用廃棄サービス等）に従わなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="8" customHeight="1">
+      <c r="A66" s="7" t="inlineStr"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+    </row>
+    <row r="67" ht="10" customHeight="1"/>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>第4章　従業員の義務</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>（秘密保持義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、在職中及び退職後においても、秘密情報及び個人情報を漏らしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>（退職時の返還）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、退職時に会社から貸与された機器、資料、データ等をすべて返還し、社内システムへのアクセス権を消去しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>（事故報告義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>第14条　従業員は、情報の漏えい、紛失、改ざん、マルウェア感染等の事故を知ったときは、直ちに会社に報告しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>（ソーシャルメディア利用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>第15条　従業員は、SNS、掲示板、ブログ等を利用する際に、会社や取引先の秘密情報・個人情報を投稿・公開してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="8" customHeight="1">
+      <c r="A81" s="7" t="inlineStr"/>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="8" t="n"/>
+    </row>
+    <row r="82" ht="10" customHeight="1"/>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>第5章　教育・監査</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>（教育）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>第16条　会社は、従業員に対して情報管理及び個人情報保護に関する教育を定期的に実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>（監査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、必要に応じて情報管理状況の監査を行い、改善を指示できる。従業員は監査に協力しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="8" customHeight="1">
+      <c r="A90" s="7" t="inlineStr"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
+    </row>
+    <row r="91" ht="10" customHeight="1"/>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>第6章　罰則</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>（懲戒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>第18条　従業員が本規程に違反した場合は、「懲戒規程」に基づき懲戒処分の対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2　会社に損害が生じた場合は、法令に基づき賠償責任を負うことがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="8" customHeight="1">
+      <c r="A97" s="7" t="inlineStr"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+    </row>
+    <row r="98" ht="10" customHeight="1"/>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　情報管理規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2491,7 +4347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3110,7 +4966,694 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>【第1条（目的）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>本規程は、株式会社dhpケアマネジメント　いいかいごにおける訪問介護・居宅サービス・サポート付き住宅運営において、従業者および利用者の安全と健康を確保し、事故防止、感染症対策、労働災害防止を推進することを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>【第2条（適用範囲）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>本規程は、当法人に所属する全従業者（常勤・非常勤・登録ヘルパー・夜勤スタッフ・看護職・事務職）および協力事業者に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>【第3条（安全衛生管理体制）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>1. 法人代表者は安全衛生管理の最高責任者である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2. 事業所管理者を安全衛生責任者とし、日常運営における安全衛生管理を統括する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>3. 必要に応じて安全衛生委員会を設置し、月1回協議を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>4. 委員会構成：管理者（委員長）、サービス提供責任者、看護職代表、介護職代表、夜勤代表、事務代表、管理部（事務局）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="8" customHeight="1">
+      <c r="A39" s="7" t="inlineStr"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="10" customHeight="1"/>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>第2章　安全管理に関する基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>【第4条（安全確保）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>1. 利用者の転倒・転落・誤嚥等の事故防止のため、環境整備と見守り体制を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2. 事故予兆の早期発見のため、報告体制を整備する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>3. 職員の安全確保のため、以下を徹底する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・腰痛予防（ノーリフティング・補助具使用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・夜勤単独リスク対策</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・暴力・ハラスメント防止対策</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・移動時の交通安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>【第5条（リスクアセスメント）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>以下を月1回以上評価する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>1. 転倒・転落リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2. 徘徊・不穏リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>3. 火災・災害時の避難リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>4. 福祉用具・医療機器リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>5. 夜間緊急リスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="8" customHeight="1"/>
+    <row r="59" ht="8" customHeight="1">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+    </row>
+    <row r="60" ht="10" customHeight="1"/>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>第3章　衛生管理に関する基本事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>【第6条（職員の健康管理）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>1. 年1回以上の健康診断を受診する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>2. 発熱・嘔吐・感染症疑いがある場合は出勤を禁止する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>3. 夜勤者の連続勤務禁止、長時間労働防止を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>【第7条（感染症予防）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>1. 手洗い・手指消毒・PPEなど標準予防策を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2. 感染発生時は隔離・動線確保・消毒を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>3. 新型コロナ・インフル・ノロ等は感染症マニュアルに従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="8" customHeight="1">
+      <c r="A72" s="7" t="inlineStr"/>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+    </row>
+    <row r="73" ht="10" customHeight="1"/>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>第4章　設備・環境衛生の管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>【第8条（環境整備）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>1. 廊下・階段・共有部の整理整頓を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2. 福祉用具は定期点検を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>3. 温度・湿度・換気を適切に管理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>4. 消防設備は年1回以上点検する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>【第9条（清掃・衛生管理）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>1. 共有部・トイレ・浴室の清掃を毎日行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2. 嘔吐物・感染性廃棄物はマニュアルに従い処理する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="8" customHeight="1">
+      <c r="A85" s="7" t="inlineStr"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+    </row>
+    <row r="86" ht="10" customHeight="1"/>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>第5章　職員教育・研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>【第10条（教育研修）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>1. 安全衛生・緊急対応・感染症・腰痛予防の研修を年2回以上行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2. 新入職員は初期研修で安全衛生教育を必須とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>3. 研修記録は5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>【第11条（情報共有）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>・事故・ヒヤリハットは速やかに共有し、再発防止策を検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>・委員会の審議内容は全従業者に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="8" customHeight="1">
+      <c r="A97" s="7" t="inlineStr"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+    </row>
+    <row r="98" ht="10" customHeight="1"/>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>第6章　事故・災害・緊急時対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>【第12条（事故対応）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>1. 事故発生時は応急処置、管理者報告、家族連絡、記録を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2. 必要に応じ医療機関へ搬送する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>【第13条（災害対応）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>1. 火災・地震・風水害等の発生時は避難計画に従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2. 夜勤帯は緊急連絡体制を強化する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>【第14条（緊急時マニュアル）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>全従業者は緊急時対応マニュアルを理解し、定期的に訓練を受ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="8" customHeight="1">
+      <c r="A111" s="7" t="inlineStr"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+    </row>
+    <row r="112" ht="10" customHeight="1"/>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>第7章　附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>【第15条（規程の見直し）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>本規程は年1回、または必要時に見直しを行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>【施行日】</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="76">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　安全衛生規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3773,7 +6316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4237,7 +6780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5077,7 +7620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6246,1176 +8789,4 @@
     <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E81"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>競業避止規程</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の事業上の正当な利益を保護し、従業員による競業行為を防止するとともに、従業員の職業選択の自由との調和を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>第2条　本規程は、会社に雇用される従業員のうち、経営管理、営業、研究開発その他会社が特に指定する者に適用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2　派遣社員、業務委託契約者等については、個別契約に基づき適用することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="8" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>（定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>第3条　本規程における「競業行為」とは、会社と同一または類似の事業を営む行為、会社と競合する他社への就業、または会社の取引先を利用して自己または第三者の利益を図る行為をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="8" customHeight="1">
-      <c r="A37" s="7" t="inlineStr"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-    </row>
-    <row r="38" ht="10" customHeight="1"/>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>第2章　在職中の義務</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>（競業禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>第4条　従業員は、在職中、会社の承認なく競業行為を行ってはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>（副業・兼業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>第5条　従業員は、副業・兼業を行う場合であっても、会社の業務に支障を及ぼさず、かつ競業行為に該当しない範囲に限り許可される。詳細は「人事管理規程」及び「副業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="8" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>（秘密情報の利用禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>第6条　従業員は、在職中に知り得た会社の秘密情報を利用して競業行為を行ってはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="8" customHeight="1"/>
-    <row r="49" ht="8" customHeight="1">
-      <c r="A49" s="7" t="inlineStr"/>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-    </row>
-    <row r="50" ht="10" customHeight="1"/>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>第3章　退職後の義務</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>（競業避止義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>第7条　管理職、営業担当その他会社が特に指定した従業員は、退職後1年間、会社が営業する地域（大阪府・兵庫県・京都府・奈良県）において、会社と競合する事業に従事してはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="8" customHeight="1"/>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>（合理的範囲の限定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>第8条　前条の地域・期間は、会社の事業規模、従業員の職務内容、社会通念を考慮し、合理的な範囲に限定される。過度に広範な競業禁止は適用しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>（補償）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>第9条　会社は、退職後競業避止義務を個別合意で課す場合、社会通念上相当と認められる補償を行う。補償の内容は合意時に明示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="8" customHeight="1"/>
-    <row r="61" ht="8" customHeight="1">
-      <c r="A61" s="7" t="inlineStr"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-    </row>
-    <row r="62" ht="10" customHeight="1"/>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>第4章　管理・措置</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>（特別合意）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>第10条　会社は、必要に応じ、従業員との間で退職後競業避止に関する特別合意を締結することができる。その場合、地域、期間、業務範囲及び補償内容を明示する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="8" customHeight="1"/>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>（違反時の措置）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>第11条　従業員が在職中に本規程に違反した場合は「懲戒規程」に基づき懲戒処分の対象とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>2　従業員が退職後に本規程に違反し会社に損害を与えた場合は、会社は法令に基づき損害賠償を請求することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="8" customHeight="1"/>
-    <row r="71" ht="8" customHeight="1">
-      <c r="A71" s="7" t="inlineStr"/>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
-      <c r="E71" s="8" t="n"/>
-    </row>
-    <row r="72" ht="10" customHeight="1"/>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>第5章　雑則</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>（他規程との関係）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>第12条　本規程に定めのない事項は、就業規則、情報管理規程、秘密保持契約その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="8" customHeight="1"/>
-    <row r="77" ht="8" customHeight="1">
-      <c r="A77" s="7" t="inlineStr"/>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-    </row>
-    <row r="78" ht="10" customHeight="1"/>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程施行前に締結された労働契約その他の合意についても、本規程に反しない範囲で適用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>2　本規程は令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　競業避止規程</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E137"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>育児・介護休業規程</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員が、育児・介護休業法その他関係法令に基づき、仕事と育児・介護を両立できるよう育児休業、介護休業等の制度を定め、従業員の職業生活の安定と充実を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>第2条　本規程は、会社に雇用される全ての正社員に適用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2　契約社員、嘱託社員、パートタイマー等については、労働契約書において別段の定めがある場合を除き、本規程を準用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="8" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>（定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>第3条　本規程における用語の定義は、育児・介護休業法に準拠し、次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>1　「育児休業」：満1歳に満たない子を養育するために取得する休業をいう。ただし、一定の場合は1歳6か月、さらに2歳まで延長できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>2　「介護休業」：要介護状態にある家族（法令に定める範囲）を介護するために取得する休業をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>3　「子の看護等休暇」：小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のために取得できる休暇をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>5　「出生時育児休業」：子の出生後8週間以内に4週間（28日）まで取得できる休業をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>4　「介護休暇」：要介護状態にある家族の介護や通院付添のために取得できる休暇をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="8" customHeight="1">
-      <c r="A42" s="7" t="inlineStr"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="10" customHeight="1"/>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>第2章　育児休業</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>（育児休業の取得要件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>第4条　従業員は、1歳に満たない子を養育する場合、会社に申し出ることにより育児休業を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>2　育児休業は、子1人につき原則2回まで分割して取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>3　労使協定により、次の者を育児休業の対象から除外することがある。（1）継続雇用期間が1年未満の者　（2）申出の日から1年以内に雇用関係が終了することが明らかな者　（3）1週間の所定労働日数が2日以下の者</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>4　有期雇用の従業員は、子が1歳6か月に達する日までに労働契約が満了し更新されないことが明らかでない場合に取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>（育児休業の期間）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>第5条　育児休業の期間は、原則として子が1歳に達するまでとする。ただし、保育所に入所できない場合等、法令の定めに従い1歳6か月、最長2歳まで延長できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>（育児休業の申出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>第6条　育児休業を取得しようとする従業員は、原則として休業開始予定日の1か月前までに、所定の書式により会社へ申し出なければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="8" customHeight="1"/>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>（出生時育児休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>第6条の2　従業員は、子の出生後8週間以内に、4週間（28日）を限度として、2回まで分割して出生時育児休業を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>2　出生時育児休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに会社へ申し出なければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="8" customHeight="1"/>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>（育児休業中の処遇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>第7条　育児休業中は無給とする。ただし、雇用保険法に基づき育児休業給付金の受給が可能である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>2　社会保険料の免除については、健康保険法及び厚生年金保険法の定めに従う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="8" customHeight="1">
-      <c r="A65" s="7" t="inlineStr"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-    </row>
-    <row r="66" ht="10" customHeight="1"/>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>第3章　介護休業</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>（介護休業の取得要件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>第8条　従業員は、要介護状態にある家族を介護する場合、会社に申し出ることにより介護休業を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="8" customHeight="1"/>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>（介護休業の期間）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>第9条　介護休業は、対象家族1人につき通算93日まで取得できる。分割して3回まで分けて取得することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="8" customHeight="1"/>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>（介護休業の申出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>第10条　介護休業を取得しようとする従業員は、原則として休業開始予定日の2週間前までに、所定の書式により会社へ申し出なければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="8" customHeight="1"/>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>（介護休業中の処遇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>第11条　介護休業中は無給とする。ただし、雇用保険法に基づき介護休業給付金の受給が可能である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="8" customHeight="1">
-      <c r="A80" s="7" t="inlineStr"/>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="10" customHeight="1"/>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>第4章　子の看護等休暇・介護休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>（子の看護等休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="48" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、小学校第3学年修了までの子の看護、予防接種・健康診断、感染症に伴う学級閉鎖等、入園（入学）式・卒園式への出席のため、年5日（子が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>2　子の看護等休暇は、1日または時間単位で取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>（介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、要介護状態にある家族の介護や通院付添のため、年5日（対象家族が2人以上の場合は年10日）を限度として休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>2　介護休暇は、1日または時間単位で取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="8" customHeight="1"/>
-    <row r="91" ht="8" customHeight="1">
-      <c r="A91" s="7" t="inlineStr"/>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-    </row>
-    <row r="92" ht="10" customHeight="1"/>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>第4章の2　働き方の制限・措置</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>（所定外労働の制限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>第13条の2　小学校就学前の子を養育する従業員、または要介護状態にある家族を介護する従業員が請求した場合、事業の正常な運営を妨げる場合を除き、所定労働時間を超えて労働させない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>（時間外労働・深夜業の制限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="48" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>第13条の3　前条の従業員が請求した場合、時間外労働は1か月24時間、1年150時間を超えないものとし、深夜（午後10時から午前5時まで）に労働させない。ただし、法令に定める除外者はこの限りでない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="8" customHeight="1"/>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>（短時間勤務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>第13条の4　3歳に満たない子を養育する従業員、または要介護状態にある家族を介護する従業員は、申し出により、所定労働時間を1日6時間とする短時間勤務を利用できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="8" customHeight="1"/>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>（柔軟な働き方を実現するための措置）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>第13条の5　3歳から小学校就学前の子を養育する従業員に対し、会社は次の措置を講じ、従業員はいずれか1つを選択して利用できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>1　始業・終業時刻の変更（時差出勤）</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>2　養育両立支援休暇（年10日、時間単位で取得可）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="8" customHeight="1"/>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>（個別周知・意向確認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>第13条の6　会社は、従業員から本人または配偶者の妊娠・出産の申出があったとき、及び子が3歳になる前の適切な時期に、育児休業等の制度を個別に周知し、取得や働き方の意向を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>2　会社は、従業員から家族の介護に直面した旨の申出があったとき、介護休業等の制度を個別に周知し、意向を確認する。また、40歳に達した従業員に対し、介護両立支援制度の情報を提供する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>（ハラスメントの防止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>第13条の7　会社は、妊娠・出産、育児休業・介護休業等の利用に関する言動により従業員の就業環境が害されることのないよう、相談体制の整備その他必要な措置を講じる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="8" customHeight="1"/>
-    <row r="115" ht="8" customHeight="1">
-      <c r="A115" s="7" t="inlineStr"/>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-    </row>
-    <row r="116" ht="10" customHeight="1"/>
-    <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>第5章　復職・不利益取扱い禁止</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>（復職）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="48" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>第14条　育児休業または介護休業を終了した従業員は、原則として休業前と同じ職務に復職させる。ただし、業務運営上やむを得ない場合は、同等の地位・待遇を有する職務に配置することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="8" customHeight="1"/>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>（不利益取扱い禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="32" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>第15条　会社は、従業員が育児休業・出生時育児休業・介護休業・子の看護等休暇・介護休暇その他本規程の制度を利用したことを理由として、解雇その他不利益な取扱いをしてはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="8" customHeight="1"/>
-    <row r="124" ht="8" customHeight="1">
-      <c r="A124" s="7" t="inlineStr"/>
-      <c r="B124" s="8" t="n"/>
-      <c r="C124" s="8" t="n"/>
-      <c r="D124" s="8" t="n"/>
-      <c r="E124" s="8" t="n"/>
-    </row>
-    <row r="125" ht="10" customHeight="1"/>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>第6章　雑則</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>（制度の周知）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="32" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>第16条　会社は、本規程の内容を就業規則とともに従業員へ周知し、希望者が適切に制度を利用できるよう努めなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="8" customHeight="1"/>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>（個人情報保護）</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="32" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>第17条　会社は、休業申請や取得に関して知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="8" customHeight="1">
-      <c r="A133" s="7" t="inlineStr"/>
-      <c r="B133" s="8" t="n"/>
-      <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
-      <c r="E133" s="8" t="n"/>
-    </row>
-    <row r="134" ht="10" customHeight="1"/>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、育児・介護休業法、就業規則その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>2　本規程は、令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A136:E136"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A119:E119"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A127:E127"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A117:E117"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　育児・介護休業規程</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
 </file>
--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,13 +65,27 @@
       <name val="Arial"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -94,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -135,6 +150,29 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3059,6 +3097,1494 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E207"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>感染症対策指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Ⅰ．平常時の対策</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>1．総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>（1）目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護事業者には、利用者の居宅において、利用者の健康と安全を守るための支援が求められている。訪問介護員は複数の利用者宅を訪問するため、職員が感染を媒介するおそれがあり、利用者の安全確保の観点から感染対策はきわめて重要である。感染を未然に防止し、発生した場合には感染症が拡大しないよう可及的速やかに対応する体制を構築することが必要である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>この指針は、感染予防・再発防止対策及び感染症発生時の適切な対応など、事業所における感染予防対策体制を確立し、適切かつ安全で、質の高いサービスの提供を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2．体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>（1）委員会の設置・運営</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>1　目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>事業所における感染症の発生や感染拡大を防止するために、感染対策委員会を設置する。感染対策委員会は、虐待防止委員会等の事業所の他の委員会と独立して設置・運営する。なお、他の会議体と一体的に開催することを妨げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2　位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>代表取締役</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>感染対策委員会</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>虐待防止委員会</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>身体拘束適正化委員会</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>サービス提供責任者</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>訪問介護員</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>事務職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>3　活動内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>感染対策委員会の主な活動内容は、以下の通りとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事業所の感染課題を明確にし、感染対策の方針・計画を定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染予防に関する決定事項や具体的対策を事業所全体に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事業所における感染に関する問題を把握し、問題意識を共有・解決する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・職員の健康状態を把握する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染症が発生した場合、適切に対処するとともに、感染対策及び拡大防止の指揮を執る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・その他、感染関連の検討が必要な場合に、対処する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>4　委員会構成メンバー</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>感染対策委員会は、次のメンバーで構成する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・管理者（委員長）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス提供責任者（感染対策担当者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問介護員の代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事務職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて、外部の感染対策の専門家（医師・看護師・保健所等）の助言を得る</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>5　運営方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>感染対策委員会は、おおむね6か月に1回以上（4月・10月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>会議の詳細（実施時間や内容、検討事項、開催方法等）は、感染対策委員会開催1週間前までに管理者より各メンバーへ連絡する。結果は記録し、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>（2）役割分担</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>各担当の役割分担は、以下の通りとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>事業所全体の管理、感染対策委員会の運営</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="20" t="n"/>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="21" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>感染対策担当者
+感染対策の立案・指導
+利用者・職員の健康状態の把握</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="21" t="inlineStr">
+        <is>
+          <t>サービス提供責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>訪問現場における感染対策の実施
+利用者の体調変化の報告</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="21" t="inlineStr">
+        <is>
+          <t>訪問介護員</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>委員会実施のための連絡・調整、記録の管理
+衛生用品の在庫管理</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="n"/>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
+          <t>事務職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>（3）指針の整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>感染対策委員会は、感染に関する最新の情報を把握し、研修や訓練を通して課題を見つけ、定期的に指針を見直し、更新する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="10" customHeight="1"/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>（4）研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>感染対策の基本的内容等の適切な知識を普及・啓発するとともに、本指針に基づいた衛生管理の徹底や衛生的な支援の励行を行うものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>指針に基づいた研修プログラムを作成し、全職員（登録ヘルパーを含む）を対象に定期的に年2回以上、かつ、新規採用時に感染対策研修を実施する。研修の企画、運営、実施記録の作成は、感染対策委員会が実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>全職員</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>新規入職者</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="n"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>開催時期</t>
+        </is>
+      </c>
+      <c r="B82" s="21" t="inlineStr">
+        <is>
+          <t>5月・11月</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>入職時</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="n"/>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>感染予防対策と
+感染症発生時の対応方法</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>感染対策の重要性と
+標準予防策の理解</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="n"/>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>研修講師は、感染対策委員会が任命する。研修内容の詳細（開催日時、講師、方法、内容等）は、研修1か月前に、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="10" customHeight="1"/>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>（5）訓練</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>感染者発生時において迅速に行動できるよう、発生時の対応を定めた本指針及び研修内容に基づき、全職員を対象に年2回以上の訓練（シミュレーション）を実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="48" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>内容は、役割分担の確認や、感染対策をした上での訪問介護の演習（個人防護具の着脱等）などを実施するものとする。訓練方法は、机上訓練と実地訓練を組み合わせながら実施する。訓練の企画、運営、実施記録の作成は、感染対策委員会が実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>訓練内容の詳細（開催日時、実施方法、内容等）は、訓練1か月前に、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>全職員</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="n"/>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>全職員</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="n"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>開催時期</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n"/>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="n"/>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>感染対策マニュアルや
+感染症BCPを利用した行動確認</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>感染症発生時の対応訓練
+（個人防護具の着脱等）</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="n"/>
+    </row>
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>3．日常の支援にかかる感染管理（平常時の対策）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>（1）利用者の健康管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>主担当：サービス提供責任者（副担当：管理者）を中心に利用者の健康を管理するために必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　サービス開始前に、既往歴や感染症の有無について把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　訪問時に利用者の様子を観察し、体調の把握に努める</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　利用者の体調、様子などを、居宅介護支援事業所（ケアマネジャー）や家族と共有する方法を構築する</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　利用者・家族に対し、感染対策の方法を説明し、協力を依頼する</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　利用者の感染対策実施状況を把握し、不足している対策を支援する</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>（2）職員の健康管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に職員の健康を管理するために必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　入職時の感染症の既往やワクチン接種状況を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　定期健康診断の必要性を説明し、受診状況を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　訪問前に検温等を行い、職員の体調把握に努める</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　体調不良時の申告方法を周知し、申告しやすい環境を整える。発熱等の症状がある職員は訪問させない</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　職員へ感染対策の方法を教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6　職員の感染に対する知識を評価し、不足している部分に対し、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7　ワクチン接種の必要性を説明し、接種を推奨する</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　8　業務中に感染した場合の方針を明確にし、対応について準備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>（3）標準的な感染予防策</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>主担当：サービス提供責任者（副担当：管理者）を中心に、標準的な感染予防策の実施に必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>A．職員の感染予防策</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　訪問の前後及びケアの前後の手指衛生の実施状況（方法、タイミングなど）を評価し、適切な方法を教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　個人防護具（手袋・マスク・エプロン等）の使用状況（着用しているケアと着用状況、着脱方法など）を評価し、適切な方法を教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　食事介助時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　排泄介助・おむつ交換時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　入浴介助・清拭時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6　上記以外の支援時の対応を確認し、適切な方法を指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="8" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>B．利用者の感染予防策</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　食事前、排泄後の手洗い状況を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　手指を清潔に保つために必要な支援について検討し、実施する</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　居宅内で共用する物品（タオル・食器等）の使用状況を把握し、清潔な管理を助言する</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="8" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>C．その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　個人防護具・消毒液等の衛生用品を十分に確保し、管理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　訪問用の衛生用品セットを準備し、訪問介護員が常に携行できるようにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="8" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>（4）衛生管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>主担当：サービス提供責任者（副担当：管理者）を中心に、衛生管理に必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>A．環境整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　事業所内の整理整頓、清掃を計画的に実施し、実施状況を評価する</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　事業所及び利用者宅の換気の状況（方法や時間）を把握し、助言する</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　利用者宅での掃除援助において、トイレ・洗面所等の清掃を適切に行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　効果的な環境整備について、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>B．食品衛生（調理援助時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　食品の購入、保管状況（冷蔵庫内の期限切れ食品等）を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　調理工程の衛生状況（手洗い、加熱、まな板・包丁の使い分け等）を確認し、評価する</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　調理を行う訪問介護員の衛生状況を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　課題を検討し、対策を講じる</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　衛生的に調理できるよう、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="8" customHeight="1"/>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>C．血液・体液・排泄物等の処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　標準予防策について指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　ケアごとの標準予防策を策定し、周知する</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　嘔吐物・排泄物等の処理方法、処理状況を確認する。処理用品を訪問用セットに含める</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　使用済みのおむつ・手袋等は、利用者宅の廃棄ルールに従い、ビニール袋で密閉して処理する</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　適切な血液・体液・排泄物等の処理方法について、教育、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="8" customHeight="1"/>
+    <row r="156" ht="26" customHeight="1">
+      <c r="A156" s="15" t="inlineStr">
+        <is>
+          <t>Ⅱ．発生時の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="26" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>1．発生状況の把握</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、感染症発生時の状況を把握するための必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　感染者及び感染疑い者（利用者・職員）の状況を把握し、情報を共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　事業所全体（訪問先の利用者を含む）の感染者及び感染疑い者の発生状況を調査し、把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　感染者等を訪問した訪問介護員及び訪問先を特定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="8" customHeight="1"/>
+    <row r="163" ht="26" customHeight="1">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>2．感染拡大の防止</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="32" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、感染拡大防止のために必要な対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="32" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　感染者及び感染疑い者への訪問方法（訪問順を最後にする、担当者を限定する等）を検討し、周知、指導する</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　訪問介護員は、個人防護具を適切に着用し、感染者及び感染疑い者への支援方法を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="32" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　感染状況を本人・家族へ説明し、感染対策（マスクの着用、手指衛生、換気など）の協力を依頼する</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　感染者及び感染疑い者と接触した関係者（職員、家族など）の体調を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5　ウイルスや細菌に効果的な消毒薬を選定し、消毒を実施する</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6　職員の感染対策の状況を確認し、感染対策の徹底を促す</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7　訪問継続が困難な場合は、居宅介護支援事業所と連携し、サービス調整を行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="8" customHeight="1"/>
+    <row r="173" ht="26" customHeight="1">
+      <c r="A173" s="15" t="inlineStr">
+        <is>
+          <t>3．医療機関や保健所、行政関係機関との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、必要な公的機関との連携について対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>A．医療機関との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　主治医へ感染者及び感染疑い者の状態を報告し、対応方法を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　受診の協力を依頼する</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　医療機関からの指示内容を事業所内で共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="8" customHeight="1"/>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>B．保健所との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　疾病の種類、状況により報告を検討する</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　感染者及び感染疑い者の状況を報告し、指示を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　保健所からの指導内容を正しく全職員に共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="8" customHeight="1"/>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>C．行政関係機関との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　大阪市への報告の必要性について検討する</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　感染者及び感染疑い者の状況を報告し、指示を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="8" customHeight="1"/>
+    <row r="189" ht="26" customHeight="1">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>4．関係者への連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="32" customHeight="1">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、関係先との情報共有や連携について対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　事業所内・法人内での情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　利用者家族との情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　居宅介護支援事業所（ケアマネジャー）との情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4　利用者が利用している他のサービス事業所との情報共有体制を構築、整備する</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="8" customHeight="1"/>
+    <row r="196" ht="26" customHeight="1">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>5．感染者発生後の支援（利用者、職員ともに）</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="32" customHeight="1">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>主担当：管理者（副担当：サービス提供責任者）を中心に、感染者の支援（心のケアなど）について対策を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　感染者及び感染疑い者の病状や予後を把握する</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　感染者及び関係者の精神的ケアを行う体制を構築する</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　感染症からの回復後のサービス再開について、居宅介護支援事業所と調整する</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="8" customHeight="1"/>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>＜変更・廃止手続＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>本指針の変更および廃止は、感染対策委員会の審議を経て、代表取締役が決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="8" customHeight="1"/>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>本指針は、令和8年2月1日から適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="23" t="inlineStr">
+        <is>
+          <t>以上</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="157">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="A166:E166"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A207:E207"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A182:E182"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="A168:E168"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A192:E192"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="A194:E194"/>
+    <mergeCell ref="A203:E203"/>
+    <mergeCell ref="A181:E181"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A171:E171"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A196:E196"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A205:E205"/>
+    <mergeCell ref="A183:E183"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A198:E198"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A159:E159"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A200:E200"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A186:E186"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A197:E197"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A187:E187"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A174:E174"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A189:E189"/>
+    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="A160:E160"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A206:E206"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A199:E199"/>
+    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A191:E191"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A178:E178"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A163:E163"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A180:E180"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A190:E190"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　感染症対策指針</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -3415,7 +3415,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>感染対策委員会は、おおむね6か月に1回以上（4月・10月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
+          <t>感染対策委員会は、おおむね6か月に1回以上（6月・11月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>5月・11月</t>
+          <t>6月・11月</t>
         </is>
       </c>
       <c r="C82" s="22" t="n"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="C92" s="22" t="n"/>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="賃金規程" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1221,6 +1222,1177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E193"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>福利厚生規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における福利厚生制度に関し必要な事項を定め、従業員の生活の安定と向上、健康保持、能力開発及び職場環境の充実を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての正社員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2　契約社員、嘱託社員、パートタイマー等については、雇用契約書において別途定めがある場合を除き、本規程を準用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="8" customHeight="1">
+      <c r="A34" s="7" t="inlineStr"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="10" customHeight="1"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>第2章　法定福利厚生</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>（社会保険）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>第3条　会社は、健康保険、厚生年金保険、雇用保険及び労災保険の適用事業所として、法令に基づき従業員を加入させ、会社負担分の保険料を負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="8" customHeight="1">
+      <c r="A40" s="7" t="inlineStr"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+    </row>
+    <row r="41" ht="10" customHeight="1"/>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>第3章　通勤手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>（支給対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>第4条　会社は、従業員の通勤に要する費用について、次の範囲内で通勤手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>1　公共交通機関を利用する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2　片道2km以上の自動車・バイクによる通勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>3　自転車による通勤</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>4　その他事前申請の上会社が認めた通勤方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>（支給基準および額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>第5条　通勤手当の支給額は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>1　公共交通機関の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>（1）定期券を購入している場合はその額</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>（2）定期券を購入していない場合は、実費または1か月分の定期代相当額</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>ただし、いずれの場合も上限は月額50,000円とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2　自動車・バイクによる場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>（1）往復距離 × 出勤日数 × 20円</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>（2）月額の上限は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>片道距離</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>上限（月額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>2km以上10km未満</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>4,200円</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>10km以上15km未満</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>7,100円</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>15km以上25km未満</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>12,900円</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>25km以上35km未満</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>18,700円</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>35km以上45km未満</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>24,400円</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>45km以上55km未満</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>28,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>55km以上</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>31,600円</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>3　自転車による場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>（1）1日あたり100円 × 出勤日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>（2）月額上限は2,500円とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>4　その他事前申請の上会社が認めた通勤方法の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>会社が合理的と認める方法により算出する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>（申請・承認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>第6条　通勤手当の支給を受けるには、従業員が所定の様式により通勤方法、経路、実費額を申請し、会社の承認を得なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2　通勤経路が複数ある場合、会社は合理的かつ経済的と認められる経路を通勤経路として指定できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>（例外支給）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>第7条　会社が必要と判断した場合には、前条の基準を超えて通勤手当を支給することがある。その場合、当該支給額は課税対象となる可能性があることを従業員は承知するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="8" customHeight="1"/>
+    <row r="83" ht="8" customHeight="1">
+      <c r="A83" s="7" t="inlineStr"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+    </row>
+    <row r="84" ht="10" customHeight="1"/>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>第4章　特別通勤手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>（支給対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>第8条　会社は、従業員が通勤のために負担した駐輪場利用料等について、次のとおり特別通勤手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>1　駐輪場の月極契約金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2　一時利用料 × 出勤日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>3　その他事前申請の上会社が合理的と認めるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="8" customHeight="1"/>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>（支給限度額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>第9条　特別通勤手当の上限は月額10,000円とする。超過分は従業員負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="8" customHeight="1">
+      <c r="A95" s="7" t="inlineStr"/>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+    </row>
+    <row r="96" ht="10" customHeight="1"/>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>第5章　住宅手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>第10条　本手当に関する用語の定義は、次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>1　「社員」とは、会社に雇用される全ての正社員をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2　「賃料」とは、賃貸借契約書に記載された月額家賃をいい、共益費・管理費・水道光熱費等の付帯費用は含まないものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>3　「対象住宅」とは、社員が自己名義または同居配偶者名義の賃貸住宅に居住するものをいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>（支給対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>第11条　本手当の支給対象者は、第10条に定義する対象住宅に居住し、本規程に定める申請手続きを完了した社員とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2　配偶者等が他の会社から住宅手当を受給している場合、当該社員は本手当の支給対象外とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>（支給要件・申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>第12条　住宅手当を受給しようとする社員は、次の書類をマネジメント本部長宛てに提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>1　住宅手当申請書兼誓約書（賃料、配偶者等が他社から住宅手当を受給していないことの念書を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2　賃貸借契約書の写し（賃料確認用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>3　同居家族構成届（氏名、続柄、生年月日、同居・別居区分を明記）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>4　世帯主証明書（住民票の写し等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2　同月中に申請がない場合は当該月分の支給を受けられない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>3　賃料が減少した場合は、遅滞なくマネジメント本部へ変更届を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>（支給額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>第13条　住宅手当額は、賃料（月額）×30％の金額を算出し、100円未満を切り上げた額とする。ただし、支給額が30,000円を超える場合は30,000円を上限とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>（変更届出義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>第14条　住宅手当に関わる以下の事項に変更が生じた場合、社員は速やかにマネジメント本部へ届出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>1　賃料額の増減</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>2　住居の転居または同居家族構成の変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="8" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>（不正受給時の措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>第15条　虚偽の申請または書類偽造等により住宅手当を受給した場合、会社は既に支給した住宅手当の全額返還を命じるとともに、懲戒規程に基づき処分を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="8" customHeight="1"/>
+    <row r="128" ht="8" customHeight="1">
+      <c r="A128" s="7" t="inlineStr"/>
+      <c r="B128" s="8" t="n"/>
+      <c r="C128" s="8" t="n"/>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="8" t="n"/>
+    </row>
+    <row r="129" ht="10" customHeight="1"/>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>第6章　生活支援・慶弔関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>（食事補助手当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>第16条　会社は、従業員に対し、月額10,000円の食事補助手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>2　パートタイマー等の所定労働日数が少ない従業員については、出勤日数に応じて按分して支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="8" customHeight="1"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>（制服・作業着）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="32" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>2　制服または作業着は、原則として従業員が自ら準備するものとする。ただし、会社が特に必要と認めた場合は、会社が貸与または支給することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>（慶弔給付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>1　結婚祝い金：30,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>2　出産祝い金：30,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>4　災害見舞金：取締役会の判断により、最大100,000円を限度として支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="8" customHeight="1"/>
+    <row r="146" ht="8" customHeight="1">
+      <c r="A146" s="7" t="inlineStr"/>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="8" t="n"/>
+    </row>
+    <row r="147" ht="10" customHeight="1"/>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>第7章　健康・医療支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>（健康診断）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="32" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>第19条　会社は、労働安全衛生法に基づき、従業員に対し年1回の健康診断を実施し、費用を会社が負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>2　夜勤に従事する従業員については、年2回実施し、費用は会社が負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="8" customHeight="1"/>
+    <row r="153" ht="8" customHeight="1">
+      <c r="A153" s="7" t="inlineStr"/>
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+    </row>
+    <row r="154" ht="10" customHeight="1"/>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>第8章　教育研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>（外部研修）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>第20条　会社は、業務に資すると判断される外部研修について、参加費用を全額負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="8" customHeight="1"/>
+    <row r="159" ht="8" customHeight="1">
+      <c r="A159" s="7" t="inlineStr"/>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="8" t="n"/>
+    </row>
+    <row r="160" ht="10" customHeight="1"/>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>第9章　特別休暇に関連する給付</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>（誕生日休暇・手当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>第21条　会社は、休暇規程に基づき誕生日休暇を付与するとともに、当該休暇を取得した従業員に対して誕生日手当として10,000円を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="8" customHeight="1"/>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>（特別休暇に伴う給付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>第22条　会社は、休暇規程に基づき付与される特別休暇について、必要に応じて記念品、金銭その他の給付を行うことができる。内容は取締役会の決議により定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="8" customHeight="1"/>
+    <row r="168" ht="8" customHeight="1">
+      <c r="A168" s="7" t="inlineStr"/>
+      <c r="B168" s="8" t="n"/>
+      <c r="C168" s="8" t="n"/>
+      <c r="D168" s="8" t="n"/>
+      <c r="E168" s="8" t="n"/>
+    </row>
+    <row r="169" ht="10" customHeight="1"/>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>第10章　運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>（支給方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>第23条　通勤手当、特別通勤手当及び各種手当は、毎月1日から末日までの1か月分を集計し、当月の給与と併せて支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="8" customHeight="1"/>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>（中途入社・退職時の取扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>第24条　月中に入社または退職した者についても、出勤日数に応じて日割り計算で支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="8" customHeight="1"/>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>（休職・休暇・在宅勤務時の取扱い）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>第25条　休職中・休暇中・休業中または在宅勤務の場合、通勤手当及び特別通勤手当は支給しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="8" customHeight="1"/>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>（虚偽申請の禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>第26条　通勤手当、特別通勤手当、住宅手当その他各種手当の申請に虚偽が発覚した場合、会社は入社時に遡って再計算を行い、超過支給分を返還請求できるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="8" customHeight="1"/>
+    <row r="183" ht="8" customHeight="1">
+      <c r="A183" s="7" t="inlineStr"/>
+      <c r="B183" s="8" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
+      <c r="E183" s="8" t="n"/>
+    </row>
+    <row r="184" ht="10" customHeight="1"/>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>第11章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>（周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>第27条　会社は、本規程の内容を従業員に周知し、常時確認できるよう掲示またはイントラネット等で公開する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="8" customHeight="1"/>
+    <row r="189" ht="8" customHeight="1">
+      <c r="A189" s="7" t="inlineStr"/>
+      <c r="B189" s="8" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="8" t="n"/>
+    </row>
+    <row r="190" ht="10" customHeight="1"/>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="122">
+    <mergeCell ref="A166:E166"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A168:E168"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A192:E192"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="A181:E181"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A171:E171"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A183:E183"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A175:E175"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A159:E159"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A186:E186"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A172:E172"/>
+    <mergeCell ref="A187:E187"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A174:E174"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A189:E189"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A151:E151"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A191:E191"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A178:E178"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A162:E162"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A163:E163"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A180:E180"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　福利厚生規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1626,7 +2798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2387,7 +3559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3097,7 +4269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4591,6 +5763,648 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E116"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>賃金規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に支給する賃金の基本事項を定め、労働基準法その他関係法令を遵守しつつ、公正かつ適正な賃金管理を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2　嘱託社員、短時間勤務者、アルバイト等の賃金については、別に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>（賃金の構成）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>第3条　賃金は、次の項目から構成する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>1　基本給</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2　諸手当（役職手当、資格手当、夜勤手当、住宅手当、業務手当その他）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>3　通勤手当・特別通勤手当（「福利厚生規程」による）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>4　割増賃金（時間外・休日・深夜）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>5　賞与（年2回）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>6　その他会社が定めるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="8" customHeight="1">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+    </row>
+    <row r="44" ht="10" customHeight="1"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>第2章　基本給・手当</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>（基本給）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>第4条　基本給は、従業員の職務内容、能力、経験、勤務成績等を考慮して決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>（諸手当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>第5条　会社は、役職手当、資格手当、夜勤手当、住宅手当、業務手当その他会社が必要と認める手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2　手当の名称、金額、支給基準、算定方法その他詳細は「手当支給規程」及び「福利厚生規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>（通勤手当・特別通勤手当）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>第6条　従業員の通勤に要する交通費等については、通勤手当または特別通勤手当を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2　通勤手当および特別通勤手当の支給条件、算定方法、上限額等は「福利厚生規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="8" customHeight="1">
+      <c r="A57" s="7" t="inlineStr"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+    </row>
+    <row r="58" ht="10" customHeight="1"/>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>第3章　賞与・昇給</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>（賞与）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>第7条　会社は、業績、勤務成績、勤怠状況その他を総合的に勘案し、年2回賞与を支給する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>2　賞与の支給額、基準、計算方法は会社の決定による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>3　賞与の在職要件等、支給対象の範囲は別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>（昇給）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>第8条　昇給は、勤務成績、能力、会社の業績その他を総合的に勘案し、会社の定めるところにより実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="8" customHeight="1">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+    </row>
+    <row r="69" ht="10" customHeight="1"/>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>第4章　賃金の支払</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>（締切日・支払日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>第9条　賃金の締切日は毎月末日とし、翌月27日に支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2　支払日が土曜日、日曜日または祝日にあたる場合は、直前の平日に繰り上げて支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>3　賃金は、従業員の同意を得て、従業員が指定する銀行口座への振込により支払う。振込手数料は会社負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>（控除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>第10条　賃金からは法令に基づく税金、社会保険料等を控除する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2　前項以外の控除は、労使協定を締結した場合に限り行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="8" customHeight="1">
+      <c r="A80" s="7" t="inlineStr"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="8" t="n"/>
+    </row>
+    <row r="81" ht="10" customHeight="1"/>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>第5章　割増賃金</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>（時間外労働の割増率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>第11条　法定労働時間を超えて労働させた場合は、通常の労働時間の賃金の25％以上を加算して支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2　月60時間を超える時間外労働については、50％以上の率で支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>（休日労働の割増率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>第12条　法定休日に労働させた場合は、通常の労働時間の賃金の35％以上を加算して支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>（深夜労働の割増率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>第13条　午後10時から翌午前5時までの労働については、通常の労働時間の賃金の25％以上を加算して支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>（重複適用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>第14条　時間外労働、休日労働および深夜労働が重複した場合は、各割増率を合算して支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="8" customHeight="1">
+      <c r="A96" s="7" t="inlineStr"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+    </row>
+    <row r="97" ht="10" customHeight="1"/>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>第6章　欠勤・遅刻・控除</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>（欠勤・遅刻等の控除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>第15条　欠勤、遅刻、早退その他により所定労働時間を労務提供しなかった場合は、その時間または日数に応じて賃金を控除する。算定方法は別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="8" customHeight="1"/>
+    <row r="102" ht="8" customHeight="1">
+      <c r="A102" s="7" t="inlineStr"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
+    </row>
+    <row r="103" ht="10" customHeight="1"/>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>第7章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>（非常時の賃金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="48" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>第16条　天災地変その他不可抗力により業務が休止した場合の賃金の取扱いは、労働基準法その他関係法令の定めによる。会社の責に帰すべき事由により休業させた場合は、休業手当（平均賃金の100分の60以上）を支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="8" customHeight="1"/>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>（不支給・減額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>第17条　従業員が懲戒解雇された場合、退職金や賞与の全部または一部を不支給とすることがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2　従業員が著しい服務規律違反を行った場合、賞与や特別手当の減額または不支給とすることがある。詳細は「懲戒規程」「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="8" customHeight="1">
+      <c r="A112" s="7" t="inlineStr"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
+    </row>
+    <row r="113" ht="10" customHeight="1"/>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="70">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　賃金規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5107,7 +6921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5873,7 +7687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6492,7 +8306,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7179,7 +8993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7842,7 +9656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8306,7 +10120,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9144,1175 +10958,4 @@
     <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E193"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>福利厚生規程</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における福利厚生制度に関し必要な事項を定め、従業員の生活の安定と向上、健康保持、能力開発及び職場環境の充実を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>第2条　本規程は、会社に雇用されるすべての正社員に適用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2　契約社員、嘱託社員、パートタイマー等については、雇用契約書において別途定めがある場合を除き、本規程を準用する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="8" customHeight="1"/>
-    <row r="34" ht="8" customHeight="1">
-      <c r="A34" s="7" t="inlineStr"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="10" customHeight="1"/>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>第2章　法定福利厚生</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>（社会保険）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>第3条　会社は、健康保険、厚生年金保険、雇用保険及び労災保険の適用事業所として、法令に基づき従業員を加入させ、会社負担分の保険料を負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="8" customHeight="1">
-      <c r="A40" s="7" t="inlineStr"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-    </row>
-    <row r="41" ht="10" customHeight="1"/>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>第3章　通勤手当</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>（支給対象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>第4条　会社は、従業員の通勤に要する費用について、次の範囲内で通勤手当を支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>1　公共交通機関を利用する場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>2　片道2km以上の自動車・バイクによる通勤</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>3　自転車による通勤</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>4　その他事前申請の上会社が認めた通勤方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="8" customHeight="1"/>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>（支給基準および額）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>第5条　通勤手当の支給額は次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>1　公共交通機関の場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>（1）定期券を購入している場合はその額</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>（2）定期券を購入していない場合は、実費または1か月分の定期代相当額</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>ただし、いずれの場合も上限は月額50,000円とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="8" customHeight="1"/>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>2　自動車・バイクによる場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>（1）往復距離 × 出勤日数 × 20円</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>（2）月額の上限は次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>片道距離</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>上限（月額）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>2km以上10km未満</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>4,200円</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>10km以上15km未満</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>7,100円</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>15km以上25km未満</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>12,900円</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>25km以上35km未満</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>18,700円</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>35km以上45km未満</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>24,400円</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>45km以上55km未満</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>28,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>55km以上</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>31,600円</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="8" customHeight="1"/>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>3　自転車による場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>（1）1日あたり100円 × 出勤日数</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>（2）月額上限は2,500円とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="8" customHeight="1"/>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>4　その他事前申請の上会社が認めた通勤方法の場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>会社が合理的と認める方法により算出する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="8" customHeight="1"/>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>（申請・承認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>第6条　通勤手当の支給を受けるには、従業員が所定の様式により通勤方法、経路、実費額を申請し、会社の承認を得なければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>2　通勤経路が複数ある場合、会社は合理的かつ経済的と認められる経路を通勤経路として指定できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="8" customHeight="1"/>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>（例外支給）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>第7条　会社が必要と判断した場合には、前条の基準を超えて通勤手当を支給することがある。その場合、当該支給額は課税対象となる可能性があることを従業員は承知するものとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="8" customHeight="1"/>
-    <row r="83" ht="8" customHeight="1">
-      <c r="A83" s="7" t="inlineStr"/>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="10" customHeight="1"/>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>第4章　特別通勤手当</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>（支給対象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>第8条　会社は、従業員が通勤のために負担した駐輪場利用料等について、次のとおり特別通勤手当を支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>1　駐輪場の月極契約金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>2　一時利用料 × 出勤日数</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>3　その他事前申請の上会社が合理的と認めるもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="8" customHeight="1"/>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>（支給限度額）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>第9条　特別通勤手当の上限は月額10,000円とする。超過分は従業員負担とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="8" customHeight="1"/>
-    <row r="95" ht="8" customHeight="1">
-      <c r="A95" s="7" t="inlineStr"/>
-      <c r="B95" s="8" t="n"/>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="8" t="n"/>
-    </row>
-    <row r="96" ht="10" customHeight="1"/>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>第5章　住宅手当</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>（定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>第10条　本手当に関する用語の定義は、次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>1　「社員」とは、会社に雇用される全ての正社員をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>2　「賃料」とは、賃貸借契約書に記載された月額家賃をいい、共益費・管理費・水道光熱費等の付帯費用は含まないものとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>3　「対象住宅」とは、社員が自己名義または同居配偶者名義の賃貸住宅に居住するものをいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="8" customHeight="1"/>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>（支給対象）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>第11条　本手当の支給対象者は、第10条に定義する対象住宅に居住し、本規程に定める申請手続きを完了した社員とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>2　配偶者等が他の会社から住宅手当を受給している場合、当該社員は本手当の支給対象外とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="8" customHeight="1"/>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>（支給要件・申請手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>第12条　住宅手当を受給しようとする社員は、次の書類をマネジメント本部長宛てに提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>1　住宅手当申請書兼誓約書（賃料、配偶者等が他社から住宅手当を受給していないことの念書を含む）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>2　賃貸借契約書の写し（賃料確認用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>3　同居家族構成届（氏名、続柄、生年月日、同居・別居区分を明記）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>4　世帯主証明書（住民票の写し等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>2　同月中に申請がない場合は当該月分の支給を受けられない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>3　賃料が減少した場合は、遅滞なくマネジメント本部へ変更届を提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="8" customHeight="1"/>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>（支給額）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>第13条　住宅手当額は、賃料（月額）×30％の金額を算出し、100円未満を切り上げた額とする。ただし、支給額が30,000円を超える場合は30,000円を上限とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>（変更届出義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>第14条　住宅手当に関わる以下の事項に変更が生じた場合、社員は速やかにマネジメント本部へ届出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>1　賃料額の増減</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>2　住居の転居または同居家族構成の変更</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="8" customHeight="1"/>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>（不正受給時の措置）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="32" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>第15条　虚偽の申請または書類偽造等により住宅手当を受給した場合、会社は既に支給した住宅手当の全額返還を命じるとともに、懲戒規程に基づき処分を行う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="8" customHeight="1"/>
-    <row r="128" ht="8" customHeight="1">
-      <c r="A128" s="7" t="inlineStr"/>
-      <c r="B128" s="8" t="n"/>
-      <c r="C128" s="8" t="n"/>
-      <c r="D128" s="8" t="n"/>
-      <c r="E128" s="8" t="n"/>
-    </row>
-    <row r="129" ht="10" customHeight="1"/>
-    <row r="130" ht="30" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>第6章　生活支援・慶弔関係</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>（食事補助手当）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>第16条　会社は、従業員に対し、月額10,000円の食事補助手当を支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="32" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>2　パートタイマー等の所定労働日数が少ない従業員については、出勤日数に応じて按分して支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="8" customHeight="1"/>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>（制服・作業着）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="32" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>第17条　従業員は、業務に従事するにあたり会社が指定する制服または作業着を着用しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>2　制服または作業着は、原則として従業員が自ら準備するものとする。ただし、会社が特に必要と認めた場合は、会社が貸与または支給することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="8" customHeight="1"/>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>（慶弔給付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>第18条　会社は、休暇規程に定める慶弔休暇に関連して、次の給付を行う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>1　結婚祝い金：30,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>2　出産祝い金：30,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>3　弔事：本人または家族の希望に応じ、生花を手配する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>4　災害見舞金：取締役会の判断により、最大100,000円を限度として支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="8" customHeight="1"/>
-    <row r="146" ht="8" customHeight="1">
-      <c r="A146" s="7" t="inlineStr"/>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
-    </row>
-    <row r="147" ht="10" customHeight="1"/>
-    <row r="148" ht="30" customHeight="1">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>第7章　健康・医療支援</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>（健康診断）</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="32" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>第19条　会社は、労働安全衛生法に基づき、従業員に対し年1回の健康診断を実施し、費用を会社が負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>2　夜勤に従事する従業員については、年2回実施し、費用は会社が負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="8" customHeight="1"/>
-    <row r="153" ht="8" customHeight="1">
-      <c r="A153" s="7" t="inlineStr"/>
-      <c r="B153" s="8" t="n"/>
-      <c r="C153" s="8" t="n"/>
-      <c r="D153" s="8" t="n"/>
-      <c r="E153" s="8" t="n"/>
-    </row>
-    <row r="154" ht="10" customHeight="1"/>
-    <row r="155" ht="30" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>第8章　教育研修</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>（外部研修）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>第20条　会社は、業務に資すると判断される外部研修について、参加費用を全額負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="8" customHeight="1"/>
-    <row r="159" ht="8" customHeight="1">
-      <c r="A159" s="7" t="inlineStr"/>
-      <c r="B159" s="8" t="n"/>
-      <c r="C159" s="8" t="n"/>
-      <c r="D159" s="8" t="n"/>
-      <c r="E159" s="8" t="n"/>
-    </row>
-    <row r="160" ht="10" customHeight="1"/>
-    <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>第9章　特別休暇に関連する給付</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>（誕生日休暇・手当）</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>第21条　会社は、休暇規程に基づき誕生日休暇を付与するとともに、当該休暇を取得した従業員に対して誕生日手当として10,000円を支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="8" customHeight="1"/>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>（特別休暇に伴う給付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="32" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>第22条　会社は、休暇規程に基づき付与される特別休暇について、必要に応じて記念品、金銭その他の給付を行うことができる。内容は取締役会の決議により定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="8" customHeight="1"/>
-    <row r="168" ht="8" customHeight="1">
-      <c r="A168" s="7" t="inlineStr"/>
-      <c r="B168" s="8" t="n"/>
-      <c r="C168" s="8" t="n"/>
-      <c r="D168" s="8" t="n"/>
-      <c r="E168" s="8" t="n"/>
-    </row>
-    <row r="169" ht="10" customHeight="1"/>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>第10章　運用</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>（支給方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="32" customHeight="1">
-      <c r="A172" s="6" t="inlineStr">
-        <is>
-          <t>第23条　通勤手当、特別通勤手当及び各種手当は、毎月1日から末日までの1か月分を集計し、当月の給与と併せて支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="8" customHeight="1"/>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>（中途入社・退職時の取扱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>第24条　月中に入社または退職した者についても、出勤日数に応じて日割り計算で支給する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="8" customHeight="1"/>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>（休職・休暇・在宅勤務時の取扱い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="32" customHeight="1">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>第25条　休職中・休暇中・休業中または在宅勤務の場合、通勤手当及び特別通勤手当は支給しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="8" customHeight="1"/>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>（虚偽申請の禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>第26条　通勤手当、特別通勤手当、住宅手当その他各種手当の申請に虚偽が発覚した場合、会社は入社時に遡って再計算を行い、超過支給分を返還請求できるものとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="8" customHeight="1"/>
-    <row r="183" ht="8" customHeight="1">
-      <c r="A183" s="7" t="inlineStr"/>
-      <c r="B183" s="8" t="n"/>
-      <c r="C183" s="8" t="n"/>
-      <c r="D183" s="8" t="n"/>
-      <c r="E183" s="8" t="n"/>
-    </row>
-    <row r="184" ht="10" customHeight="1"/>
-    <row r="185" ht="30" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>第11章　雑則</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>（周知）</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="32" customHeight="1">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>第27条　会社は、本規程の内容を従業員に周知し、常時確認できるよう掲示またはイントラネット等で公開する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="8" customHeight="1"/>
-    <row r="189" ht="8" customHeight="1">
-      <c r="A189" s="7" t="inlineStr"/>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="8" t="n"/>
-      <c r="D189" s="8" t="n"/>
-      <c r="E189" s="8" t="n"/>
-    </row>
-    <row r="190" ht="10" customHeight="1"/>
-    <row r="191" ht="30" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="20" customHeight="1">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="20" customHeight="1">
-      <c r="A193" s="6" t="inlineStr">
-        <is>
-          <t>2　本規程は、令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="A166:E166"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A142:E142"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A168:E168"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A193:E193"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A136:E136"/>
-    <mergeCell ref="A192:E192"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A181:E181"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A156:E156"/>
-    <mergeCell ref="A171:E171"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A165:E165"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A155:E155"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A148:E148"/>
-    <mergeCell ref="A157:E157"/>
-    <mergeCell ref="A132:E132"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A183:E183"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A175:E175"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A159:E159"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A161:E161"/>
-    <mergeCell ref="A170:E170"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A186:E186"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A146:E146"/>
-    <mergeCell ref="A172:E172"/>
-    <mergeCell ref="A187:E187"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A174:E174"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A149:E149"/>
-    <mergeCell ref="A189:E189"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A86:E86"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A151:E151"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A141:E141"/>
-    <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A150:E150"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A191:E191"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A178:E178"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A153:E153"/>
-    <mergeCell ref="A162:E162"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A177:E177"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A163:E163"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A180:E180"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A143:E143"/>
-    <mergeCell ref="A92:E92"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　福利厚生規程</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
 </file>
--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -9,18 +9,19 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="就業規則" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="賃金規程" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人事管理規程" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情報管理規程" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出張旅費規程" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="安全衛生規程（運営）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="懲戒規程" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表彰規程" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="休暇規程" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福利厚生規程" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="競業避止規程" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1222,6 +1223,846 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>休暇規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>第2章　年次有給休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>（付与要件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>（取得方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>（時季変更権）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>（時間単位年休）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>（計画的付与）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>（年5日の取得義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>（有効期限）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="7" t="inlineStr"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>第3章　特別休暇</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>（慶弔休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>1　本人の結婚：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2　子女の結婚：2日</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>3　配偶者の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>4　父母・子の死亡：5日</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>6　その他会社が必要と認めた場合：別途定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>（産前産後休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>（育児休業・介護休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>（子の看護等休暇・介護休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>（病気休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>（公務・公用休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>（感染症予防に伴う休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>（生理休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>（育児時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>（母性健康管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>（誕生日休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="8" customHeight="1"/>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>（その他の特別休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="8" customHeight="1"/>
+    <row r="114" ht="8" customHeight="1">
+      <c r="A114" s="7" t="inlineStr"/>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="8" t="n"/>
+    </row>
+    <row r="115" ht="10" customHeight="1"/>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>第4章　手続</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>（申請手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>（診断書等の提出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>1　私傷病により連続して3日以上欠勤するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>2　休職を申請するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>5　会社が安全衛生管理上必要と認めたとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="8" customHeight="1">
+      <c r="A133" s="7" t="inlineStr"/>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="10" customHeight="1"/>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>第5章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>（休暇中の待遇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="8" customHeight="1">
+      <c r="A142" s="7" t="inlineStr"/>
+      <c r="B142" s="8" t="n"/>
+      <c r="C142" s="8" t="n"/>
+      <c r="D142" s="8" t="n"/>
+      <c r="E142" s="8" t="n"/>
+    </row>
+    <row r="143" ht="10" customHeight="1"/>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="94">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2387,7 +3228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2798,7 +3639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3559,7 +4400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4269,7 +5110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6405,6 +7246,524 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>人事管理規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）に勤務する従業員に関する人事管理の基本事項を定め、適正かつ公正な人事運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、管理監督者その他特別の取り扱いを要する者については、法令に従い一部適用除外とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>第2章　採用・試用</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>（採用手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>第3条　採用は、公平かつ公正な基準により行い、採用にあたっては会社所定の書類を提出しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>（採用内定の取消・解雇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>第4条　採用内定者が経歴等について重大な虚偽申告を行っていたことが判明した場合、または重大な不正行為が判明した場合には、会社は採用内定を取り消すことがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2　入社後に前項の事実が判明した場合、または勤務に著しく不適格と認められる場合には、「退職規程」に定める手続（解雇予告等）に従い、解雇することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>（試用期間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>第5条　新たに採用された従業員には、原則として3か月以内の試用期間を設ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、試用期間満了時に従業員として不適格と判断した場合、または必要と認める場合には、本人に理由を説明した上で、試用期間を延長することができる。ただし、延長は通算6か月を限度とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>3　試用期間中の処遇その他の条件は就業規則および「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>4　試用期間は勤続年数に通算する。試用開始から14日を超えた者を解雇する場合は、「退職規程」の解雇予告の定めによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="8" customHeight="1">
+      <c r="A49" s="7" t="inlineStr"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="10" customHeight="1"/>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>第3章　異動・出向・転籍</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>（配置転換・異動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>第6条　会社は、業務上の必要に応じ、従業員に対して配置転換、職種変更、出向、転勤等を命ずることができる。ただし、労働契約で職種または勤務地を限定している場合は、本人の同意を得るものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>（転勤配慮）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>第7条　会社は転勤を命ずるにあたり、従業員の健康、家庭状況（育児・介護の状況を含む）その他の事情を考慮するよう努める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>（出向・転籍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>第8条　出向または転籍の取扱いについては、労働契約の変更手続を経て「勤務管理規程」および「退職規程」に従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2　転籍は、従業員本人の個別の同意を得た場合に限り行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="8" customHeight="1">
+      <c r="A62" s="7" t="inlineStr"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="10" customHeight="1"/>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>第4章　身分・届出</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>（身分証明書）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>第9条　会社は必要に応じ、従業員に社員証その他の身分証明書を交付する。従業員はこれを常時携帯し、第三者に貸与または譲渡してはならない。退職または会社が指示した場合は速やかに返還しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>（届出義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>第10条　従業員は、住所、氏名、家族構成、緊急連絡先その他会社の人事管理に必要な事項に変更があった場合は、速やかに会社に届け出なければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="8" customHeight="1">
+      <c r="A71" s="7" t="inlineStr"/>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+    </row>
+    <row r="72" ht="10" customHeight="1"/>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>第5章　兼業・副業</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>（兼業・副業の許可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>第11条　従業員は、会社の業務に支障を及ぼさない範囲で兼業・副業を行うことができる。ただし、会社が競業避止義務や利益相反に該当すると判断した場合は、これを禁止することがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2　従業員が兼業・副業を希望する場合は、事前に会社に申請し、許可を得なければならない。手続、判断基準その他詳細は「競業避止規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>3　会社は、兼業・副業先を含めた労働時間を把握し、長時間労働とならないよう配慮する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="8" customHeight="1">
+      <c r="A79" s="7" t="inlineStr"/>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="8" t="n"/>
+    </row>
+    <row r="80" ht="10" customHeight="1"/>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>第6章　表彰・服務事故</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>（表彰）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>第12条　会社は、勤務成績優秀、功労顕著または模範的行為のあった従業員を表彰することができる。表彰の種類、内容は「表彰規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>（身元保証）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>第13条　会社は必要に応じ、従業員の採用に際して身元保証人の提出を求めることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2　身元保証契約の期間は5年以内とし、保証人が負担する上限額（極度額）を書面で定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="8" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>（事故・災害の届出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>第14条　従業員が事故、災害、犯罪関与、重大な交通違反その他会社に影響を及ぼす事案に関与した場合は、速やかに会社に報告しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2　前項の事案が服務規律違反に該当する場合は「懲戒規程」に基づき処分を行うことがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="8" customHeight="1">
+      <c r="A93" s="7" t="inlineStr"/>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+    </row>
+    <row r="94" ht="10" customHeight="1"/>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　人事管理規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6921,7 +8280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7687,7 +9046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8306,7 +9665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8993,7 +10352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9656,7 +11015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10118,844 +11477,4 @@
     <brk id="25" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E146"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>休暇規程</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）の従業員に付与される休暇に関する事項を定め、労働基準法その他関係法令を遵守しつつ、従業員の心身の健康保持と円滑な業務運営を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。ただし、嘱託社員、短時間勤務者、アルバイト等については、就業形態に応じて別途定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1">
-      <c r="A33" s="7" t="inlineStr"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="10" customHeight="1"/>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>第2章　年次有給休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>（付与要件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>第3条　会社は、継続勤務6か月を経過し、その期間の全労働日の8割以上出勤した従業員に対し、10日の年次有給休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>2　その後は、継続勤務年数に応じ、1年ごとに次の日数を付与する。ただし、直前の1年間の全労働日の8割以上出勤した者に限る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　継続勤務1年6か月：11日　2年6か月：12日　3年6か月：14日　4年6か月：16日　5年6か月：18日　6年6か月以上：20日</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>3　週所定労働日数が4日以下かつ週所定労働時間が30時間未満の従業員には、労働基準法第39条第3項に定める日数を比例付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>（取得方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>第4条　年次有給休暇の取得は、従業員の請求による。会社は業務の正常な運営を妨げる場合を除き、これを認めなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>（時季変更権）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>第5条　会社は、業務の正常な運営を妨げる場合、休暇の取得時季を変更することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>（時間単位年休）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>第6条　会社は、労使協定を締結した場合に限り、年次有給休暇のうち年5日の範囲内で、時間単位で取得させることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>（計画的付与）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>第7条　会社は、労使協定に基づき、年次有給休暇の一部を計画的に付与することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>（年5日の取得義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>第8条　会社は、年次有給休暇のうち年間5日については、従業員が必ず取得するよう管理しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>2　従業員が自ら請求しない場合、会社は取得時季を指定して取得させる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>（有効期限）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>第9条　年次有給休暇の有効期限は、付与日から2年間とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>2　繰越は1年間に限り認められるが、2年を経過した分については消滅する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>3　消滅した年次有給休暇については、会社は金銭その他の補償を行わない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="8" customHeight="1">
-      <c r="A63" s="7" t="inlineStr"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-    </row>
-    <row r="64" ht="10" customHeight="1"/>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>第3章　特別休暇</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>（慶弔休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>第10条　従業員に対し、次の慶弔休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>1　本人の結婚：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>2　子女の結婚：2日</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>3　配偶者の死亡：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>4　父母・子の死亡：5日</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>5　祖父母・兄弟姉妹の死亡：3日</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>6　その他会社が必要と認めた場合：別途定める</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>2　慶弔休暇に伴う見舞金・祝い金等は「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="8" customHeight="1"/>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>（産前産後休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>第11条　従業員が出産する場合は、労働基準法に基づき産前6週間（多胎妊娠の場合は14週間）、産後8週間を休業とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="8" customHeight="1"/>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>（育児休業・介護休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、育児・介護休業法に基づき、育児休業及び介護休業を取得することができる。期間・条件等は同法および「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="8" customHeight="1"/>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>（子の看護等休暇・介護休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、小学校第3学年修了までの子を養育する場合、子1人につき年間5日（2人以上は10日）の子の看護等休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>2　要介護状態にある家族を介護する従業員は、対象家族1人につき年間5日（2人以上は10日）の介護休暇を取得できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>3　子の看護等休暇及び介護休暇は、1日または時間単位で取得できる。詳細は「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>（病気休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>第14条　従業員が私傷病により就業できない場合は、会社の承認を得て病気休暇を与えることがある。日数や給与の取扱いは「休職規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="8" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>（公務・公用休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>第15条　従業員が裁判員、証人、選挙、官公庁の要請による職務に従事する場合は、その期間を休暇とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>（感染症予防に伴う休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>第16条　従業員が感染症に罹患し、医師の診断や法令に基づき出勤停止とされた場合は、その期間を休暇とする。賃金その他の取扱いは就業規則および賃金規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>2　法令に基づかず、会社の判断により出勤を停止させた場合は、労働基準法第26条に基づき休業手当（平均賃金の100分の60以上）を支払う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>（生理休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>第16条の2　生理日の就業が著しく困難な女性従業員が請求したときは、必要な期間の休暇を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="8" customHeight="1"/>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>（育児時間）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="32" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>第16条の3　生後1年に達しない子を育てる女性従業員が請求したときは、休憩時間のほか1日2回、各30分の育児時間を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="8" customHeight="1"/>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>（母性健康管理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>第16条の4　妊娠中及び出産後1年以内の女性従業員が請求したときは、男女雇用機会均等法に基づき、保健指導または健康診査を受けるための時間を与える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="8" customHeight="1"/>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>（誕生日休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>第17条　会社は、従業員に対し、誕生日月に1日の誕生日休暇を付与する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>2　シフト勤務等の都合により、従業員の希望がある場合は、誕生日に代えて前後の勤務日に振り替えることができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>3　誕生日休暇に伴う手当については「福利厚生規程」に定める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="8" customHeight="1"/>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>（その他の特別休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>第18条　会社は、災害その他社会的要請や会社が必要と認める場合に、特別休暇を付与することがある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="8" customHeight="1">
-      <c r="A114" s="7" t="inlineStr"/>
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="8" t="n"/>
-      <c r="D114" s="8" t="n"/>
-      <c r="E114" s="8" t="n"/>
-    </row>
-    <row r="115" ht="10" customHeight="1"/>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>第4章　手続</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>（申請手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>第19条　従業員は、休暇を取得しようとするときは、所定の様式により事前に申請し、上長の承認を得なければならない。ただし、やむを得ない場合は事後速やかに届け出る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>（診断書等の提出）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>第20条　従業員は、次の場合に医師の診断書その他会社が認める証明書を提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>1　私傷病により連続して3日以上欠勤するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>2　休職を申請するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>3　復職を希望するとき（精神疾患・適応障害・うつ病等を含む）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>4　産前産後休業、育児休業、介護休業、感染症罹患など、法令に基づく休暇を取得するとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>5　会社が安全衛生管理上必要と認めたとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>2　診断書等の作成費用は、原則として従業員の負担とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>3　ただし、次の各号に該当する場合は会社が費用を負担する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1　会社が独自に必要と判断し、従業員の申請とは別に診断書その他の証明書を求めた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2　労働安全衛生法に基づく健康診断や再検査、特殊健康診断に関する場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　3　労災（業務災害・通勤災害）に関する診断書の場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="8" customHeight="1">
-      <c r="A133" s="7" t="inlineStr"/>
-      <c r="B133" s="8" t="n"/>
-      <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
-      <c r="E133" s="8" t="n"/>
-    </row>
-    <row r="134" ht="10" customHeight="1"/>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>第5章　その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>（不利益取扱い禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>第21条　会社は、従業員が法令に基づく休暇または本規程による休暇を取得したことを理由として、不利益取扱いをしてはならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="8" customHeight="1"/>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>（休暇中の待遇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="32" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>第22条　休暇中の賃金、社会保険その他の待遇については、就業規則、賃金規程及び関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="8" customHeight="1"/>
-    <row r="142" ht="8" customHeight="1">
-      <c r="A142" s="7" t="inlineStr"/>
-      <c r="B142" s="8" t="n"/>
-      <c r="C142" s="8" t="n"/>
-      <c r="D142" s="8" t="n"/>
-      <c r="E142" s="8" t="n"/>
-    </row>
-    <row r="143" ht="10" customHeight="1"/>
-    <row r="144" ht="30" customHeight="1">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>2　本規程は令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A142:E142"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A136:E136"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="A131:E131"/>
-    <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A120:E120"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A146:E146"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A127:E127"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A145:E145"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A111:E111"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　休暇規程</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
 </file>
--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -22,6 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +77,11 @@
       <name val="Arial"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -111,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -175,6 +181,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6598,6 +6607,562 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>身体拘束排除マニュアル</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>来歴管理表</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>版数・日付</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>来歴</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>審議</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>立案</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>0　2026.2.1</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>新規制定（訪問介護事業所用）</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr"/>
+      <c r="D28" s="21" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="21" t="inlineStr"/>
+      <c r="B29" s="21" t="inlineStr"/>
+      <c r="C29" s="21" t="inlineStr"/>
+      <c r="D29" s="21" t="inlineStr"/>
+      <c r="E29" s="21" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="21" t="inlineStr"/>
+      <c r="B30" s="21" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr"/>
+      <c r="D30" s="21" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="21" t="inlineStr"/>
+      <c r="B31" s="21" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr"/>
+      <c r="D31" s="21" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="21" t="inlineStr"/>
+      <c r="B32" s="21" t="inlineStr"/>
+      <c r="C32" s="21" t="inlineStr"/>
+      <c r="D32" s="21" t="inlineStr"/>
+      <c r="E32" s="21" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="21" t="inlineStr"/>
+      <c r="B33" s="21" t="inlineStr"/>
+      <c r="C33" s="21" t="inlineStr"/>
+      <c r="D33" s="21" t="inlineStr"/>
+      <c r="E33" s="21" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="21" t="inlineStr"/>
+      <c r="B34" s="21" t="inlineStr"/>
+      <c r="C34" s="21" t="inlineStr"/>
+      <c r="D34" s="21" t="inlineStr"/>
+      <c r="E34" s="21" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="21" t="inlineStr"/>
+      <c r="B35" s="21" t="inlineStr"/>
+      <c r="C35" s="21" t="inlineStr"/>
+      <c r="D35" s="21" t="inlineStr"/>
+      <c r="E35" s="21" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="21" t="inlineStr"/>
+      <c r="B36" s="21" t="inlineStr"/>
+      <c r="C36" s="21" t="inlineStr"/>
+      <c r="D36" s="21" t="inlineStr"/>
+      <c r="E36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="21" t="inlineStr"/>
+      <c r="B37" s="21" t="inlineStr"/>
+      <c r="C37" s="21" t="inlineStr"/>
+      <c r="D37" s="21" t="inlineStr"/>
+      <c r="E37" s="21" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="21" t="inlineStr"/>
+      <c r="B38" s="21" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr"/>
+      <c r="D38" s="21" t="inlineStr"/>
+      <c r="E38" s="21" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="21" t="inlineStr"/>
+      <c r="B39" s="21" t="inlineStr"/>
+      <c r="C39" s="21" t="inlineStr"/>
+      <c r="D39" s="21" t="inlineStr"/>
+      <c r="E39" s="21" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="21" t="inlineStr"/>
+      <c r="B40" s="21" t="inlineStr"/>
+      <c r="C40" s="21" t="inlineStr"/>
+      <c r="D40" s="21" t="inlineStr"/>
+      <c r="E40" s="21" t="inlineStr"/>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>身体拘束をせずに行うケア</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>1　身体拘束を誘発する原因を探り、除去する</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>身体拘束をやむを得ず行う理由として、次のような状況を防止するために「必要」だといわれることがある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・徘徊や興奮状態での周囲への迷惑行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・転倒のおそれのある不安定な歩行や、点滴の抜去などの危険な行動</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・かきむしりや体をたたき続けるなどの自傷行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・姿勢が崩れ、体位保持が困難であること</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>しかし、それらの状況には必ずその人なりの理由や原因があり、ケアする側の関わり方や環境に問題があることも少なくない。従って、その人なりの理由や原因を徹底的に探り除去するケアが必要である。在宅においては、住環境や家族の介護状況も原因となりうるため、居宅介護支援事業所（ケアマネジャー）や家族と協力して原因を探る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="10" customHeight="1"/>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>2　五つの基本的ケアを徹底する</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>1　起きる</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　人間は座っているとき、重力が上からかかることにより覚醒する。目が開き、耳が聞こえ、自分の周囲で起こっていることがわかるようになる。これは仰臥して天井を見ていたのではわからない。起きるのを助けることは人間らしさを追求する第一歩である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2　食べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　人にとって食べることは楽しみや生きがいであり、脱水予防、感染予防にもなり、点滴や経管栄養が不要になる。食べることはケアの基本である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>3　排泄する</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　なるべくトイレで排せつしてもらうことを基本に考える。おむつを使用している人については、随時交換が重要である。おむつに排せつ物が付いたままになっていると気持ち悪く、「おむついじり」などの行為につながることになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>4　清潔にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　きちんと入浴することが基本である。皮膚が不潔なことがかゆみの原因になり、そのために大声を出したり、夜眠れずに不穏になったりすることになる。皮膚をきれいにしておけば、本人も快適になり、また、周囲も世話をしやすくなり、人間関係も良好になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>5　活動する</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　その人の状態や生活歴に合ったよい刺激を提供することが重要である。具体的には、音楽、工芸、園芸、ゲーム、体操、家事、ペット、テレビなどが考えられる。言葉によるよい刺激もあれば、言葉以外の刺激もあるが、いずれにせよ、その人らしさを追求するうえで、心地よい刺激が必要である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>という五つの基本的事項について、その人に合った十分なケアを徹底することである。訪問介護においては、訪問介護計画に基づき、限られた訪問時間の中でもこれらのケアを意識して支援を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>3　身体拘束廃止をきっかけに「よりよいケア」の実現を</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>このように身体拘束の廃止を実現していく取り組みは、在宅介護におけるケア全体の向上や生活環境の改善のきっかけとなりうる。「身体拘束廃止」を最終ゴールとせず、身体拘束を廃止していく過程で提起された様々な課題を真摯に受け止め、よりよいケアの実現に取り組んでいくことが期待される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="10" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>4　三つの要件をすべて満たすことが必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>以下の三つの要件をすべて満たす状態であることを「身体拘束適正化委員会」等のチームで検討、確認し記録しておく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　切迫性：利用者本人又は他の利用者等の生命又は身体が危険にさらされる可能性が著しく高いこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　非代替性：身体拘束その他の行動制限を行う以外に代替する介護方法がないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　一時性：身体拘束その他の行動制限が一時的なものであること</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>5　手続きの面でも慎重な取り扱いが求められる</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>仮に三つの要件を満たす場合にも、以下の点に留意すべきである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="6" customHeight="1"/>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>①「緊急やむを得ない場合」に該当するかどうかの判断は、担当の訪問介護員個人では行わず、事業所全体としての判断が行われるように、あらかじめルールや手続きを定めておく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="48" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>②利用者本人や家族に対して、身体拘束の内容、目的、理由、拘束の時間、時間帯、期間等をできる限り詳細に説明し、十分な理解を得るよう努める。その際には、管理者やサービス提供責任者から説明を行うなど、説明手続きや説明者について事前に明文化しておく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>仮に、事前に身体拘束について事業所としての考え方を利用者や家族に説明し、理解を得ている場合であっても、実際に身体拘束を行う時点で、必ず個別に説明を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>③緊急やむを得ず身体拘束を行う場合についても、「緊急やむを得ない場合」に該当するかどうかを常に観察、再検討し、要件に該当しなくなった場合には直ちに解除すること。この場合には、実際に身体拘束を一時的に解除して状態を観察するなどの対応をとることが重要である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>④身体拘束を行う場合は、居宅介護支援事業所（ケアマネジャー）に報告し、ケアプランに位置づけて関係者間で情報を共有する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="10" customHeight="1"/>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>6　身体拘束に関する記録が義務づけられている</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>緊急やむを得ず身体拘束等を行う場合には、その態様及び時間、その際の利用者の心身の状況、緊急やむを得なかった理由を記録しなければならない。記録は5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="10" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>7　家族による身体拘束への対応（訪問介護事業所として）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>訪問時に、家族等による身体拘束（ベッド柵で囲む、ひもで縛る、部屋に鍵をかける等）を発見した場合は、訪問介護員は速やかに管理者に報告する。事業所は、居宅介護支援事業所と連携して家族の介護負担や原因を確認し、代替となるケアを提案する。高齢者虐待のおそれがある場合は、高齢者虐待防止法に基づき、大阪市（区保健福祉センター）又は地域包括支援センターに通報する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="10" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="23" t="inlineStr">
+        <is>
+          <t>以上</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　身体拘束排除マニュアル</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="41" min="0" max="16383" man="1"/>
+    <brk id="67" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -23,6 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +83,11 @@
       <b val="1"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="22"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -183,6 +189,13 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7163,6 +7176,1114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E174"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>事故発生時・緊急時対応マニュアル
+（訪問介護事業所用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>1．目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、訪問介護サービス提供中または利用者宅において事故・緊急事態が発生した際に、迅速かつ適切な対応を行い、利用者の安全確保と被害拡大防止、関係機関との連携強化を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="10" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2．適用範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、訪問介護に従事する全職員（登録ヘルパーを含む）に適用し、利用者宅・移動中・事業所内で発生した事故・緊急事態すべてを対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>3．定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>【事故】転倒・転落・誤嚥・誤薬・火災・物損等、利用者の身体・生活に影響を及ぼす事象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>【緊急事態】生命に危険が及ぶ可能性のある急変（意識障害・呼吸困難・心肺停止等）、暴力行為、行方不明など。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="10" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>4．基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 利用者の生命・安全を最優先とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② その場で必要な応急処置・救急要請を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 管理者・関係機関へ迅速に報告する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 記録と事後検証を確実に実施し、再発防止を図る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>5．緊急時の初期対応フロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 状況確認（意識・呼吸・外傷・環境状況）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 応急処置（可能な範囲で）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 119番通報が必要か判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 家族・ケアマネへ連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 管理者へ即時報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑥ 訪問中の職員は利用者から離れず見守りを継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑦ 必要時、立会い・同行支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>6．事故種別ごとの対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>【転倒・転落】</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・意識・痛み・出血の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・無理に動かさない</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて救急要請</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>【誤薬】</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・薬剤名・量・時間を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・かかりつけ医・薬剤師に連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・症状出現時は119番</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>【誤嚥】</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・咳・呼吸状態を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・背部叩打法などの応急処置</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・呼吸困難時は直ちに救急通報</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>【急変（意識消失・発作等）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・刺激に反応するか確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・救急要請</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・安全な体勢に整える</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>【火災・ガス漏れ】</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者を安全な場所へ誘導</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・消防・管理会社へ連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>【暴力・虐待が疑われる場合】</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者の安全確保</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・管理者へ直ちに報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・虐待が疑われる場合は、高齢者虐待防止法に基づき、大阪市（区保健福祉センター）又は地域包括支援センターへ通報する</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>【行方不明】</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・最終確認時間・居場所・服装を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・家族・ケアマネへ連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて警察へ通報</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="8" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>7．119番通報時のポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・場所の住所</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者の状態（呼吸・意識・症状）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・既往歴・服薬情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・通報者の氏名・連絡先</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・救急隊の到着まで行った処置内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>8．家族・関係者への連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 家族へ状況報告、対応内容、今後の流れを説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② ケアマネジャーへ即時報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 必要時、主治医へ連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　※ 感情的状況では言葉を簡潔に、落ち着いた説明を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>9．管理者への報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>事故発生から速やかに以下を伝える：</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事故発生日時・場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・状況と職員の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者の状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・家族・関係機関への連絡状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・今後想定されるリスク</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="8" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="16" t="inlineStr">
+        <is>
+          <t>10．事故報告書の作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事実を時系列で記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・主観・推測は記載しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・関係者の証言を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・使用器具・環境の状況も明記</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・管理者の確認・押印を得る</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　※ 事故報告書は当日または翌営業日までに提出する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>11．事故後の再発防止策</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 職員間で事例共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② マニュアル・手順の修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 環境改善（段差・照明・物品配置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 職員研修（介助技術向上、リスク感知向上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ ケアプラン変更の検討（ケアマネと連携）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="8" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="16" t="inlineStr">
+        <is>
+          <t>12．行政・保険者への報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="48" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・死亡事故、医療機関での受診や入院を要した事故、誤薬、虐待の疑いなど、大阪市の事故報告の対象となる事故は、大阪市（保険者）へ報告する（第1報は事故発生後おおむね5日以内、最終報告は対応終了後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者の住所地が大阪市以外の場合は、その市町村の基準に従って報告する</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・保険者からの照会があれば迅速に回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問記録・事故記録・写真などを整理し保管</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・賠償すべき事故の場合は、損害賠償保険会社へ連絡し、速やかに賠償を行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="8" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>13．職員のメンタルケア</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事故対応後の職員のストレス確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて管理者面談</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・責任追及ではなく再発防止型の検証を徹底する</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="8" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>14．研修計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・年1回以上、事故対応訓練を実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・急変対応、誤嚥時対応、火災対応の実技を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事例検討会で事故防止の意識向上を図る</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="8" customHeight="1"/>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="16" t="inlineStr">
+        <is>
+          <t>15．記録と保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>事故報告書・関係記録は5年間保存し、必要時は監査・実地指導（運営指導）で提示する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="10" customHeight="1"/>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="10" customHeight="1"/>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>【最終確認】</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="26" t="inlineStr">
+        <is>
+          <t>管理者署名：</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+    </row>
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="26" t="inlineStr">
+        <is>
+          <t>確認日：</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n"/>
+      <c r="C147" s="8" t="n"/>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="27" t="inlineStr">
+        <is>
+          <t>事故対応フローチャート</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="23" t="inlineStr">
+        <is>
+          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="10" customHeight="1"/>
+    <row r="151" ht="30" customHeight="1">
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>【事故発生】</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>① 状況確認
+（意識・呼吸・出血・環境）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>② 応急処置
+（可能な範囲で安全確保）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>③ 緊急度判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="B159" s="17" t="inlineStr">
+        <is>
+          <t>【高】生命の危険あり</t>
+        </is>
+      </c>
+      <c r="D159" s="17" t="inlineStr">
+        <is>
+          <t>【低】生命の危険なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="B160" s="17" t="inlineStr">
+        <is>
+          <t>④ 119番通報</t>
+        </is>
+      </c>
+      <c r="D160" s="17" t="inlineStr">
+        <is>
+          <t>必要に応じ受診調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>⑤ 家族・ケアマネへ連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="C164" s="17" t="inlineStr">
+        <is>
+          <t>⑥ 管理者へ即時報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="C166" s="17" t="inlineStr">
+        <is>
+          <t>⑦ 救急隊到着まで
+見守り・対応継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>⑧ 事故報告書作成
+（当日～翌営業日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="C170" s="17" t="inlineStr">
+        <is>
+          <t>⑨ 大阪市へ報告
+（対象事故の場合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="16" customHeight="1">
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="C172" s="17" t="inlineStr">
+        <is>
+          <t>⑩ 再発防止策の検討・共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="16" customHeight="1">
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="C174" s="17" t="inlineStr">
+        <is>
+          <t>【完了】</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="103">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A149:E149"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　事故発生時・緊急時対応マニュアル</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="147" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束廃止に関する指針" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8284,6 +8285,904 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E148"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>身体拘束廃止に関する指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>1．身体拘束廃止に関する考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>身体拘束は人間の活動そのものを制限し、自由を抑制してしまいます。そして、何よりも拘束は、短期間でも大きな苦痛と著しい被害・ダメージをその方に与えてしまい、尊厳ある生活を阻むものです。当事業所では利用者の尊厳と主体性を尊重し、身体拘束廃止に向けた意識を持ち、身体拘束をしないケアの実施に努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>（1）介護保険指定基準の身体拘束禁止の規定</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>サービス提供にあたっては、当該利用者又は他の利用者等の生命又は身体を保護するため、緊急やむを得ない場合を除き、身体拘束その他利用者の行動を制限する行為（以下「身体拘束等」という。）を禁止しています（指定居宅サービス等の事業の人員、設備及び運営に関する基準及び大阪市条例）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>（2）緊急やむを得ない場合の例外三原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>利用者個々の心身の状況を勘案し、疾病・障害を理解した上で身体拘束を行わないケアの提供をすることが原則です。しかしながら、以下の3つの要件の全てを満たす状態にある場合は、必要最低限の身体拘束を行うことがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 切迫性：利用者本人又は他の利用者等の生命又は身体が危険にさらされる可能性が著しく高いこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 非代替性：身体拘束その他の行動制限を行う以外に代替する介護方法がないこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 一時性：身体拘束その他の行動制限が一時的なものであること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>上記3つの要件に照らし合わせながら最も良いケアの方法を常に検討していく姿勢を持ちます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="10" customHeight="1"/>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>2．身体拘束廃止に向けての基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>（1）身体拘束の原則禁止</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>当事業所においては、原則として身体拘束及びその他の行動制限を禁止します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>（2）やむを得ず身体拘束を行う場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="96" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>その方にとって何が良いか、拘束に代わる方法はないか、常に考え、相談し、色々な方法を検討していきます。本人や家族の思いを尊重しながら最も良い方法を模索していきますが、本人又は他の利用者等の生命又は身体を保護するための措置として緊急やむを得ず身体拘束を行う場合は、身体拘束適正化委員会を中心に充分検討を行い、身体拘束による心身の損害よりも、拘束をしないリスクの方が高い場合で、切迫性・非代替性・一時性の3要件の全てを満たした場合のみ、本人・家族への説明と同意を得て行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>また、身体拘束を行った場合は、その状況についての経過を記録し、出来るだけ早期に拘束を解除すべく努力します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>（3）日常ケアにおける留意事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>身体拘束を行う必要性を生じさせないために、日常的に以下のことに取り組みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 利用者主体の行動・尊厳ある生活に努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 言葉や応対等で、利用者の精神的な自由を妨げないよう努めます（「ちょっと待って」等の言葉による拘束（スピーチロック）を含む）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 利用者の思いを汲み取り、利用者の意向に添ったサービスを提供し、居宅介護支援事業所（ケアマネジャー）や他職種と協働で個々に応じた丁寧な対応をします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 利用者の安全を確保する観点から、利用者の自由（身体的・精神的）を安易に妨げるような行為は行いません。万が一やむを得ず安全確保を優先する場合は、身体拘束適正化委員会において検討します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 「やむを得ない」と拘束に順ずる行為を行っていないか、常に振り返りながら利用者に主体的な生活をしていただけるよう努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>3．身体拘束廃止に向けた体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>（1）身体拘束適正化委員会の設置</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>当事業所では、身体拘束廃止に向けて、身体拘束適正化委員会（以下「委員会」という。）を設置します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>① 設置目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ア）事業所内での身体拘束廃止に向けての現状把握及び改善についての検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　イ）身体拘束を実施せざるを得ない場合の検討及び手続き</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ウ）身体拘束を実施した場合の解除の検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　エ）身体拘束廃止に関する職員全体への指導</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>② 委員会の構成員</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・代表取締役（法人代表者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・管理者</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス提供責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>③ 委員会の開催</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>年1回以上定期的に開催するほか、必要時に随時開催します。開催はテレビ電話装置等を活用して行うことができ、虐待防止委員会等と一体的に開催することを妨げません。結果は記録し、全職員に周知します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="10" customHeight="1"/>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>4．やむを得ず身体拘束を行う場合の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>本人又は他の利用者等の生命又は身体を保護するための措置として、緊急やむを得ず身体拘束を行わなければならない場合は、以下の手順に従って実施します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="6" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>1）カンファレンスの実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="48" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>緊急やむを得ない状況になった場合、委員会の構成員が集まり、拘束による利用者の心身の損害や拘束をしない場合のリスクについて検討し、身体拘束を行う事を選択する前に①切迫性②非代替性③一時性の3要件全てを満たしているかどうかについて検討、確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="64" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>要件を検討・確認した上で、身体拘束を行うことを選択した場合は、拘束の方法、場所、時間帯、期間等について検討し、本人・家族に対する説明書を作成します。また、廃止に向けた取り組み改善の検討会を早急に行い実施に努めます。居宅介護支援事業所（ケアマネジャー）にも報告し、ケアプランへの位置づけについて協議します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="6" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2）利用者本人や家族に対しての説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>また、身体拘束の同意期限を越え、なお拘束を必要とする場合については、事前に契約者・家族等と行っている内容と方向性、利用者の状態などを確認説明し、同意を得たうえで実施します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="6" customHeight="1"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>3）記録と再検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="64" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>法律上、身体拘束に関する記録は義務付けられており、専用の様式を用いてその態様及び時間・その際の利用者の心身の状況・やむを得なかった理由などを記録します。身体拘束の早期解除に向けて、拘束の必要性や方法を逐次検討します。その記録は5年間保存し、行政担当部局の運営指導等が行われる際に提示できるようにします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="6" customHeight="1"/>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>4）拘束の解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>3）の記録と再検討の結果、身体拘束を継続する必要性がなくなった場合は、速やかに身体拘束を解除します。その場合には、契約者、家族、居宅介護支援事業所に報告します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="10" customHeight="1"/>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>5．身体的拘束等の報告方法等のための方策に関する基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1）身体的拘束等を行う場合には、4．の手続きに基づき利用者家族に速やかに説明し、報告を行うこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3）適切な手続きに依らない身体的拘束の事実が判明した場合は、利用者及び利用者家族への謝罪を行い、大阪市への報告を行うこと。高齢者虐待に該当するおそれがある場合は、高齢者虐待防止法に基づき通報すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4）訪問時に家族等による身体拘束を発見した場合は、管理者に報告し、居宅介護支援事業所と連携して対応すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="8" customHeight="1"/>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>介護保険指定基準において身体拘束禁止の対象となる具体的な行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（4）点滴・経管栄養等のチューブを抜かないように、四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="32" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（6）車椅子・椅子からずり落ちたり、立ち上がったりしないように、Y字型拘束帯や腰ベルト・車椅子テーブルをつける</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（11）自分の意思で開けることのできない居室等に隔離する</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="26" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>6．身体拘束廃止に向けた各職種の役割</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>身体拘束の廃止のために、各職種の専門性に基づくアプローチから、チームケアを行うことを基本とし、それぞれの果たすべき役割に責任をもって対応します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="6" customHeight="1"/>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>（代表取締役）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2）委員会総括責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3）家族、医療、行政機関、その他関係機関への対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="8" customHeight="1"/>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>（身体拘束適正化委員会）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5）身体拘束廃止に向けた職員教育</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="8" customHeight="1"/>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>（全従業者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　11）利用者宅の住環境（段差・家具配置等）や福祉用具の改善提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="8" customHeight="1"/>
+    <row r="138" ht="26" customHeight="1">
+      <c r="A138" s="15" t="inlineStr">
+        <is>
+          <t>7．身体拘束廃止・改善のための職員教育・研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="32" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>支援に携わる全ての職員（登録ヘルパーを含む）に対して、身体拘束廃止と人権を尊重したケアの励行を図り、事故防止と合わせてリスクマネジメントとしての職員教育を行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ その他必要な教育・研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="8" customHeight="1"/>
+    <row r="144" ht="26" customHeight="1">
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>8．身体拘束廃止に関する指針の閲覧について</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="32" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>この指針は、当事業所内に掲示するとともに、利用者・家族がいつでも自由に閲覧することができます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="10" customHeight="1"/>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>9．附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>この指針は令和8年2月1日より施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="102">
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　身体拘束廃止に関する指針</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束廃止に関する指針" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情対応マニュアル" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +90,10 @@
       <b val="1"/>
       <sz val="22"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -198,6 +203,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9183,6 +9191,1106 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E158"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>苦情対応マニュアル
+（訪問介護事業所用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>1．目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、利用者・家族等からの苦情や相談に対し、適切かつ迅速に対応し、サービス品質向上と信頼関係維持を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="10" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2．基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 苦情は事業改善の重要な情報源と捉える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 迅速・誠実・公平を徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 利用者の感情に寄り添い、尊厳を損なわない対応を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 対応内容は必ず記録し、再発防止策を組織的に検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 苦情を申し立てたことを理由に、利用者を不利益に取り扱わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3．苦情の分類</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス内容に関する苦情</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・職員の態度・言動に関する苦情</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・安全衛生・感染症対策に関する苦情</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事務手続・連絡体制に関する苦情</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・その他（家族間トラブルとの境界案件など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="8" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>4．苦情受付の流れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>【受付窓口】</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>窓口</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>連絡先・受付時間</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+    </row>
+    <row r="46" ht="48" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>事業所（いいかいご）
+担当：管理者　生田 友哉</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>TEL 06-4400-9333　FAX 06-4400-9332
+午前9時～午後6時（営業日）</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="48" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>大阪市福祉局高齢者施策部
+介護保険課（指定・指導グループ）</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>TEL 06-6241-6310　FAX 06-6241-6608
+9:00～17:30</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>大阪府国民健康保険団体連合会</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>TEL 06-6949-5309
+午前9時～午後5時</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>※利用者の住所地の区役所（保健福祉センター）でも受け付けている。重要事項説明書に記載し、利用者に説明する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="8" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>【受付方法】電話・対面・書面・代理を問わず受け付ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>【受付時の基本姿勢】</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・遮らず傾聴し、感情を受け止める</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・否定せず、事実確認は後で行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・謝罪すべき点は即時に簡潔に謝罪</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>【初期記録】</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・受付職員は必ず「苦情（相談）記録表」に記入する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・緊急度を必ず判断する（高・中・低）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>5．初期対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者の安全に直結する場合は直ちに管理者へ連絡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・担当職員の交代や訪問スケジュール調整が必要な場合は早急に実施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・状況によっては主治医またはケアマネジャーへ連絡し共同対応。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>6．事実確認の手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 関係職員への聞き取り（時系列整理、具体的行動の確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 他職員による第三者証言の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ ケア記録・訪問記録の照合</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 利用者宅での状況（環境要因）の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　※ 偏りのない調査を徹底。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>7．事業所としての判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・苦情の原因を分析（ヒューマンエラー、コミュニケーション不足、体制の問題など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・責任区分を明確化</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・改善策の方向性を管理者が決定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="8" customHeight="1"/>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>8．対応策の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問担当者の変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・介助方法の見直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・職員指導・再教育</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス内容変更の説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・緊急時には行政・医療機関との連携強化</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="8" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>9．利用者・家族への説明方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事実確認結果と改善策を丁寧に説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・時間を空けず迅速に連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・説明者は管理者またはサービス提供責任者が担当</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者の感情に配慮し、専門用語を避ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・理解状況および同意の有無を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>10．記録と保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・苦情（相談）記録表にすべての対応履歴を記入</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・改善内容・最終判断を管理者が記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・保存期間は5年間とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>11．再発防止策</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・業務フロー改善（引継ぎ強化、訪問時の声かけ方法など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・定期研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・管理者によるモニタリング訪問</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・同類事案がないか定期的にチェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>12．フォローアップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・改善後、利用者へ状況確認の連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・再度不満がないか確認し、記録に残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・苦情対応の完了日は必ず記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="8" customHeight="1"/>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>13．行政・国保連への対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・大阪市（保険者）が行う文書の提出・提示の求め、質問・照会、調査に協力し、指導・助言を受けた場合は必要な改善を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・大阪府国民健康保険団体連合会が行う調査に協力し、指導・助言を受けた場合は必要な改善を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・大阪市又は国保連から求めがあった場合は、改善の内容を報告する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・虐待や重大事故の可能性がある苦情は、虐待防止・事故対応の手順により大阪市へ報告・通報する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>14．管理者の責任</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・全体の指揮、判断、行政報告の要否判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・職員教育の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・個別面談による職員フォロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・苦情対応の組織的改善を推進</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>15．年間集計と分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・苦情の種類別・月別件数をExcelで管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・傾向分析（特定職員に偏りがないか等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・改善策の実施状況を年1回まとめ、全体会議で共有する</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="8" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="16" t="inlineStr">
+        <is>
+          <t>16．研修計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・新人研修に苦情対応を必ず含める</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・年1回以上の継続研修を実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・ロールプレイ研修で対応力向上を図る</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="8" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="10" customHeight="1"/>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>【最終確認】</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="26" t="inlineStr">
+        <is>
+          <t>管理者署名：</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n"/>
+      <c r="C135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="26" t="inlineStr">
+        <is>
+          <t>確認日：</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="8" t="n"/>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>苦情対応フローチャート（訪問介護事業所）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="23" t="inlineStr">
+        <is>
+          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="10" customHeight="1"/>
+    <row r="140" ht="56" customHeight="1">
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>① 苦情・相談の受付</t>
+        </is>
+      </c>
+      <c r="C140" s="28" t="inlineStr">
+        <is>
+          <t>電話／対面／書面／代理で受理
+傾聴し、感情を受け止める
+否定・反論をしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="56" customHeight="1">
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>② 初期情報の記録</t>
+        </is>
+      </c>
+      <c r="C142" s="28" t="inlineStr">
+        <is>
+          <t>苦情（相談）記録表へ記入
+内容・緊急度・対象利用者を整理
+管理者へ速やかに報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="56" customHeight="1">
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>③ 緊急度判定</t>
+        </is>
+      </c>
+      <c r="C144" s="28" t="inlineStr">
+        <is>
+          <t>【高】生命・安全に係る／重大クレーム
+【中】早急に対応が必要
+【低】通常対応で可</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>④ 初期対応の実施</t>
+        </is>
+      </c>
+      <c r="C146" s="28" t="inlineStr">
+        <is>
+          <t>担当交代、訪問調整、緊急措置
+必要に応じて主治医・ケアマネへ連絡</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="56" customHeight="1">
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>⑤ 事実確認</t>
+        </is>
+      </c>
+      <c r="C148" s="28" t="inlineStr">
+        <is>
+          <t>関係職員への聞き取り
+訪問記録・ケア記録との照合
+利用者・家族へ状況確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>⑥ 分析・判断</t>
+        </is>
+      </c>
+      <c r="C150" s="28" t="inlineStr">
+        <is>
+          <t>原因の特定（ヒューマンエラー／体制要因など）
+事業所としての判断と改善方針決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>⑦ 利用者・家族への説明</t>
+        </is>
+      </c>
+      <c r="C152" s="28" t="inlineStr">
+        <is>
+          <t>事実確認結果と改善策を説明
+理解状況と同意の有無を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>⑧ 是正措置・改善策の実行</t>
+        </is>
+      </c>
+      <c r="C154" s="28" t="inlineStr">
+        <is>
+          <t>担当者変更／介助方法改善／研修の実施
+再発防止策を組織として実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="B156" s="17" t="inlineStr">
+        <is>
+          <t>⑨ フォローアップ</t>
+        </is>
+      </c>
+      <c r="C156" s="28" t="inlineStr">
+        <is>
+          <t>後日、利用者へ確認の連絡
+収束状況を記録、必要に応じて再対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="56" customHeight="1">
+      <c r="B158" s="17" t="inlineStr">
+        <is>
+          <t>⑩ 終結・保存</t>
+        </is>
+      </c>
+      <c r="C158" s="28" t="inlineStr">
+        <is>
+          <t>管理者が最終確認
+苦情（相談）記録表を保存（5年）
+年間集計へ反映</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="108">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C47:E47"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　苦情対応マニュアル</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="136" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -26,6 +26,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束廃止に関する指針" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情対応マニュアル" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント防止規程" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職場ハラスメント防止規定" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +99,11 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="20"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -129,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -206,6 +216,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10933,6 +10946,3965 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E144"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>ハラスメント防止規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）における各種ハラスメントを防止し、発生時には迅速かつ適正に対応し、従業員が安心して働ける職場環境を確保することを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に雇用されるすべての従業員に適用する。役員、派遣社員、アルバイト、業務委託先を含む関係者についても、会社が必要と認める範囲で適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>第2章　定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>（ハラスメントの種類）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>第3条　本規程における「ハラスメント」とは、次に掲げる行為をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>1．パワーハラスメント（パワハラ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　職場において優位な立場を背景に、業務上必要かつ相当な範囲を超えて他人の就業環境を害する行為をいう。代表例は以下のとおりとする。なお、客観的にみて、業務上必要かつ相当な範囲で行われる適正な業務指示や指導については、パワーハラスメントには該当しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 身体的攻撃（暴行・傷害）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 精神的攻撃（侮辱・威圧的発言・過度な叱責・人格否定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 人間関係からの切り離し（無視、隔離、仲間外し）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 過大な要求（遂行不可能な業務の押し付け）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 過小な要求（業務を与えない、能力発揮を妨げる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 個の侵害（私生活への過度な干渉、プライバシー侵害、性的指向・性自認や病歴等の機微な個人情報の暴露）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2．セクシュアルハラスメント（セクハラ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　性的言動により他人に不快感や不利益を与える行為をいう。相手の性的指向又は性自認にかかわらず、同性に対する言動も該当する。代表例は以下のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 不必要な身体接触や性的な冗談・発言</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 性的な噂の流布や性的評価の強要</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 性的関係を断ったことを理由に不利益を与える行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 職場外であっても業務上の関係に基づき行われた性的言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>3．妊娠・出産・育児・介護に関するハラスメント（マタハラ・パタハラ・ケアハラ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　妊娠・出産・育児休業・介護休業等の制度の利用に関する不利益取扱いや嫌がらせ行為をいう。なお、業務分担や安全配慮等の観点から、客観的にみて業務上の必要性に基づく言動は該当しない。例として以下がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 妊娠・出産・休業取得を理由とする解雇・降格・減給</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 休業取得希望に対する嫌味や阻害的言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- 育児・介護を理由とした合理性のない不利益取扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>4．その他のハラスメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- モラルハラスメント（人格否定、悪意のある無視）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- SOGIハラスメント（性的指向・性自認に関する差別的言動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- リモートハラスメント（オンライン会議での過剰な監視・侮辱）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- カスタマーハラスメント（利用者・家族・取引先からの著しい迷惑行為。「利用者等からのハラスメント防止・対応規程」による）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- アルコールハラスメント（飲酒の強要、不適切な酒席での言動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- スモークハラスメント（喫煙に関する迷惑行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　- その他職場環境を不当に害する行為 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="8" customHeight="1">
+      <c r="A69" s="7" t="inlineStr"/>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+    </row>
+    <row r="70" ht="10" customHeight="1"/>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>第3章　禁止と責務</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>（禁止行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>第4条　従業員は、前条に掲げるあらゆる形態のハラスメントを行ってはならない。また、利用者・取引先等の従業員以外の者に対しても、これに類する行為を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>（従業員の責務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>第5条　従業員は、健全な職場環境を維持するため、互いを尊重し、ハラスメントの未然防止に努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>（管理職の責務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>第6条　管理職は、自らハラスメントを行わないことはもとより、部下間のハラスメントを防止し、発生時には速やかに会社へ報告しなければならない。部下がハラスメントを受けている事実を認めながら、これを黙認してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>（会社の責務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>第7条　会社は、ハラスメント防止に関する方針を明示し、相談窓口を設け、教育・啓発を行い、発生時には迅速かつ適正に対応しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="8" customHeight="1">
+      <c r="A84" s="7" t="inlineStr"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
+    </row>
+    <row r="85" ht="10" customHeight="1"/>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>第4章　相談・通報</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>（相談窓口）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>第8条　会社は、従業員が安心して相談できるよう、相談窓口を設置し、可能な限り男女各1名以上の相談担当者を置く。相談担当者は管理者（生田 友哉）及び会社が指名する者とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2　相談は、面談、電話、電子メール、手紙、匿名通報等の方法により受け付ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>3　相談者のプライバシーは厳格に保護し、相談したことを理由に不利益取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>4　相談への具体的な対応は「ハラスメント対応マニュアル」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>（外部相談機関の活用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>第9条　会社は、必要に応じて弁護士、社会保険労務士、行政機関（大阪労働局 総合労働相談コーナー等）を外部相談窓口として指定することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="8" customHeight="1">
+      <c r="A96" s="7" t="inlineStr"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+    </row>
+    <row r="97" ht="10" customHeight="1"/>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>第5章　調査・是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>（調査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>第10条　会社は、相談または通報を受けた場合、速やかに事実関係を確認しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2　調査にあたっては、公平性を確保し、関係者に十分な意見聴取の機会を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>3　調査への協力を求められた従業員は、正当な理由なくこれを拒んではならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>（是正措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="48" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>第11条　会社は、事実確認の結果、ハラスメント行為が認められた場合、加害者に対し指導、配置転換、懲戒処分等の適切な措置を講じるとともに、被害者の労働条件及び就業環境の改善、メンタルケア等の措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2　相談者・協力者に対する二次被害を防止するため、必要な措置を講じなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>3　事実が確認できなかった場合も、職場環境の見直しと防止策の徹底を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="8" customHeight="1"/>
+    <row r="109" ht="8" customHeight="1">
+      <c r="A109" s="7" t="inlineStr"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+    </row>
+    <row r="110" ht="10" customHeight="1"/>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>第6章　再発防止</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>（教育・研修）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>第12条　会社は、全従業員（登録ヘルパーを含む）を対象に、ハラスメント防止に関する教育・研修を入社時及び年1回以上実施する。管理職向け研修は特に重点的に実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2　性別役割分担意識に基づく言動や、妊娠・出産・育児・介護休業等に関する否定的な言動は、ハラスメントの原因や背景となり得ることを研修等で周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="8" customHeight="1"/>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>（再発防止措置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>第13条　会社は、ハラスメントが発生した場合、その原因を分析し、方針の再周知、研修の実施その他職場環境の改善に必要な再発防止措置を講じなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="8" customHeight="1"/>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>（定期報告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>第14条　会社は、相談・通報・対応状況について、個人情報を除いた概要を定期的に取りまとめ、代表取締役に報告し、従業員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="8" customHeight="1"/>
+    <row r="122" ht="8" customHeight="1">
+      <c r="A122" s="7" t="inlineStr"/>
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="8" t="n"/>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+    </row>
+    <row r="123" ht="10" customHeight="1"/>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>第7章　懲戒</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>（懲戒との関係）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>第15条　従業員が本規程に違反しハラスメント行為を行った場合は、「懲戒規程」に基づき懲戒処分の対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="8" customHeight="1"/>
+    <row r="128" ht="8" customHeight="1">
+      <c r="A128" s="7" t="inlineStr"/>
+      <c r="B128" s="8" t="n"/>
+      <c r="C128" s="8" t="n"/>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="8" t="n"/>
+    </row>
+    <row r="129" ht="10" customHeight="1"/>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>第8章　その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>（秘密保持義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="32" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>第16条　会社は、相談・調査・対応の過程で知り得た個人情報を適切に管理し、業務遂行上必要な場合を除き、第三者に開示してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="8" customHeight="1"/>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>（不利益取扱い禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、相談者、協力者、証人となった者等に対して、不利益な取扱いをしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="8" customHeight="1"/>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>（社内外への周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="32" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>第18条　会社は、本規程の内容を従業員に周知し、事業所内への掲示等により常時確認できる状態にしておかなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="8" customHeight="1"/>
+    <row r="140" ht="8" customHeight="1">
+      <c r="A140" s="7" t="inlineStr"/>
+      <c r="B140" s="8" t="n"/>
+      <c r="C140" s="8" t="n"/>
+      <c r="D140" s="8" t="n"/>
+      <c r="E140" s="8" t="n"/>
+    </row>
+    <row r="141" ht="10" customHeight="1"/>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="93">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A132:E132"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　ハラスメント防止規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>職場におけるハラスメントの
+防止に関する規定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規定は、職場におけるパワーハラスメント、セクシュアルハラスメント及び妊娠・出産・育児休業等に関するハラスメント（以下「職場におけるハラスメント」という）を防止するために従業員が遵守するべき事項を定める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　なお、この規定にいう従業員とは、正社員だけではなく、契約社員・登録ヘルパー等の非正規社員及び派遣労働者も含まれるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（パワーハラスメント、セクシュアルハラスメント及び妊娠・出産・育児休業等に関するハラスメントの定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　パワーハラスメントとは、優越的な関係を背景とした言動であって、業務上必要かつ相当な範囲を超えたものにより、就業環境を害することをいう。なお、客観的にみて、業務上必要かつ相当な範囲で行われる適正な業務指示や指導については、職場におけるパワーハラスメントには該当しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2　セクシュアルハラスメントとは、職場における性的な言動に対する他の従業員の対応等により当該従業員の労働条件に関して不利益を与えること又は性的な言動により他の従業員の就業環境を害することをいう。また、相手の性的指向又は性自認の状況にかかわらないほか、異性に対する言動だけでなく、同性に対する言動も該当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>3　前項の他の従業員とは直接的に性的な言動の相手方となった被害者に限らず、性的な言動により就業環境を害されたすべての従業員を含むものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>4　妊娠・出産・育児休業等に関するハラスメントとは、職場において、上司や同僚が、従業員の妊娠・出産及び育児・介護等に関する制度又は措置の利用に関する言動により従業員の就業環境を害すること並びに妊娠・出産等に関する言動により女性従業員の就業環境を害することをいう。なお、業務分担や安全配慮等の観点から、客観的にみて、業務上の必要性に基づく言動によるものについては、妊娠・出産・育児休業等に関するハラスメントには該当しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>5　第1項、第2項及び第4項の職場とは、事業所のみならず、利用者宅その他従業員が業務を遂行するすべての場所をいい、また、就業時間内に限らず、実質的に職場の延長とみなされる就業時間外の時間を含むものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>（禁止行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>第3条　すべての従業員は、他の従業員を業務遂行上の対等なパートナーとして認め、職場における健全な秩序並びに協力関係を保持する義務を負うとともに、その言動に注意を払い、職場内において次の第2項から第5項に掲げる行為をしてはならない。また、自社の従業員以外の者に対しても、これに類する行為を行ってはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2　パワーハラスメント（第2条第1項の要件を満たした以下のような行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 殴打、足蹴りするなどの身体的攻撃</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 人格を否定するような言動をするなどの精神的な攻撃</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 自身の意に沿わない従業員に対して、仕事を外し、長期間にわたり、別室に隔離するなどの人間関係からの切り離し</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 長期間にわたり、肉体的苦痛を伴う過酷な環境下で、勤務に直接関係ない作業を命じるなどの過大な要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 管理職である部下を退職させるため誰でも遂行可能な業務を行わせるなどの過小な要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑥ 他の従業員の性的指向・性自認や病歴などの機微な個人情報について本人の了解を得ずに他の従業員に暴露するなどの個の侵害</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>3　セクシュアルハラスメント（第2条第2項の要件を満たした以下のような行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 性的及び身体上の事柄に関する不必要な質問・発言</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② わいせつ図画の閲覧、配付、掲示</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ うわさの流布</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 不必要な身体への接触</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 性的な言動により、他の従業員の就業意欲を低下せしめ、能力の発揮を阻害する行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑥ 交際・性的関係の強要</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑦ 性的な言動への抗議又は拒否等を行った従業員に対して、解雇、不当な人事考課、配置転換等の不利益を与える行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑧ その他、相手方及び他の従業員に不快感を与える性的な言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>4　妊娠・出産・育児休業等に関するハラスメント（第2条第4項の要件を満たした以下のような行為）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 部下の妊娠・出産、育児・介護に関する制度や措置の利用等に関し、解雇その他不利益な取扱いを示唆する言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 部下又は同僚の妊娠・出産、育児・介護に関する制度や措置の利用を阻害する言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　③ 部下又は同僚が妊娠・出産、育児・介護に関する制度や措置を利用したことによる嫌がらせ等</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　④ 部下が妊娠・出産等したことにより、解雇その他の不利益な取扱いを示唆する言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⑤ 部下又は同僚が妊娠・出産等したことに対する嫌がらせ等</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>5　部下である従業員が職場におけるハラスメントを受けている事実を認めながら、これを黙認する上司の行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>（懲戒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>第4条　次の各号に掲げる場合に応じ、当該各号に定める懲戒処分を行う。処分の手続は「懲戒規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>1　第3条第2項（①を除く。）、第3条第3項①から⑤及び⑧並びに第4項の行為を行った場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　懲戒規程に定めるけん責（譴責）、減給、出勤停止又は降格</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>2　前号の行為が再度に及んだ場合、その情状が悪質と認められる場合、第3条第2項①又は第3条第3項⑥、⑦の行為を行った場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　懲戒規程に定める懲戒解雇</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="8" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>（相談及び苦情への対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="48" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>第5条　職場におけるハラスメントに関する相談及び苦情処理の相談窓口の責任者は代表取締役とし、相談担当者は管理者（生田 友哉）とする。代表取締役は、担当者に対する対応マニュアルの作成及び対応に必要な研修を行うものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>2　職場におけるハラスメントの被害者に限らず、すべての従業員は、パワーハラスメントや性的な言動、妊娠・出産・育児休業等に関する就業環境を害する言動に関する相談及び苦情を相談窓口の担当者に申し出ることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="48" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>3　対応マニュアルに沿い、相談窓口の担当者は相談者のプライバシーに配慮した上で、被害者、行為者から事実関係を聴取する。また、必要に応じて当事者の上司、その他の従業員から事情を聴くことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>4　前項の聴取を求められた従業員は、正当な理由なくこれを拒むことはできない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>5　対応マニュアルに沿い、問題解決のための措置として、第4条による懲戒の他、行為者の異動等被害者の労働条件及び就業環境を改善するために必要な措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>6　相談及び苦情への対応に当たっては、関係者のプライバシーは保護されるとともに、相談をしたこと又は事実関係の確認に協力したこと等を理由として不利益な取扱いは行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>（再発防止の義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>第6条　代表取締役は、職場におけるハラスメント事案が生じた時は、周知の再徹底及び研修の実施、事案発生の原因の分析と再発防止等、会社全体の業務体制の整備等、適切な再発防止策を講じなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>（その他）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>第7条　性別役割分担意識に基づく言動は、セクシュアルハラスメントの発生の原因や要因になり得ること、また、妊娠・出産・育児休業等に関する否定的な言動は、妊娠・出産・育児休業等に関するハラスメントの発生の原因や背景となり得ることから、このような言動を行わないよう注意すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>附則　本規定は令和8年2月1日より実施する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="55">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　職場におけるハラスメントの防止に関する規定</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E111"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>ハラスメント対応マニュアル</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Ⅰ．相談・苦情への対応のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>ハラスメントに関する相談・苦情を受けた場合、本マニュアルに基づき対応することとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>なお、職場におけるハラスメントが現実に生じている場合だけでなく、その発生のおそれがある場合や、職場におけるハラスメントに該当するか否か微妙な場合であっても、相談・苦情に対応するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="10" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>［1］相談窓口の設置</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>1．相談方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　原則面談によるものとするが、電話、手紙、電子メールも可とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2．相談窓口担当者</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　担当者は、可能な限り男女各1名以上とし、相談者が相談しやすい構成とする。担当者に対しては、定期的な研修を行い、資質の向上を図ることとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　相談担当者（ 管理者　生田 友哉 ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>3．適切な対応のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　相談、苦情への対応は、別添フローチャートによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>［2］相談窓口担当者の心得</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1．初めに相談を受けた者の対応によっては問題が大きくなりかねないことから、初期対応は非常に重要であり、適切、迅速に対応すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2．相談者やその相談内容に関係する者のプライバシーや名誉などを尊重し、知り得た事実の秘密を厳守すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3．相談は公正真摯な態度で、丁寧に聞くこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4．相談者が面接による相談を望まない場合は、手紙、電話等の方法によることも教示すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5．相談者の直面する問題の把握が大切であり、そのために不安感を取り除く等の配慮をしながら、解決策を考えること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6．解決のための行動を起こす場合には、その都度事前に相談者にその旨を伝え、意向を確認しながら行うこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7．解決に時間を要するおそれのある場合は、相談者にその旨と所要日数の見込みを伝え、その後も、相談者に不安を与えないため、進捗状況を知らせながら進めること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　8．相談の対象は、ハラスメントにあたるかどうか厳密に判断するのではなく、放置しておけばハラスメントになってしまうものもあるので幅広く対象とすること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>［3］相談・苦情の受け方</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>1．相談内容の聴取</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>相談の中で次の事項について確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（1）相談者と行為者の関係（上司・部下・同僚・利用者宅での同行者等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（2）問題とされる言動がいつ、どこで、どのように行われたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（3）行為者の言動に対し相談者はどのように感じ、どのような対応をとったか、また、それに対する行為者の反応</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（4）行為者の言動について、以前にこのような言動を行ったなど聞いたことがあるか、また、他の人に対しても同様な言動がなされているか</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（5）上司等に対する相談は行ったか</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（6）現在の相談者と行為者との状況はどうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="8" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2．相談に当たっての留意点</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（1）相談者からの話は、本人の了解を得た上で、相談者と担当者の認識のずれをなくすためにきちんと記録しておくこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（2）相談者の求める援助が、加害者に言動を止めるよう求めているか、不利益の回復なのか、謝罪を要求するか、職場全体としての対処を望むのか等、的確に把握すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（3）相談者の様子をよく観察して、対応に時間的な余裕があるかどうかを見極めること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（4）相談者の意向を踏まえ、解決方法やこれからの手順を説明するとともに、当面の対処の仕方についてアドバイスすること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>3．相談対応後の対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　事実関係を調査する苦情処理担当との連携を密にすること。担当以外の者にこの件で接触しようとする場合は、必ず相談者に事前に同意を得ること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="10" customHeight="1"/>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Ⅱ．事後の迅速・適切な対応のために</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>［1］苦情処理担当</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>職場でハラスメントが発生した場合の対応として、相談窓口のほか苦情処理担当を設けることとする。苦情処理担当は、公正かつ客観的な立場で対処する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>苦情処理担当は、代表取締役とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>［2］迅速な事実確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1．苦情処理担当は、事実の確認のため迅速に事情聴取を行うこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2．把握した事実関係、対応状況等についての記録を作成し、保管しておくこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3．事実確認の過程であっても、必要に応じて適切な応急措置を講ずること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4．被害者からの事実確認について</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　苦情処理担当が、相談記録に基づいて、事実関係を改めて被害者に確認すること。ハラスメントの内容が公になり、職場に居づらくなるようなことがないよう、担当は十分配慮すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　5．加害者とされた従業員からの事情聴取について</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　被害者の相談内容を説明した上で、事実関係についての事情聴取を行うと同時に、十分な弁明の機会を与えること。なお、加害者とされる者のプライバシーが十分守られるよう、細心の注意を払い事情聴取すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　6．当事者双方の言い分が食い違っている場合等には、職場の同僚等からの事実確認も行うこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　7．事実確認をした者が管理者である場合は、管理者は、代表取締役に事実確認した内容を報告すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>［3］事実に基づく適正な対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1．相談したこと、又は事実関係の確認に協力したこと等を理由として不利益な取扱いは行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2．事案に対しては問題の深刻度や緊急性に応じた措置を講ずること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（1）加害者に対する注意（問題となっている言動の中止、注意喚起など）や、加害者の監督者に対して状況の観察等を要請する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（2）加害者の担当利用者や勤務シフトを変更する等、当事者を引き離すよう人事上の配慮を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（3）当事者間の関係改善について援助を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（4）被害者に労働条件、就業環境上の不利益が存在している場合には、それを回復する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（5）被害者の精神的ショックが大きい場合には、メンタルケアに配慮する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　（6）就業規則及び懲戒規程に基づき、加害者に一定の制裁を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3．事案に関し具体的に講じられた措置について、当事者に説明すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4．会社全体で再発防止策を講ずること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>相談苦情への対応の流れ（フローチャート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="10" customHeight="1"/>
+    <row r="98" ht="28" customHeight="1">
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>相談・苦情</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n"/>
+      <c r="D98" s="22" t="n"/>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="46" customHeight="1">
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>相談・苦情窓口
+（相談担当者：管理者 生田 友哉／苦情処理担当：代表取締役）</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n"/>
+      <c r="D100" s="22" t="n"/>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>事実関係の確認</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="n"/>
+      <c r="D102" s="22" t="n"/>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>相談者からの
+ヒヤリング</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>加害者とされた者
+からのヒヤリング</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="inlineStr">
+        <is>
+          <t>同僚など第三者
+からのヒヤリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>事実が確認された</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>事実が確認されない</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="70" customHeight="1">
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>会社の対応を検討</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>職場環境の見直しと
+防止策の徹底
+相談者への説明
+当事者間の関係改善の援助</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="82" customHeight="1">
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>雇用管理上の措置（担当変更、不利益回復やメンタルケア、当事者間の関係改善の援助等）
+相談者への説明
+就業規則・懲戒規程に基づく加害者への制裁（けん責、出勤停止、懲戒解雇等）
+職場環境の見直しと再発防止策の徹底</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n"/>
+      <c r="D109" s="22" t="n"/>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="71">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　ハラスメント対応マニュアル</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="95" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E169"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>利用者等からのハラスメント
+防止・対応規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　本規程は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という）の従業員が、利用者またはその家族その他の関係者（以下「利用者等」という）からのハラスメント行為により、心身の安全や就労環境を害されることを防止し、安心して職務に従事できる体制を確保することを目的とする。あわせて、労働契約法、労働安全衛生法その他関係法令の趣旨に則り、会社の安全配慮義務を明確にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　本規程は、会社に勤務する全従業員（正社員、契約社員、嘱託社員、パートタイマー、アルバイト、登録ヘルパー、派遣社員を含む）に適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は、利用者等によるハラスメントを対象とし、従業員間のハラスメントについては「ハラスメント防止規程」及び「職場におけるハラスメントの防止に関する規定」を適用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="8" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>第3条　本規程において「ハラスメント」とは、利用者等の言動により従業員が不快感、屈辱感、恐怖感等を受け、健康や就業環境が害される行為をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2　ハラスメントには、次の行為を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>（1）身体的暴力</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・殴打、押し倒し、突き飛ばし、掴みかかる行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・物を投げつける、蹴る、刃物等を示すなどの威嚇行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>（2）精神的暴力</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・大声での罵倒、威嚇、脅迫、恫喝</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・「無能」「役立たず」等の人格を否定する発言</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・差別的言動（国籍、性別、年齢、障害、宗教等に基づくもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・過度で不合理な要求、業務妨害となる過剰な干渉</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>（3）セクシュアル・ハラスメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・性的な冗談や発言、卑猥な言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・不必要かつ一方的な身体接触</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・性的関心の示唆、交際の強要</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・性的な言動を拒否したことによる嫌がらせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>（4）ストーカー的言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問や電話、メール等の執拗な繰り返し</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・待ち伏せ、尾行、従業員の私生活への過度な介入</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・個人情報を不当に入手・利用しようとする行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="8" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>（5）業務妨害行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・業務の進行を妨げる過剰な監視、干渉、無理難題の要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・正当な理由なく職員の交代を強要すること</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス提供を阻害する虚偽の申し立て</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>（6）その他社会通念上許容されない行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・常識的に見て従業員の心身に負担を与え、職務遂行を困難にさせる一切の言動</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>3　「二次被害」とは、被害を申告した従業員に対する詮索、責任転嫁、報復、中傷、孤立化など、被害を拡大・継続させる行為をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>4　認知症等の病状や障害の特性による言動であっても、従業員の安全確保の対象とする。ただし、その対応にあたっては、利用者の病状等を踏まえ、居宅介護支援事業所（ケアマネジャー）・主治医等と連携してケアの方法を検討する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="10" customHeight="1"/>
+    <row r="70" ht="8" customHeight="1">
+      <c r="A70" s="7" t="inlineStr"/>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+    </row>
+    <row r="71" ht="10" customHeight="1"/>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>第2章　会社の責務</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>（基本方針）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>第4条　会社は、利用者等からのハラスメントを一切容認しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、従業員の安全と尊厳を守り、報告を行った者に不利益取扱いをしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>（防止責任者および相談窓口）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>第5条　会社は、ハラスメント防止責任者を設置し、その職務は代表取締役が担う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2　ハラスメント相談窓口は事業所に設置し、管理者（生田 友哉）が担当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>3　相談窓口は通報を受けた際、速やかに事実確認・初動対応を行い、防止責任者に報告する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>（教育・研修）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>第6条　会社は、従業員に対し、次の措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>（1）入社時および年1回のハラスメント防止研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>（2）管理職に対する事案対応力強化研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>（3）利用者・家族に対する契約時の「ハラスメント禁止条項」の説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="8" customHeight="1"/>
+    <row r="88" ht="8" customHeight="1">
+      <c r="A88" s="7" t="inlineStr"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+    </row>
+    <row r="89" ht="10" customHeight="1"/>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>第3章　従業員の行動指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>（発生時の対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>第7条　従業員は、利用者等からのハラスメントを受けた場合には、自身の安全を最優先とし、速やかに退避または制止の意思表示を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2　緊急の危険がある場合は、直ちに110番通報等を行うことができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>3　従業員は、発生から15分以内にサービス提供責任者または管理者へ連絡するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>（報告義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>第8条　従業員は、当日中に必ず口頭で報告しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2　管理者は、当日中に職員の安全確認と精神的ケアを実施し、サービス継続可否を即断する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>3　被害を受けた従業員は、24時間以内に「ハラスメント報告書」を提出する。ただし、心身の状況により困難な場合は、管理者が聞き取りにより作成する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="8" customHeight="1"/>
+    <row r="101" ht="8" customHeight="1">
+      <c r="A101" s="7" t="inlineStr"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="8" t="n"/>
+    </row>
+    <row r="102" ht="10" customHeight="1"/>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>第4章　会社の対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>（調査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>第9条　防止責任者（代表取締役）は、報告を受けた場合、3日以内に事実確認を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2　調査は、被害職員のヒアリング、同席者・目撃者の聴取、ケアマネジャーへの報告、利用者・家族への確認（安全な場合に限る）等を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>3　利用者側には必要に応じて弁明機会を与える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="8" customHeight="1"/>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>（レベル判定と対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>第10条　防止責任者は調査後、直ちに以下の区分に基づき対応を決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>1　レベル1（軽度）：注意指導で改善可能な場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・家族へ書面での注意・改善要請</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・ケアマネジャーへの情報提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・1か月後の状況確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2　レベル2（中度）：条件付きでサービス継続可能な場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・複数職員での訪問を義務化（必要に応じて2人訪問の算定について利用者の同意を得る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス時間短縮等の条件変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・月1回の状況確認とケアマネ連携強化</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>3　レベル3（重度）：サービス継続不能と判断される場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・契約解除通知（契約書の定めによる予告期間と引継ぎ期間を考慮）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・警察への被害相談・通報</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・ケアマネジャー・地域包括支援センター・大阪市と連携した他事業所紹介等、利用者への配慮措置</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・代表取締役への緊急報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="8" customHeight="1"/>
+    <row r="125" ht="8" customHeight="1">
+      <c r="A125" s="7" t="inlineStr"/>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+    </row>
+    <row r="126" ht="10" customHeight="1"/>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>第5章　被害職員の保護・支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>（医療・精神的支援）</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>第11条　会社は、被害職員に対し、医療機関・カウンセリングの利用を支援し、費用について必要な配慮を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、被害職員の心身の健康状態を継続的に確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>3　会社は、労災申請を含む必要な法的手続を支援する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="8" customHeight="1"/>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>（職場環境の配慮）</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>第12条　会社は、被害職員の希望を尊重し、担当変更や休養措置を講じることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、不利益取扱いの禁止を明確にし、必要に応じて文書で確約する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>3　会社は、職場復帰に際し、フォロー体制を整備する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="8" customHeight="1"/>
+    <row r="138" ht="8" customHeight="1">
+      <c r="A138" s="7" t="inlineStr"/>
+      <c r="B138" s="8" t="n"/>
+      <c r="C138" s="8" t="n"/>
+      <c r="D138" s="8" t="n"/>
+      <c r="E138" s="8" t="n"/>
+    </row>
+    <row r="139" ht="10" customHeight="1"/>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>第6章　再発防止・改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>（社内対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>第13条　会社は、匿名化した事例を四半期ごとの社内研修で共有し、再発防止を図る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="8" customHeight="1"/>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>（利用者・家族への対応）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>第14条　会社は、利用者・家族に対し、定期的にハラスメント防止の啓発文書を配布する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="8" customHeight="1"/>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>（代表取締役への報告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>第15条　レベル3に該当する案件については、代表取締役が再発防止策を決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="8" customHeight="1"/>
+    <row r="150" ht="8" customHeight="1">
+      <c r="A150" s="7" t="inlineStr"/>
+      <c r="B150" s="8" t="n"/>
+      <c r="C150" s="8" t="n"/>
+      <c r="D150" s="8" t="n"/>
+      <c r="E150" s="8" t="n"/>
+    </row>
+    <row r="151" ht="10" customHeight="1"/>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>第7章　外部対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>（行政への報告・相談）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>第16条　会社は、重大事案について大阪市（保険者）に速やかに報告・相談する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="8" customHeight="1"/>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>（外部への説明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>第17条　会社は、社会的影響が大きい場合は、代表取締役が適切な外部説明を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="8" customHeight="1"/>
+    <row r="159" ht="8" customHeight="1">
+      <c r="A159" s="7" t="inlineStr"/>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="8" t="n"/>
+    </row>
+    <row r="160" ht="10" customHeight="1"/>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>第8章　雑則</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>（マニュアルとの関係）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>第18条　本規程に基づく具体的な対応手順は、別途定める「利用者等からのハラスメント防止・対応マニュアル」に従う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="8" customHeight="1"/>
+    <row r="165" ht="8" customHeight="1">
+      <c r="A165" s="7" t="inlineStr"/>
+      <c r="B165" s="8" t="n"/>
+      <c r="C165" s="8" t="n"/>
+      <c r="D165" s="8" t="n"/>
+      <c r="E165" s="8" t="n"/>
+    </row>
+    <row r="166" ht="10" customHeight="1"/>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>1　本規程の改廃その他定めのない事項は、代表取締役の決定その他関係規程による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>2　本規程は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="114">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A168:E168"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A136:E136"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
+    <mergeCell ref="A157:E157"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A159:E159"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A147:E147"/>
+    <mergeCell ref="A161:E161"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A153:E153"/>
+    <mergeCell ref="A162:E162"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A154:E154"/>
+    <mergeCell ref="A163:E163"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　利用者等からのハラスメント防止・対応規程</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E138"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>利用者等からのハラスメント
+防止・対応マニュアル</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>1．本マニュアルの位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1．本マニュアルは「利用者等からのハラスメント防止・対応規程」に基づき、従業員が現場で直面した際に適切かつ迅速に対応するための具体的手順を示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2．規程が「会社としての方針・責任体制」を定めるのに対し、本マニュアルは「現場職員の実務行動指針」として機能する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　3．本マニュアルは全従業員（登録ヘルパーを含む）に周知し、常に最新の知見・事例に基づき改訂される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2．発生時の現場対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2-1．即時退避判断基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>以下に該当する場合は、原則として即座に退避する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・身体への接触や暴力の兆候</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・性的発言・行為・身体接触</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・大声での威嚇・恫喝・暴言</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・物を投げる等の威嚇行為</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・継続的な人格否定発言</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>2-2．現場での行動手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・「困ります、やめてください」と明確に制止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・継続する場合は即座に退避、安全な場所へ移動。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者に急変等の危険がある場合は、退避後に管理者・家族・ケアマネジャーへ連絡し、安全確認の方法を相談する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・生命の危険を感じた場合は110番通報、負傷時は119番通報。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・15分以内にサービス提供責任者→管理者へ電話連絡。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・可能であれば音声録音・写真撮影等で証拠を保全（安全確保優先）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>3．第一報・初期対応（当日中）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>3-1．職員の第一報</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・発生直後にサービス提供責任者へ報告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・その後、管理者へ報告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>3-2．管理者の初期対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・職員の安全確認と精神的ケア。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・当日のサービス継続可否を即断（安全第一原則）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・代替職員手配またはサービス停止の判断（停止する場合はケアマネジャーへ連絡）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・24時間以内に「ハラスメント報告書」作成を依頼。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・証拠（音声・写真・目撃証言・診断書等）の有無を確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・報告内容を代表取締役へ送付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1"/>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>4．事実確認・調査（3日以内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・調査主体：代表取締役（防止責任者）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・被害職員への詳細ヒアリング（録音・記録）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・同席者・目撃者の事情聴取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・ケアマネジャーへの状況報告・情報収集。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・家族への事実確認（安全な場合に限る）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者側への弁明機会の提供。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・結果は「調査報告書」にまとめ、防止責任者が対応レベルを判定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="8" customHeight="1"/>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>5．レベル判定と対応決定（調査完了後即時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>レベル1（軽度）：注意指導で改善可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・家族へ書面での注意・改善要請。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・ケアマネジャーへの情報提供。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・1か月後の状況確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="8" customHeight="1"/>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>レベル2（中度）：条件付きサービス継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・複数職員での訪問を義務化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・サービス時間短縮等の条件変更。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・月1回の状況確認とケアマネジャー連携。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>レベル3（重度）：契約解除・警察対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・契約解除通知（契約書の予告期間と引継ぎ期間を確保）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・警察への相談・通報。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・ケアマネジャー・地域包括支援センターと連携した他事業所紹介等、利用者への配慮措置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・代表取締役への緊急報告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>6．被害職員の保護・支援（全レベル共通）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>医療・精神的支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・医療機関・カウンセリングの案内と費用支援。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・定期的な心身健康確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・労災申請支援と必要書類作成協力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>職場環境の配慮</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・担当変更・休養措置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・不利益取扱い禁止を文書で確約。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・職場復帰時のフォロー体制を整備。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="26" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>7．再発防止・継続改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・匿名化事例の社内研修での共有。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・四半期ごとの「ハラスメント事例検討会」を開催。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・家族への啓発文書を定期配布。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・レベル3案件は代表取締役が再発防止策を決定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・年度末に「ハラスメント対応年次報告書」を作成し、代表取締役に提出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="8" customHeight="1"/>
+    <row r="105" ht="26" customHeight="1">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>8．記録・報告・保管</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・報告書、調査報告書、証拠資料は管理者が一元管理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・保存期間は原則5年間とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・個人情報は個人情報保護法および「情報管理規程」に基づき厳格に管理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="26" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>9．改訂・見直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・本マニュアルは、法令改正、行政指導、判例、社会情勢、実際の事案発生状況等を踏まえ、適宜改訂する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・改訂は管理者が案を作成し、防止責任者（代表取締役）が承認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・改訂版は全従業員に速やかに周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="8" customHeight="1"/>
+    <row r="115" ht="26" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>10．参考：対応フロー（図解）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="10" customHeight="1"/>
+    <row r="117" ht="26" customHeight="1">
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>発生</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="n"/>
+      <c r="D117" s="22" t="n"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="26" customHeight="1">
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>退避・制止（困ります、やめてください）</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n"/>
+      <c r="D119" s="22" t="n"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="26" customHeight="1">
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>110番／119番（必要時）</t>
+        </is>
+      </c>
+      <c r="C121" s="22" t="n"/>
+      <c r="D121" s="22" t="n"/>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>15分以内にサービス提供責任者・管理者へ報告</t>
+        </is>
+      </c>
+      <c r="C123" s="22" t="n"/>
+      <c r="D123" s="22" t="n"/>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>当日中：管理者が安全確認・サービス可否判断</t>
+        </is>
+      </c>
+      <c r="C125" s="22" t="n"/>
+      <c r="D125" s="22" t="n"/>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="26" customHeight="1">
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>24時間以内：報告書作成・証拠確認</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="n"/>
+      <c r="D127" s="22" t="n"/>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="26" customHeight="1">
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>3日以内：代表取締役が調査・弁明機会付与</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n"/>
+      <c r="D129" s="22" t="n"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="26" customHeight="1">
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>レベル判定（1：注意／2：条件付継続／3：契約解除・警察）</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n"/>
+      <c r="D131" s="22" t="n"/>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="26" customHeight="1">
+      <c r="B133" s="17" t="inlineStr">
+        <is>
+          <t>被害職員支援（医療・休養・労災・不利益禁止）</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n"/>
+      <c r="D133" s="22" t="n"/>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="26" customHeight="1">
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>再発防止（研修・事例検討会・代表取締役への報告）</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n"/>
+      <c r="D135" s="22" t="n"/>
+    </row>
+    <row r="136" ht="10" customHeight="1"/>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>本マニュアルは、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="91">
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="B133:D133"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="B135:D135"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="B119:D119"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="B127:D127"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A111:E111"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　利用者等からのハラスメント防止・対応マニュアル</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="114" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -31,6 +31,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14905,6 +14906,766 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>虐待防止に関する指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第1条　この指針は、株式会社dhpケアマネジメント　いいかいごが運営する指定訪問介護事業に係る虐待を防止するための体制を整備することにより、利用者の権利を擁護するとともに、利用者がサービス等を適切に利用できるように支援することを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>（対象とする虐待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>第2条　この指針において「虐待」とは、職員が支援等を行う利用者に対して行う、次の各号の行為をいう（高齢者虐待防止法第2条に定める行為を含む）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>① 利用者の身体に外傷が生じ、または生じるおそれのある暴行を加えること（身体的虐待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>② 正当な理由なく利用者の身体を拘束すること（身体的虐待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>③ 利用者にわいせつな行為をすることまたはわいせつな行為をさせること（性的虐待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>④ 利用者に対する暴言、拒絶的な対応、不当な差別的言動、心理的外傷を与える言動を行うこと（心理的虐待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>⑤ 利用者を衰弱させるような減食、長時間の放置等、介護・世話の放棄（ネグレクト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>⑥ 利用者の財産を不当に処分すること、その他当該利用者から不当な財産上の利益を得ること（経済的虐待）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>（虐待に対する基本方針）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>第3条　職員は利用者に対し、いかなる虐待もしてはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>第2章　虐待対応体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>（虐待対応責任者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>第4条　本指針による虐待の責任主体を明確にするため、虐待防止責任者（以下「虐待対応責任者」という。）を設置する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待対応責任者は、管理者（生田 友哉）があたるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>（虐待対応責任者の職務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>第5条　虐待対応責任者の職務は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>① 虐待内容及び原因の把握、解決策の検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>② 解決のための当事職員との話し合い</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>③ 利用者（家族含む）及び通報者への結果報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>④ 大阪市等の各自治体への通報・報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>（虐待受付担当者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>第6条　利用者等が虐待通報を行いやすくするため、虐待受付担当者を設置する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待受付担当者はサービス提供責任者とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>3　虐待受付担当者の不在時は、虐待受付担当者以外の職員が通報を受けることができるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>4　前項により虐待の通報を受けた職員は、遅滞なく虐待受付担当者に別に定める「苦情受付」によりその内容を報告しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>（虐待受付担当者の職務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>第7条　虐待受付担当者の職務は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>① 利用者または家族、職員等からの虐待通報受付</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>② 虐待内容、利用者等への意向の確認と記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>③ 虐待対応責任者への前号による記録を用いた報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="8" customHeight="1">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+    </row>
+    <row r="69" ht="10" customHeight="1"/>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>第3章　虐待防止対応及び解決</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>（虐待対応の周知）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>第8条　虐待対応責任者は、事業所内への掲示等により、虐待対応について周知を図らなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>（虐待通報及び発見）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>第9条　利用者本人、またはその家族、職員等からの通報がある時は本指針に基づき適切に対応しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2　職員は、虐待を受けたと思われる利用者を発見した際は、直ちに虐待受付担当者に通報しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="48" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>3　訪問時に、家族等の養護者による虐待を受けたと思われる利用者を発見した場合も同様とし、事業所は居宅介護支援事業所と連携のうえ、大阪市（区保健福祉センター）又は地域包括支援センターに通報する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>4　職員は、高齢者虐待防止法に基づき、直接市町村に通報することもできる。通報したことを理由として、解雇その他不利益な取扱いを受けない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>（虐待通報の受付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>第10条　虐待の通報は、別に定める「苦情受付」によるほか、様式によらない文書、口頭による通報によっても受け付けることができるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="48" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待受付担当者は利用者等から虐待通報を受け付けた際に「苦情受付・経過記録書」を作成し、その内容を虐待通報者に確認するものとする。なお、通報者名の記載については、通報者本人の同意を必要とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>（虐待の報告・確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>第11条　虐待受付担当者は、受け付けた虐待の内容を直ちに虐待対応責任者に報告する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待対応責任者は、職員による虐待を受けたと思われる利用者を発見した場合、または通報を受けた場合は、事実確認の結果を待たず、速やかに大阪市（保険者）に通報する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="8" customHeight="1"/>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>（虐待解決に向けた協議）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>第12条　虐待対応責任者は、虐待通報の内容を正確に理解するため、虐待通報者及び当該利用者から通報内容を詳細に聞き取るものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待対応責任者は、当事職員と解決に向けた話し合いを行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>3　前項による話し合いは、原則として虐待通報のあった日から7日以内に行わなければならないものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>4　虐待通報者及び虐待対応責任者は、必要に応じて第三者の専門家に助言を求めることができるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>5　事実確認の間、必要に応じて当事職員の担当を外す等、利用者の安全を最優先とした措置を講じる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>（虐待解決に向けた記録・結果報告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>第13条　虐待対応責任者は、当事職員との話し合いの結果や改善を約束した事項について別に定める「虐待解決協議報告書」に記録するものとする。記録は5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待対応責任者は、当事職員との話し合いの結果や改善を約束した事項について、利用者及びその家族、虐待通報者に対して書面により報告をする。尚、報告は、原則として話し合いを終了した日から7日以内に行わなければならないものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>3　虐待対応責任者は、利用者及びその家族が満足する解決が図られなかった場合には、大阪市等の自治体の苦情相談窓口を紹介するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>4　虐待の事実が認められた職員については、「懲戒規程」に基づき処分を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="8" customHeight="1"/>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>（解決結果の公表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>第14条　サービスの質の向上を図るため、本指針に基づく虐待防止及び解決の対応状況について、個人情報に関する事項を除き、事業報告書に記載する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>（虐待防止のための職員等研修）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>第15条　虐待対応責任者は、虐待防止啓発のための職員研修を年1回以上定期的に開催するとともに、新規採用時には必ず実施しなければならない。研修の実施内容は記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2　前項の研修は、介護業務に携わる職員（登録ヘルパーを含む）以外の職員にも行うものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>3　第16条に規定する虐待防止委員会の委員長は、虐待防止に関する外部研修等に職員を積極的に参加させるよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="8" customHeight="1"/>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>（虐待防止委員会の設置）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>第16条　虐待防止責任者は、事業所における虐待防止を図るため、虐待防止委員会を設置しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="48" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2　虐待防止委員会は、年1回以上定期的に開催するほか、虐待発生の都度開催しなければならない。開催はテレビ電話装置等を活用して行うことができ、感染対策委員会等の他の会議体と一体的に開催することを妨げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>3　虐待防止委員会の委員長は、虐待対応責任者とする。委員は管理者、サービス提供責任者及び訪問介護員の代表とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>4　委員長が必要と認める場合は、第三者の専門家に虐待防止委員会への参加を求めることができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>5　虐待防止委員会の結果は記録し、全職員に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>6　虐待防止委員は、日ごろから虐待防止の啓発に努めなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>（権利擁護のための成年後見制度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>第17条　虐待対応責任者は、高齢者の人権等の権利擁護のため、成年後見制度の利用を利用者及びその家族等に啓発するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>（指針の閲覧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>第18条　本指針は事業所内に掲示するとともに、利用者及びその家族等がいつでも閲覧できるようにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="8" customHeight="1"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>（改廃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>第19条　本指針の改定は、虐待防止委員会の審議を経て、必要に応じて代表取締役が行うものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="8" customHeight="1"/>
+    <row r="126" ht="8" customHeight="1">
+      <c r="A126" s="7" t="inlineStr"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+    </row>
+    <row r="127" ht="10" customHeight="1"/>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>この指針は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="85">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　虐待防止に関する指針</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -816,7 +816,7 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>（3）訪問介護員　3名以上（常勤換算2.5名以上）</t>
+          <t>（3）訪問介護員　10名（常勤7名、非常勤3名）（常勤換算2.5名以上を確保する）</t>
         </is>
       </c>
     </row>
@@ -830,14 +830,14 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>（4）事務職員　0名（常勤又は非常勤 0名）</t>
+          <t>（4）事務職員　1名（常勤1名）</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　必要な事務を行う。</t>
+          <t xml:space="preserve">　　介護給付費等の請求事務及び通信連絡事務等を行う。</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>（1）営業日　月曜日から日曜日までとする。ただし、祝日、12月30日から1月3日までを除く。</t>
+          <t>（1）営業日　月曜日から金曜日までとする。ただし、祝日、8月13日から8月15日まで、12月30日から1月3日までを除く。</t>
         </is>
       </c>
     </row>
@@ -873,416 +873,423 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>（3）サービス提供時間　24時間（午前0時から午後12時まで）とする。</t>
+          <t>（3）サービス提供日　1月1日から1月3日までを除く毎日とする。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>（4）営業時間外は電話等により常時連絡が可能な体制とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="8" customHeight="1"/>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+          <t>（4）サービス提供時間　午前7時から午後11時までとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>（5）営業時間外のサービス提供時間帯は、電話等により連絡が可能な体制とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>（指定訪問介護の内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>第7条　事業所で行う指定訪問介護の内容は次のとおりとする。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>第7条　事業所で行う指定訪問介護の内容は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>（1）訪問介護計画の作成</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>（2）身体介護に関する内容　①排泄・食事介助 ②清拭・入浴・身体整容 ③体位変換 ④移動・移乗介助、外出介助 ⑤その他の必要な身体の介護</t>
         </is>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>（2）身体介護に関する内容　①排泄・食事介助 ②清拭・入浴・身体整容 ③体位変換 ④移動・移乗介助、外出介助 ⑤その他の必要な身体の介護</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>（3）生活援助に関する内容　①調理 ②衣類の洗濯、補修 ③住居の掃除、整理整頓 ④生活必需品の買い物 ⑤その他必要な家事</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="8" customHeight="1"/>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>（指定訪問介護の利用料等）</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="64" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="74" ht="64" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>第8条　指定訪問介護を提供した場合の利用料の額は、介護報酬告示上の額とし、そのサービスが法定代理受領サービスであるときは、利用料のうち各利用者の負担割合に応じた額の支払いを受けるものとする。なお、法定代理受領以外の利用料については、「指定居宅サービスに要する費用の額の算定に関する基準」（平成12年2月10日厚生省告示第19号）によるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>2　次条に定める通常の事業の実施地域を越えて行う事業に要する交通費は、その実費を徴収する。なお、自動車を使用した場合の交通費は、次の額とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>（1）事業所から片道5キロメートル未満　100円（税別）</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>（2）事業所から片道5キロメートル以上　1kmを増すごとに20円ずつ加算（税別）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
+          <t>（1）事業所から片道5キロメートル未満　200円</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
+          <t>（2）事業所から片道5キロメートル以上　500円</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
           <t>3　前2項の利用料等の支払を受けたときは、利用者又はその家族に対し、利用料とその他の利用料（個別の費用ごとに区分したもの）について記載した領収書を交付する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>4　指定訪問介護の提供の開始に際しては、あらかじめ、利用者又はその家族に対し、当該サービスの内容及び費用に関し事前に文書で説明した上で、その内容及び支払いに同意する旨の文書に署名（記名押印）を受けるものとする。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
+          <t>4　指定訪問介護の提供の開始に際しては、あらかじめ、利用者又はその家族に対し、当該サービスの内容及び費用に関し事前に文書で説明した上で、その内容及び支払いに同意する旨の文書に署名（記名押印）を受けるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
           <t>5　法定代理受領サービスに該当しない指定訪問介護に係る利用料の支払いを受けたときは、提供した指定訪問介護の内容、費用の額その他必要と認められる事項を記載したサービス提供証明書を利用者に対して交付するものとする。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="8" customHeight="1"/>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>（通常の事業の実施地域）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>第9条　通常の事業の実施地域は、大阪市とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>第9条　通常の事業の実施地域は、大阪市西淀川区、淀川区、東淀川区、天王寺区、中央区、北区とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>（衛生管理等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>第10条　訪問介護員等の清潔の保持及び健康状態の管理を行うとともに、事業所の設備及び備品等の衛生的な管理に努めるものとする。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>第10条　訪問介護員等の清潔の保持及び健康状態の管理を行うとともに、事業所の設備及び備品等の衛生的な管理に努めるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
           <t>2　事業所は、感染症の予防及びまん延の防止のため、感染対策委員会の開催（おおむね6か月に1回以上）、指針の整備、研修及び訓練の実施を行う。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="8" customHeight="1"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="88" ht="8" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>（緊急時等における対応方法）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="48" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="90" ht="48" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>第11条　訪問介護員等は、指定訪問介護の提供を行っているときに利用者に病状の急変、その他緊急事態が生じたときは、速やかに主治医に連絡する等の措置を講じるとともに、管理者に報告する。また、主治医への連絡が困難な場合は、緊急搬送等の必要な措置を講じるものとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>2　指定訪問介護の提供により事故が発生した場合は、利用者の所在する市町村、利用者の家族、利用者に係る居宅介護支援事業者等に連絡するとともに、必要な措置を講じるものとする。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
+          <t>2　指定訪問介護の提供により事故が発生した場合は、利用者の所在する市町村、利用者の家族、利用者に係る居宅介護支援事業者等に連絡するとともに、必要な措置を講じるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
           <t>3　利用者に対する指定訪問介護の提供により賠償すべき事故が発生した場合には、損害賠償を速やかに行うものとする。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="93" ht="8" customHeight="1"/>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>（苦情処理）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>第12条　指定訪問介護の提供に係る利用者及びその家族からの苦情に迅速かつ適切に対応するために必要な措置を講じるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="64" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>2　事業所は、提供した指定訪問介護に関し、介護保険法第23条の規定により市町村が行う文書その他の物件の提出若しくは提示の求め又は当該市町村の職員からの質問若しくは照会に応じ、及び市町村が行う調査に協力するとともに、市町村から指導又は助言を受けた場合は、当該指導又は助言に従って必要な改善を行うものとする。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>3　事業所は、提供した指定訪問介護に係る利用者からの苦情に関して国民健康保険団体連合会が行う調査に協力するとともに、国民健康保険団体連合会から指導又は助言を受けた場合は、当該指導又は助言に従って必要な改善を行うものとする。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="8" customHeight="1"/>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>（個人情報の保護）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>第13条　事業所は、利用者の個人情報について「個人情報の保護に関する法律」及び厚生労働省が策定した「医療・介護関係事業者における個人情報の適切な取扱いのためのガイダンス」を遵守し適切な取り扱いに努めるものとする。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
+          <t>第13条　事業所は、利用者の個人情報について「個人情報の保護に関する法律」及び厚生労働省が策定した「医療・介護関係事業者における個人情報の適切な取扱いのためのガイダンス」を遵守し適切な取り扱いに努めるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
           <t>2　事業者が得た利用者又はその家族の個人情報については、事業者での介護サービスの提供以外の目的では原則的に利用しないものとし、外部への情報提供については必要に応じて利用者又はその代理人の了解を得るものとする。</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="8" customHeight="1"/>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>（虐待防止に関する事項）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>第14条　事業所は、利用者の人権の擁護・虐待等の防止のため次の措置を講ずるものとする。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>（1）虐待防止のための対策を検討する委員会の定期的な開催と、その結果の従業者への周知</t>
+          <t>第14条　事業所は、利用者の人権の擁護・虐待等の防止のため次の措置を講ずるものとする。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>（2）虐待防止のための指針の整備</t>
+          <t>（1）虐待防止のための対策を検討する委員会の定期的な開催と、その結果の従業者への周知</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>（3）虐待を防止するための従業者に対する研修の実施（年1回以上及び新規採用時）</t>
+          <t>（2）虐待防止のための指針の整備</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>（4）前3号の措置を適切に実施するための担当者の設置（虐待防止責任者：管理者）</t>
+          <t>（3）虐待を防止するための従業者に対する研修の実施（年1回以上及び新規採用時）</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>（5）利用者及びその家族からの苦情処理体制の整備</t>
+          <t>（4）前3号の措置を適切に実施するための担当者の設置（虐待防止責任者：管理者）</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>（5）利用者及びその家族からの苦情処理体制の整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
           <t>（6）その他虐待防止のために必要な措置</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="111" ht="48" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>2　事業所は、サービス提供中に、当該事業所従業者又は養護者（利用者の家族等高齢者を現に養護する者）による虐待を受けたと思われる利用者を発見した場合は、速やかに、これを市町村に通報するものとする。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="112" ht="8" customHeight="1"/>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>（身体拘束等の禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>第15条　事業所は、利用者又は他の利用者等の生命又は身体を保護するため緊急やむを得ない場合を除き、身体的拘束その他利用者の行動を制限する行為を行わない。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
+          <t>第15条　事業所は、利用者又は他の利用者等の生命又は身体を保護するため緊急やむを得ない場合を除き、身体的拘束その他利用者の行動を制限する行為を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
           <t>2　緊急やむを得ず身体的拘束等を行う場合には、その態様及び時間、その際の利用者の心身の状況並びに緊急やむを得ない理由を記録する。</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="8" customHeight="1"/>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>（業務継続計画の策定等）</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="48" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
+    <row r="118" ht="48" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>第16条　事業所は、感染症や非常災害の発生時において、利用者に対する指定訪問介護の提供を継続的に実施し、及び非常時の体制で早期の業務再開を図るための業務継続計画を策定し、当該計画に従い必要な措置を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>2　事業所は、従業者に対し、業務継続計画について周知するとともに、必要な研修及び訓練を定期的に実施する。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>（その他運営に関する重要事項）</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>第17条　事業所は、従業者の資質向上のために次のとおり研修の機会を設けるものとし、また、業務の執行体制についても検証、整備する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>（1）採用時研修　採用後1か月以内</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>（2）継続研修　年2回</t>
+          <t>（1）採用時研修　採用後1か月以内</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
+          <t>（2）継続研修　年2回</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>2　従業者は、業務上知り得た利用者又はその家族の秘密を保持する。</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="126" ht="48" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>3　事業所は、従業者であった者に、業務上知り得た利用者又はその家族の秘密を保持させるため、従業者でなくなった後においてもこれらの秘密を保持するべき旨を、従業者との雇用契約の内容とする。</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>4　事業所は、職場におけるハラスメントの防止のための方針の明確化等の必要な措置を講じる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>5　事業所は、指定訪問介護に関する諸記録を整備し、そのサービス提供をした日から最低5年間は保存するものとする。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="32" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>5　事業所は、指定訪問介護に関する諸記録を整備し、そのサービス提供をした日から最低5年間は保存するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
           <t>6　この規程に定める事項の外、運営に関する重要事項は株式会社dhpケアマネジメントと事業所の管理者との協議に基づいて定めるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="8" customHeight="1"/>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
+    <row r="130" ht="8" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>附則</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>この規程は、令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="93">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A1:E1"/>
@@ -1290,6 +1297,8 @@
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A128:E128"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
@@ -1298,29 +1307,33 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A131:E131"/>
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A115:E115"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
     <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A96:E96"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A40:E40"/>
@@ -1333,16 +1346,12 @@
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
@@ -1351,11 +1360,9 @@
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
@@ -1364,17 +1371,18 @@
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A116:E116"/>
     <mergeCell ref="A126:E126"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -33,6 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +43,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +107,21 @@
       <b val="1"/>
       <sz val="20"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11.5"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -141,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -221,6 +237,21 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16309,6 +16340,599 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>苦情（相談）記録表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No.　　　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>受付日</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>受付方法（電話・対面・書面・代理等）</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>苦情（相談）者氏名／続柄</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>対象利用者名</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>受付職員名</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>苦情（相談）区分
+（サービス内容・職員対応・安全衛生・事務手続・その他）</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>発生日時・場所</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>緊急度（高・中・低）</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>1．苦情（相談）内容の詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>（事実関係、発生状況、当事者の言動、経緯などを可能な限り具体的に記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>2．利用者・家族の意向／感情の状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>（怒り・不安・困惑など、受け止め方を含めて明確に記述）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="23" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>3．初期対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>（受付時の対応、説明内容、緊急対応の要否、関係者（管理者・ケアマネジャー・主治医等）への連絡など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="23" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>4．関係職員への聞き取り記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>（事実確認内容、職員の説明、第三者の証言等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="23" t="n"/>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="23" t="n"/>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="23" t="n"/>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>5．事業所としての分析・判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>（原因分析、再発要因、責任区分の検討など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="23" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="23" t="n"/>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="23" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="23" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="33" t="inlineStr">
+        <is>
+          <t>6．対応内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>（是正措置、改善策、訪問調整、担当変更、職員指導内容など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="23" t="n"/>
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="23" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="23" t="n"/>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="23" t="n"/>
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>7．利用者・家族への説明／同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
+        <is>
+          <t>（説明日、説明者、理解状況、同意の有無）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="23" t="n"/>
+      <c r="B55" s="23" t="n"/>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="23" t="n"/>
+      <c r="E55" s="23" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="23" t="n"/>
+      <c r="B56" s="23" t="n"/>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="23" t="n"/>
+      <c r="B57" s="23" t="n"/>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="23" t="n"/>
+      <c r="E57" s="23" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>8．再発防止策</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>（教育、マニュアル改訂、業務フロー改善等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="23" t="n"/>
+      <c r="B61" s="23" t="n"/>
+      <c r="C61" s="23" t="n"/>
+      <c r="D61" s="23" t="n"/>
+      <c r="E61" s="23" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="23" t="n"/>
+      <c r="B62" s="23" t="n"/>
+      <c r="C62" s="23" t="n"/>
+      <c r="D62" s="23" t="n"/>
+      <c r="E62" s="23" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="23" t="n"/>
+      <c r="B63" s="23" t="n"/>
+      <c r="C63" s="23" t="n"/>
+      <c r="D63" s="23" t="n"/>
+      <c r="E63" s="23" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>9．フォローアップ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>（後日の確認状況、苦情の収束状況、残課題、対応完了日など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="23" t="n"/>
+      <c r="B67" s="23" t="n"/>
+      <c r="C67" s="23" t="n"/>
+      <c r="D67" s="23" t="n"/>
+      <c r="E67" s="23" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="23" t="n"/>
+      <c r="B68" s="23" t="n"/>
+      <c r="C68" s="23" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="23" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="23" t="n"/>
+      <c r="B69" s="23" t="n"/>
+      <c r="C69" s="23" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="23" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>10．管理者コメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>（総括、必要な追加措置、大阪市・国保連への報告の要否、虐待・事故に該当する場合の通報・報告など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="23" t="n"/>
+      <c r="B73" s="23" t="n"/>
+      <c r="C73" s="23" t="n"/>
+      <c r="D73" s="23" t="n"/>
+      <c r="E73" s="23" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="23" t="n"/>
+      <c r="B74" s="23" t="n"/>
+      <c r="C74" s="23" t="n"/>
+      <c r="D74" s="23" t="n"/>
+      <c r="E74" s="23" t="n"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="23" t="n"/>
+      <c r="B75" s="23" t="n"/>
+      <c r="C75" s="23" t="n"/>
+      <c r="D75" s="23" t="n"/>
+      <c r="E75" s="23" t="n"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>【最終確認】</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="26" t="inlineStr">
+        <is>
+          <t>管理者署名：</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>確認日：　　　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="9" t="n"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="34" t="inlineStr">
+        <is>
+          <t>※本記録表は対応完了日から5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A43:E45"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A67:E69"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E26"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A49:E51"/>
+    <mergeCell ref="A30:E32"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A73:E75"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A61:E63"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A16:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A55:E57"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A36:E39"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B10:E10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="33" min="0" max="16383" man="1"/>
+    <brk id="58" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -32,8 +32,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15586,6 +15587,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>セクシャルハラスメント防止指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>1．目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>本指針は、株式会社dhpケアマネジメント　いいかいごにおける訪問介護事業の運営において、利用者・家族・職員すべてが安心して関われる環境を保持するため、セクシャルハラスメント（以下「セクハラ」という。）の防止、早期発見、適切な対応を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2．定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>セクハラとは、意に反する性的な言動により、相手に不快感・苦痛・屈辱を与え、就労環境やサービス提供環境を害する行為を指す。相手の性的指向・性自認にかかわらず、同性に対する言動も含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>3．適用範囲</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>全職員（登録ヘルパーを含む）および関係者に適用し、職員から利用者・家族への行為、職員間の行為、利用者・家族から職員への行為を対象とする。利用者宅、移動中、事業所内など業務を行うすべての場所を含む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="8" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>4．基本方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>当社はセクハラを一切容認せず、適切な距離感と報告体制を徹底する。相談・報告をしたことや調査に協力したことを理由に、不利益な取扱いは行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>5．職員の行動基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>身体介助時の声かけ・必要最小限の接触・私的交流の禁止（個人の連絡先の交換、業務外での面会等）などを徹底する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>6．利用者・家族からの不適切行為への対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>速やかに管理者へ報告し、ケアマネジャー等と連携し職員保護を最優先に対応する。具体的な手順は「利用者等からのハラスメント防止・対応規程」及び同マニュアルによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>7．相談・報告窓口</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>管理者（生田 友哉）・サービス提供責任者・代表取締役へ相談可能。匿名相談可。相談者のプライバシーは厳守する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>8．調査および対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>迅速かつ公平に調査し、必要な処分（「懲戒規程」による）・被害者への配慮・再発防止策を行う。職員から利用者への行為で虐待に該当するおそれがある場合は、「虐待防止に関する指針」に基づき大阪市へ通報する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>9．教育・研修</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>セクハラ防止研修・距離感指導などを入社時及び年1回以上継続実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="8" customHeight="1"/>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>10．記録と保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>相談・報告・対応記録は適切に管理し、5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="8" customHeight="1"/>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>11．見直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>必要に応じて改訂する。関連規程：「ハラスメント防止規程」「職場におけるハラスメントの防止に関する規定」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="8" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>本指針は、令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A44:E44"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　セクシャルハラスメント防止指針</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16340,7 +16626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -23,18 +23,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="育児・介護休業規程" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退職規程" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策指針" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束廃止に関する指針" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情対応マニュアル" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント防止規程" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職場ハラスメント防止規定" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症対策委員会 運営要綱" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束廃止に関する指針" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情対応マニュアル" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント防止規程" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職場ハラスメント防止規定" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -226,10 +227,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7284,6 +7288,1150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E142"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>感染症対策委員会
+運営要綱・委員会資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>1．目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>本資料は、株式会社dhpケアマネジメント　いいかいごにおける感染症対策委員会の設置・運営体制を明確にし、平常時および感染症発生時において適切な感染対策を推進することを目的とする。感染症対策指針、業務継続計画（BCP）等と連動して、委員会の役割・構成・年間活動計画を整理するものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="10" customHeight="1"/>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2．関連規程・位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>本委員会は、以下の社内規程・指針に基づき設置・運営する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染症対策指針</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・安全衛生規程</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染症業務継続計画（BCP）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・虐待防止委員会等、他委員会との連携</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>また、感染症対策委員会は他の委員会とは独立した組織として位置づけ、感染症に関する意思決定および現場支援を専門的に担う。なお、他の会議体と一体的に開催することを妨げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="10" customHeight="1"/>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>3．組織体制</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>代表取締役</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>感染症対策委員会
+（委員長：管理者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>│</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>副委員長
+（サービス提供責任者）</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>委員
+（看護職・ヘルパー代表）</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>委員
+（事務・総務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>顧問（主治医・外部専門家・保健所等：必要に応じて）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>4．委員構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>事業所の規模に応じて、兼務・省略・追加を行ってよい。委員の氏名は別紙1「委員名簿」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>役職</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>所属・職種</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>備考（役割のポイント）</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>委員長</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>感染症対策全体の統括・最終判断・行政報告の責任者</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>副委員長</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>サービス提供責任者</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>現場調整、職員への周知・指導、委員会の事務実務の統括</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="n"/>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>看護職員（外部看護師等）</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>医療的知見の提供、標準予防策・PPEの指導</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="n"/>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>ヘルパー代表</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>現場の実情・課題の吸い上げ、現場へのフィードバック</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>事務・総務担当</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>記録整備、研修・訓練の資料管理、行政書類との整合確認</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>研修・教育担当</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>感染対策研修の企画・運営、参加状況・欠席者対応の管理</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>顧問（任意）</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>主治医・外部専門家等</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>専門的助言、重症例発生時の医療連携の調整</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="n"/>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>※人員が限られる場合は、委員長＝管理者、副委員長＝サービス提供責任者、ヘルパー代表・事務担当の最低3〜4名体制を基本とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="10" customHeight="1"/>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>5．委員会の開催（頻度・開催方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>（1）定例開催</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・おおむね6か月に1回以上（6月・11月）開催する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・主に平常時の感染症対策の確認、研修・訓練の計画と振り返り、感染発生状況の共有を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="8" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>（2）臨時開催</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染症の集団発生や重大事案が発生した場合、必要に応じて委員長の判断で臨時開催する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・事案の経過整理、対応内容の検証、再発防止策の策定を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>（3）開催方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・原則は対面開催とするが、状況に応じてオンライン（テレビ電話装置等）との併用も可とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>6．年間活動計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>感染症対策委員会として、以下の年間活動計画を立案・実施する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>回次</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>予定月</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>主な議題</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="n"/>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="64" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>第1回</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>前年度の感染症発生状況の振り返り／今年度の感染症対策方針・年間研修計画の確認／夏季の感染症（食中毒含む）対策／標準予防策の実地確認</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n"/>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>研修・訓練（6月）と連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>第2回</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="C75" s="22" t="inlineStr">
+        <is>
+          <t>インフルエンザ・ノロウイルス等の流行期に向けた対策／ワクチン接種の状況確認／年度総括／BCP・指針の見直し案の検討／次年度計画素案の確認</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="n"/>
+      <c r="E75" s="22" t="inlineStr">
+        <is>
+          <t>研修・訓練（11月）と連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>臨時</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>集団発生・重大事案の検証と再発防止策</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="n"/>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>委員長が招集</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>7．委員の役割（詳細）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>（1）委員長（管理者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染症対策全体の統括および最終責任者。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・委員会の招集、議題の決定、行政への報告要否の判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・重大な感染事案発生時の対外的窓口（行政・医療機関・家族等）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>（2）副委員長（サービス提供責任者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・委員長を補佐し、現場との橋渡しを行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・全ヘルパーへの周知、個別ケースの情報収集、現場改善の実務を担当。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="8" customHeight="1"/>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>（3）看護職員</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・標準予防策、PPEの使用方法等の専門的指導。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・利用者・職員の健康状態の把握に関する助言。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="8" customHeight="1"/>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>（4）ヘルパー代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・現場での実際の困りごと・ヒヤリハットの共有。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・委員会での決定事項を現場へフィードバック。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>（5）事務・総務担当</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・議事録の作成、感染症研修・訓練記録との紐づけ、帳票類の保管。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・委員会資料の準備および保存（5年間）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>（6）研修・教育担当</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・感染対策研修の企画・運営。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・欠席者へのフォロー（資料配布・別日実施・動画視聴等）の管理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="8" customHeight="1"/>
+    <row r="104" ht="26" customHeight="1">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>8．主な協議事項（チェックリスト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 事業所内における感染症発生状況の把握（利用者・職員）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 標準予防策（手指衛生、PPE、環境整備）の実施状況と課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 感染症対策指針・BCPの運用状況と見直し</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 感染対策研修の実施状況、欠席者への対応状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 感染症訓練（机上訓練・実地訓練）の計画と実施結果の検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 行政・保健所からの通知・最新情報の共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　□ 重大事案（集団発生・クラスター等）の検証と再発防止策</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="8" customHeight="1"/>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>9．記録・保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・委員会ごとに議事録を作成し、出席者を明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・議事録には、協議内容、決定事項、次回までの宿題・担当者を整理して記載する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・議事録、年間計画、研修・訓練報告書等は相互に紐づけてファイリングし、5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・委員会の結果は、全職員（登録ヘルパーを含む）に周知する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="8" customHeight="1"/>
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="16" t="inlineStr">
+        <is>
+          <t>10．別紙様式</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　別紙1：感染症対策委員会　委員名簿（本資料末尾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　別紙2：感染症対策委員会　年間開催計画表</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　別紙3：感染症対策委員会　議事録様式</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　別紙4：感染症対策研修実施報告書</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　別紙5：感染症訓練実施結果報告書</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="8" customHeight="1"/>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>【最終確認】</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="26" t="inlineStr">
+        <is>
+          <t>管理者署名：</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="9" t="n"/>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="26" t="inlineStr">
+        <is>
+          <t>確認日：</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>別紙1　感染症対策委員会　委員名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="24" t="inlineStr">
+        <is>
+          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="24" t="inlineStr">
+        <is>
+          <t>令和8年2月1日現在</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="10" customHeight="1"/>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>役職</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="n"/>
+      <c r="C133" s="20" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="D133" s="20" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="E133" s="21" t="n"/>
+    </row>
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>委員長（管理者）</t>
+        </is>
+      </c>
+      <c r="B134" s="21" t="n"/>
+      <c r="C134" s="22" t="inlineStr">
+        <is>
+          <t>生田 友哉</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="inlineStr">
+        <is>
+          <t>感染症対策全体の統括・研修・教育担当を兼務</t>
+        </is>
+      </c>
+      <c r="E134" s="23" t="n"/>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>副委員長（サービス提供責任者）</t>
+        </is>
+      </c>
+      <c r="B135" s="21" t="n"/>
+      <c r="C135" s="22" t="inlineStr">
+        <is>
+          <t>岩谷</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="inlineStr">
+        <is>
+          <t>現場調整・周知・実務統括</t>
+        </is>
+      </c>
+      <c r="E135" s="23" t="n"/>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>看護職委員</t>
+        </is>
+      </c>
+      <c r="B136" s="21" t="n"/>
+      <c r="C136" s="22" t="inlineStr">
+        <is>
+          <t>松本</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>医療的助言・PPE指導</t>
+        </is>
+      </c>
+      <c r="E136" s="23" t="n"/>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>ヘルパー代表</t>
+        </is>
+      </c>
+      <c r="B137" s="21" t="n"/>
+      <c r="C137" s="22" t="inlineStr">
+        <is>
+          <t>松川</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="inlineStr">
+        <is>
+          <t>現場情報共有・フィードバック</t>
+        </is>
+      </c>
+      <c r="E137" s="23" t="n"/>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>事務・総務</t>
+        </is>
+      </c>
+      <c r="B138" s="21" t="n"/>
+      <c r="C138" s="22" t="inlineStr">
+        <is>
+          <t>鳥羽</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>記録整備・行政書類確認</t>
+        </is>
+      </c>
+      <c r="E138" s="23" t="n"/>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>研修・教育担当</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="n"/>
+      <c r="C139" s="22" t="inlineStr">
+        <is>
+          <t>生田 友哉（兼務）</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="inlineStr">
+        <is>
+          <t>感染研修の企画・欠席者フォロー</t>
+        </is>
+      </c>
+      <c r="E139" s="23" t="n"/>
+    </row>
+    <row r="140" ht="8" customHeight="1"/>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>本資料は、令和8年2月1日から適用する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="107">
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="D135:E135"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A113:E113"/>
+    <mergeCell ref="D134:E134"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A100:E100"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="D138:E138"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D139:E139"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A86:E86"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="D133:E133"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="D136:E136"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="D137:E137"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　感染症対策委員会 運営要綱</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="77" min="0" max="16383" man="1"/>
+    <brk id="128" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7338,7 +8486,7 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>来歴管理表</t>
         </is>
@@ -7834,7 +8982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8621,7 +9769,7 @@
       <c r="C147" s="9" t="n"/>
     </row>
     <row r="148" ht="30" customHeight="1">
-      <c r="A148" s="27" t="inlineStr">
+      <c r="A148" s="28" t="inlineStr">
         <is>
           <t>事故対応フローチャート</t>
         </is>
@@ -8942,7 +10090,689 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E128"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1"/>
+    <row r="3" ht="24" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1"/>
+    <row r="7" ht="24" customHeight="1"/>
+    <row r="8" ht="24" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1"/>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>就業規則</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1"/>
+    <row r="16" ht="24" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>施行　令和8年2月1日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>第1章　総則</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>（目的）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>第1条　本規則は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）に勤務する従業員の就業に関する基本事項を定め、労務管理の適正化、従業員の生活の安定および業務の円滑な運営を図ることを目的とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>（定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>第2条　本規則における用語の定義は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>1　「従業員」とは、会社に雇用される者をいう（有期・無期、所定労働時間の長短を問わない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2　「管理監督者」とは、労働基準法第41条に定める者をいう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>3　その他の用語の詳細は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>（適用範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>第3条　本規則は、会社に雇用されるすべての従業員に適用する。管理監督者等の一部については法令に従い適用除外とし、詳細は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>（周知・改廃）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>第4条　本規則および各規程は、社内掲示・イントラネット等により周知する。改廃は労働基準法に基づく手続（意見聴取・届出等）を経て行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="8" customHeight="1"/>
+    <row r="42" ht="8" customHeight="1">
+      <c r="A42" s="8" t="inlineStr"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="10" customHeight="1"/>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>第2章　勤務</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>（勤務体制：1か月単位の変形労働時間制）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>第5条　会社は一か月単位の変形労働時間制を採用する。対象者、計算期間、各日・各週の所定労働時間の決定方法、勤務割表の作成・通知方法その他の詳細は「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>（所定労働時間・休憩）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>第6条　所定労働時間は1日8時間とする。休憩は原則として6時間を超える勤務の場合1時間、夜勤勤務の場合2時間とし、取得方法は「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>（休日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>第7条　休日は月10日を原則とし、このうち法定休日は会社の定める日とする（4週間を通じ少なくとも4日）。振替休日・代休の取扱いは「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>（時間外・休日・深夜労働）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>第8条　業務上必要がある場合、会社は36協定に基づき時間外労働および休日労働を命じることがある。22時から翌5時までの労働については法定割増賃金を支給する。手当の区分・額等は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1"/>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>（出退勤記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>第9条　従業員は会社の指定する方法により出退勤を記録しなければならない。記録方法、訂正手続等は「勤務管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="8" customHeight="1"/>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>（配置転換・出向・転勤）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>第10条　会社は業務上の必要により配置転換、出向、転勤等を命ずることがある。手続・配慮事項は「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="8" customHeight="1"/>
+    <row r="63" ht="8" customHeight="1">
+      <c r="A63" s="8" t="inlineStr"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>第3章　服務</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>（服務規律）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>第11条　従業員は、法令、本規則および各種規程並びに会社の指示に従い、誠実かつ公正に職務を遂行し、職場秩序を維持しなければならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="8" customHeight="1"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>（ハラスメントの禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>第12条　従業員は、セクシュアルハラスメント、パワーハラスメントその他一切のハラスメント行為を行ってはならない。防止体制、相談・調査・再発防止等は「ハラスメント防止規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="8" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>（秘密情報・個人情報の保護）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>第13条　従業員は、在職中および退職後において、業務上知り得た秘密情報・個人情報を漏えいしてはならない。範囲、管理措置、違反時の取扱いは「情報管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>（競業避止・利益相反）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="48" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>第14条　会社が指定する者は、在職中および退職後一定期間、会社の指定する地域において競業行為を行ってはならない。兼業・副業、利益相反の管理は「競業避止規程」および「人事管理規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="8" customHeight="1">
+      <c r="A78" s="8" t="inlineStr"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+    </row>
+    <row r="79" ht="10" customHeight="1"/>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>第4章　休暇・休業</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>（年次有給休暇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>第15条　従業員には労働基準法に基づく年次有給休暇を付与する。付与日、計画的付与、時季変更、半日・時間単位付与等は「休暇規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="8" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>（特別休暇・法定休業）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>第16条　慶弔休暇、病気休暇、産前産後休暇、育児休業、介護休業、子の看護等休暇等の付与・手続は「休暇規程」および「育児・介護休業規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="8" customHeight="1"/>
+    <row r="87" ht="8" customHeight="1">
+      <c r="A87" s="8" t="inlineStr"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+    </row>
+    <row r="88" ht="10" customHeight="1"/>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>第5章　賃金</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>（賃金の構成・決定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>第17条　賃金は、基本給、諸手当、賞与その他会社の定めるものから構成する。種類、額、計算・支給方法、欠勤・遅刻等の控除、割増賃金の算定は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="8" customHeight="1"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>（締切日・支払日・支払方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>第18条　賃金の締切日は毎月末日とし、翌月27日に支払う。支払日が土曜日、日曜日または祝日に当たるときは、直前の平日に繰り上げて支払う。支払方法は、従業員の同意を得て、従業員が指定する銀行口座への振込による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>（賃金控除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>第19条　法令に基づく控除のほか、会社と労使協定を締結した場合に限り賃金控除を行う。控除項目等は「賃金規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="8" customHeight="1">
+      <c r="A99" s="8" t="inlineStr"/>
+      <c r="B99" s="9" t="n"/>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="9" t="n"/>
+      <c r="E99" s="9" t="n"/>
+    </row>
+    <row r="100" ht="10" customHeight="1"/>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>第6章　安全衛生</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>（安全衛生管理）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="48" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>第20条　会社は労働安全衛生法その他関係法令に基づき、従業員の安全と健康の確保に努める。従業員は会社の措置に協力しなければならない。体制、健康診断、就業上の措置等は「安全衛生規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="8" customHeight="1"/>
+    <row r="105" ht="8" customHeight="1">
+      <c r="A105" s="8" t="inlineStr"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+    </row>
+    <row r="106" ht="10" customHeight="1"/>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>第7章　懲戒</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>（懲戒の基本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>第21条　従業員が服務規律に違反した場合、情状に応じて懲戒処分を行うことがある。懲戒の種類、事由、手続、弁明の機会付与等は「懲戒規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2　懲戒により減給を命ずる場合、1回の額は平均賃金の1日分の半額を超えず、総額は1賃金支払期における賃金総額の1/10を超えない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="8" customHeight="1">
+      <c r="A112" s="8" t="inlineStr"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="10" customHeight="1"/>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>第8章　退職・解雇</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>（退職）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="48" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>第22条　従業員が自己都合により退職する場合は、円滑な引継ぎのため、原則として30日前までに、書面（電磁的方法を含む）にて会社に届け出るよう努めなければならない。定年、退職時の有給休暇の取扱い、業務引継、貸与物の返還等は「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="8" customHeight="1"/>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>（解雇）</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>第23条　会社は、業務遂行困難、職務不良、服務規律違反その他やむを得ない事由がある場合に解雇を行うことがある。解雇事由、手続、予告・予告手当、整理解雇の要件等は「退職規程」による。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>（退職時証明）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>第24条　従業員が退職に際し、在職期間・業務の種類・地位・賃金・事由等の退職証明書の交付を請求したときは、法令に従い遅滞なく交付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="8" customHeight="1"/>
+    <row r="124" ht="8" customHeight="1">
+      <c r="A124" s="8" t="inlineStr"/>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="9" t="n"/>
+    </row>
+    <row r="125" ht="10" customHeight="1"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>第25条　本規則に定めのない事項は、労働基準法その他関係法令および会社の各規程による。制定・改廃の履歴は「規程管理台帳」に記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>第26条　本規則は令和8年2月1日から施行する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="74">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A114:E114"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A122:E122"/>
+    <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A121:E121"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　就業規則</oddHeader>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9840,689 +11670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E128"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1"/>
-    <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1"/>
-    <row r="8" ht="24" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1"/>
-    <row r="10" ht="24" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1"/>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>就業規則</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1"/>
-    <row r="15" ht="24" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1"/>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
-    <row r="20" ht="24" customHeight="1"/>
-    <row r="21" ht="24" customHeight="1"/>
-    <row r="22" ht="24" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>施行　令和8年2月1日</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>第1章　総則</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>（目的）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>第1条　本規則は、株式会社dhpケアマネジメント　いいかいご（以下「会社」という。）に勤務する従業員の就業に関する基本事項を定め、労務管理の適正化、従業員の生活の安定および業務の円滑な運営を図ることを目的とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>（定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>第2条　本規則における用語の定義は次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>1　「従業員」とは、会社に雇用される者をいう（有期・無期、所定労働時間の長短を問わない）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>2　「管理監督者」とは、労働基準法第41条に定める者をいう。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>3　その他の用語の詳細は「人事管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>（適用範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>第3条　本規則は、会社に雇用されるすべての従業員に適用する。管理監督者等の一部については法令に従い適用除外とし、詳細は「人事管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="8" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>（周知・改廃）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>第4条　本規則および各規程は、社内掲示・イントラネット等により周知する。改廃は労働基準法に基づく手続（意見聴取・届出等）を経て行う。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="8" customHeight="1">
-      <c r="A42" s="8" t="inlineStr"/>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-    </row>
-    <row r="43" ht="10" customHeight="1"/>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>第2章　勤務</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>（勤務体制：1か月単位の変形労働時間制）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>第5条　会社は一か月単位の変形労働時間制を採用する。対象者、計算期間、各日・各週の所定労働時間の決定方法、勤務割表の作成・通知方法その他の詳細は「勤務管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>（所定労働時間・休憩）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>第6条　所定労働時間は1日8時間とする。休憩は原則として6時間を超える勤務の場合1時間、夜勤勤務の場合2時間とし、取得方法は「勤務管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>（休日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>第7条　休日は月10日を原則とし、このうち法定休日は会社の定める日とする（4週間を通じ少なくとも4日）。振替休日・代休の取扱いは「勤務管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>（時間外・休日・深夜労働）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>第8条　業務上必要がある場合、会社は36協定に基づき時間外労働および休日労働を命じることがある。22時から翌5時までの労働については法定割増賃金を支給する。手当の区分・額等は「賃金規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="8" customHeight="1"/>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>（出退勤記録）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>第9条　従業員は会社の指定する方法により出退勤を記録しなければならない。記録方法、訂正手続等は「勤務管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="8" customHeight="1"/>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>（配置転換・出向・転勤）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>第10条　会社は業務上の必要により配置転換、出向、転勤等を命ずることがある。手続・配慮事項は「人事管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="8" customHeight="1">
-      <c r="A63" s="8" t="inlineStr"/>
-      <c r="B63" s="9" t="n"/>
-      <c r="C63" s="9" t="n"/>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="9" t="n"/>
-    </row>
-    <row r="64" ht="10" customHeight="1"/>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>第3章　服務</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>（服務規律）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>第11条　従業員は、法令、本規則および各種規程並びに会社の指示に従い、誠実かつ公正に職務を遂行し、職場秩序を維持しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="8" customHeight="1"/>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>（ハラスメントの禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>第12条　従業員は、セクシュアルハラスメント、パワーハラスメントその他一切のハラスメント行為を行ってはならない。防止体制、相談・調査・再発防止等は「ハラスメント防止規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="8" customHeight="1"/>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>（秘密情報・個人情報の保護）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>第13条　従業員は、在職中および退職後において、業務上知り得た秘密情報・個人情報を漏えいしてはならない。範囲、管理措置、違反時の取扱いは「情報管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="8" customHeight="1"/>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>（競業避止・利益相反）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="48" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>第14条　会社が指定する者は、在職中および退職後一定期間、会社の指定する地域において競業行為を行ってはならない。兼業・副業、利益相反の管理は「競業避止規程」および「人事管理規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="8" customHeight="1"/>
-    <row r="78" ht="8" customHeight="1">
-      <c r="A78" s="8" t="inlineStr"/>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="9" t="n"/>
-    </row>
-    <row r="79" ht="10" customHeight="1"/>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>第4章　休暇・休業</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>（年次有給休暇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>第15条　従業員には労働基準法に基づく年次有給休暇を付与する。付与日、計画的付与、時季変更、半日・時間単位付与等は「休暇規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>（特別休暇・法定休業）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>第16条　慶弔休暇、病気休暇、産前産後休暇、育児休業、介護休業、子の看護等休暇等の付与・手続は「休暇規程」および「育児・介護休業規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="8" customHeight="1">
-      <c r="A87" s="8" t="inlineStr"/>
-      <c r="B87" s="9" t="n"/>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="9" t="n"/>
-    </row>
-    <row r="88" ht="10" customHeight="1"/>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>第5章　賃金</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>（賃金の構成・決定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>第17条　賃金は、基本給、諸手当、賞与その他会社の定めるものから構成する。種類、額、計算・支給方法、欠勤・遅刻等の控除、割増賃金の算定は「賃金規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>（締切日・支払日・支払方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>第18条　賃金の締切日は毎月末日とし、翌月27日に支払う。支払日が土曜日、日曜日または祝日に当たるときは、直前の平日に繰り上げて支払う。支払方法は、従業員の同意を得て、従業員が指定する銀行口座への振込による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="8" customHeight="1"/>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>（賃金控除）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>第19条　法令に基づく控除のほか、会社と労使協定を締結した場合に限り賃金控除を行う。控除項目等は「賃金規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="8" customHeight="1"/>
-    <row r="99" ht="8" customHeight="1">
-      <c r="A99" s="8" t="inlineStr"/>
-      <c r="B99" s="9" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-    </row>
-    <row r="100" ht="10" customHeight="1"/>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>第6章　安全衛生</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>（安全衛生管理）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="48" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>第20条　会社は労働安全衛生法その他関係法令に基づき、従業員の安全と健康の確保に努める。従業員は会社の措置に協力しなければならない。体制、健康診断、就業上の措置等は「安全衛生規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="8" customHeight="1"/>
-    <row r="105" ht="8" customHeight="1">
-      <c r="A105" s="8" t="inlineStr"/>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="9" t="n"/>
-      <c r="E105" s="9" t="n"/>
-    </row>
-    <row r="106" ht="10" customHeight="1"/>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>第7章　懲戒</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>（懲戒の基本）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>第21条　従業員が服務規律に違反した場合、情状に応じて懲戒処分を行うことがある。懲戒の種類、事由、手続、弁明の機会付与等は「懲戒規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>2　懲戒により減給を命ずる場合、1回の額は平均賃金の1日分の半額を超えず、総額は1賃金支払期における賃金総額の1/10を超えない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="8" customHeight="1">
-      <c r="A112" s="8" t="inlineStr"/>
-      <c r="B112" s="9" t="n"/>
-      <c r="C112" s="9" t="n"/>
-      <c r="D112" s="9" t="n"/>
-      <c r="E112" s="9" t="n"/>
-    </row>
-    <row r="113" ht="10" customHeight="1"/>
-    <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>第8章　退職・解雇</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>（退職）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="48" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>第22条　従業員が自己都合により退職する場合は、円滑な引継ぎのため、原則として30日前までに、書面（電磁的方法を含む）にて会社に届け出るよう努めなければならない。定年、退職時の有給休暇の取扱い、業務引継、貸与物の返還等は「退職規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="8" customHeight="1"/>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>（解雇）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="32" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>第23条　会社は、業務遂行困難、職務不良、服務規律違反その他やむを得ない事由がある場合に解雇を行うことがある。解雇事由、手続、予告・予告手当、整理解雇の要件等は「退職規程」による。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="8" customHeight="1"/>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t>（退職時証明）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="32" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>第24条　従業員が退職に際し、在職期間・業務の種類・地位・賃金・事由等の退職証明書の交付を請求したときは、法令に従い遅滞なく交付する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="8" customHeight="1"/>
-    <row r="124" ht="8" customHeight="1">
-      <c r="A124" s="8" t="inlineStr"/>
-      <c r="B124" s="9" t="n"/>
-      <c r="C124" s="9" t="n"/>
-      <c r="D124" s="9" t="n"/>
-      <c r="E124" s="9" t="n"/>
-    </row>
-    <row r="125" ht="10" customHeight="1"/>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>附則</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>第25条　本規則に定めのない事項は、労働基準法その他関係法令および会社の各規程による。制定・改廃の履歴は「規程管理台帳」に記録する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>第26条　本規則は令和8年2月1日から施行する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A82:E82"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A119:E119"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A124:E124"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A127:E127"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A76:E76"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A122:E122"/>
-    <mergeCell ref="A91:E91"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="A96:E96"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A112:E112"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;9 株式会社dhpケアマネジメント　いいかいご　就業規則</oddHeader>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11281,7 +12429,7 @@
       <c r="C136" s="9" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="27" t="inlineStr">
+      <c r="A137" s="28" t="inlineStr">
         <is>
           <t>苦情対応フローチャート（訪問介護事業所）</t>
         </is>
@@ -11301,7 +12449,7 @@
           <t>① 苦情・相談の受付</t>
         </is>
       </c>
-      <c r="C140" s="28" t="inlineStr">
+      <c r="C140" s="29" t="inlineStr">
         <is>
           <t>電話／対面／書面／代理で受理
 傾聴し、感情を受け止める
@@ -11322,7 +12470,7 @@
           <t>② 初期情報の記録</t>
         </is>
       </c>
-      <c r="C142" s="28" t="inlineStr">
+      <c r="C142" s="29" t="inlineStr">
         <is>
           <t>苦情（相談）記録表へ記入
 内容・緊急度・対象利用者を整理
@@ -11343,7 +12491,7 @@
           <t>③ 緊急度判定</t>
         </is>
       </c>
-      <c r="C144" s="28" t="inlineStr">
+      <c r="C144" s="29" t="inlineStr">
         <is>
           <t>【高】生命・安全に係る／重大クレーム
 【中】早急に対応が必要
@@ -11364,7 +12512,7 @@
           <t>④ 初期対応の実施</t>
         </is>
       </c>
-      <c r="C146" s="28" t="inlineStr">
+      <c r="C146" s="29" t="inlineStr">
         <is>
           <t>担当交代、訪問調整、緊急措置
 必要に応じて主治医・ケアマネへ連絡</t>
@@ -11384,7 +12532,7 @@
           <t>⑤ 事実確認</t>
         </is>
       </c>
-      <c r="C148" s="28" t="inlineStr">
+      <c r="C148" s="29" t="inlineStr">
         <is>
           <t>関係職員への聞き取り
 訪問記録・ケア記録との照合
@@ -11405,7 +12553,7 @@
           <t>⑥ 分析・判断</t>
         </is>
       </c>
-      <c r="C150" s="28" t="inlineStr">
+      <c r="C150" s="29" t="inlineStr">
         <is>
           <t>原因の特定（ヒューマンエラー／体制要因など）
 事業所としての判断と改善方針決定</t>
@@ -11425,7 +12573,7 @@
           <t>⑦ 利用者・家族への説明</t>
         </is>
       </c>
-      <c r="C152" s="28" t="inlineStr">
+      <c r="C152" s="29" t="inlineStr">
         <is>
           <t>事実確認結果と改善策を説明
 理解状況と同意の有無を記録</t>
@@ -11445,7 +12593,7 @@
           <t>⑧ 是正措置・改善策の実行</t>
         </is>
       </c>
-      <c r="C154" s="28" t="inlineStr">
+      <c r="C154" s="29" t="inlineStr">
         <is>
           <t>担当者変更／介助方法改善／研修の実施
 再発防止策を組織として実行</t>
@@ -11465,7 +12613,7 @@
           <t>⑨ フォローアップ</t>
         </is>
       </c>
-      <c r="C156" s="28" t="inlineStr">
+      <c r="C156" s="29" t="inlineStr">
         <is>
           <t>後日、利用者へ確認の連絡
 収束状況を記録、必要に応じて再対応</t>
@@ -11485,7 +12633,7 @@
           <t>⑩ 終結・保存</t>
         </is>
       </c>
-      <c r="C158" s="28" t="inlineStr">
+      <c r="C158" s="29" t="inlineStr">
         <is>
           <t>管理者が最終確認
 苦情（相談）記録表を保存（5年）
@@ -11622,7 +12770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12453,7 +13601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12488,7 +13636,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>職場におけるハラスメントの
 防止に関する規定</t>
@@ -12959,7 +14107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13455,7 +14603,7 @@
     </row>
     <row r="95" ht="8" customHeight="1"/>
     <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="25" t="inlineStr">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>相談苦情への対応の流れ（フローチャート）</t>
         </is>
@@ -13690,7 +14838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13725,7 +14873,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応規程</t>
@@ -14694,7 +15842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14729,7 +15877,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応マニュアル</t>
@@ -15581,7 +16729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15866,7 +17014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16626,7 +17774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16643,28 +17791,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>苦情（相談）記録表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">No.　　　　　</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>受付日</t>
         </is>
@@ -16675,7 +17823,7 @@
       <c r="E5" s="23" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>受付方法（電話・対面・書面・代理等）</t>
         </is>
@@ -16686,7 +17834,7 @@
       <c r="E6" s="23" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>苦情（相談）者氏名／続柄</t>
         </is>
@@ -16697,7 +17845,7 @@
       <c r="E7" s="23" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>対象利用者名</t>
         </is>
@@ -16708,7 +17856,7 @@
       <c r="E8" s="23" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>受付職員名</t>
         </is>
@@ -16719,7 +17867,7 @@
       <c r="E9" s="23" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>苦情（相談）区分
 （サービス内容・職員対応・安全衛生・事務手続・その他）</t>
@@ -16731,7 +17879,7 @@
       <c r="E10" s="23" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>発生日時・場所</t>
         </is>
@@ -16742,7 +17890,7 @@
       <c r="E11" s="23" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>緊急度（高・中・低）</t>
         </is>
@@ -16753,14 +17901,14 @@
       <c r="E12" s="23" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>1．苦情（相談）内容の詳細</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>（事実関係、発生状況、当事者の言動、経緯などを可能な限り具体的に記録）</t>
         </is>
@@ -16802,14 +17950,14 @@
       <c r="E20" s="23" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>2．利用者・家族の意向／感情の状況</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>（怒り・不安・困惑など、受け止め方を含めて明確に記述）</t>
         </is>
@@ -16837,14 +17985,14 @@
       <c r="E26" s="23" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>3．初期対応</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>（受付時の対応、説明内容、緊急対応の要否、関係者（管理者・ケアマネジャー・主治医等）への連絡など）</t>
         </is>
@@ -16872,14 +18020,14 @@
       <c r="E32" s="23" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>4．関係職員への聞き取り記録</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>（事実確認内容、職員の説明、第三者の証言等）</t>
         </is>
@@ -16914,14 +18062,14 @@
       <c r="E39" s="23" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="33" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>5．事業所としての分析・判断</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>（原因分析、再発要因、責任区分の検討など）</t>
         </is>
@@ -16949,14 +18097,14 @@
       <c r="E45" s="23" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="33" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>6．対応内容</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>（是正措置、改善策、訪問調整、担当変更、職員指導内容など）</t>
         </is>
@@ -16984,14 +18132,14 @@
       <c r="E51" s="23" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="33" t="inlineStr">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>7．利用者・家族への説明／同意</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>（説明日、説明者、理解状況、同意の有無）</t>
         </is>
@@ -17019,14 +18167,14 @@
       <c r="E57" s="23" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="33" t="inlineStr">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>8．再発防止策</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="34" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>（教育、マニュアル改訂、業務フロー改善等）</t>
         </is>
@@ -17054,14 +18202,14 @@
       <c r="E63" s="23" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="33" t="inlineStr">
+      <c r="A65" s="34" t="inlineStr">
         <is>
           <t>9．フォローアップ記録</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="34" t="inlineStr">
+      <c r="A66" s="35" t="inlineStr">
         <is>
           <t>（後日の確認状況、苦情の収束状況、残課題、対応完了日など）</t>
         </is>
@@ -17089,14 +18237,14 @@
       <c r="E69" s="23" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="33" t="inlineStr">
+      <c r="A71" s="34" t="inlineStr">
         <is>
           <t>10．管理者コメント</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="35" t="inlineStr">
         <is>
           <t>（総括、必要な追加措置、大阪市・国保連への報告の要否、虐待・事故に該当する場合の通報・報告など）</t>
         </is>
@@ -17149,7 +18297,7 @@
       <c r="C79" s="9" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="34" t="inlineStr">
+      <c r="A80" s="35" t="inlineStr">
         <is>
           <t>※本記録表は対応完了日から5年間保存する。</t>
         </is>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -27,15 +27,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束排除マニュアル" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事故発生時・緊急時対応マニュアル" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束廃止に関する指針" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情対応マニュアル" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント防止規程" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職場ハラスメント防止規定" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束適正化委員会 名簿" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情対応マニュアル" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント防止規程" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="職場ハラスメント防止規定" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ハラスメント対応マニュアル" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメント規程" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="利用者等ハラスメントマニュアル" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,21 +103,21 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <sz val="20"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -159,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -238,24 +239,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11067,21 +11071,21 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・代表取締役（法人代表者）</t>
+          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 駿成</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・管理者</t>
+          <t xml:space="preserve">　・管理者（委員長）　生田 友哉</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・サービス提供責任者</t>
+          <t xml:space="preserve">　・必要に応じて、サービス提供責任者・担当訪問介護員等の参加を求める</t>
         </is>
       </c>
     </row>
@@ -11676,6 +11680,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>身体拘束適正化委員会　委員名簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>令和8年2月1日現在</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>役職</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>所属・職種</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>役割</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>委員長</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>生田 友哉</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>委員会の招集・運営、身体拘束を行う場合のカンファレンスの主宰、記録の確認、職員教育</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>吉田 駿成</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>代表取締役（法人代表者）</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>身体拘束に関する諸課題の最高責任者、家族・医療・行政機関等への対応、指針の改廃の決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12449,7 +12599,7 @@
           <t>① 苦情・相談の受付</t>
         </is>
       </c>
-      <c r="C140" s="29" t="inlineStr">
+      <c r="C140" s="32" t="inlineStr">
         <is>
           <t>電話／対面／書面／代理で受理
 傾聴し、感情を受け止める
@@ -12470,7 +12620,7 @@
           <t>② 初期情報の記録</t>
         </is>
       </c>
-      <c r="C142" s="29" t="inlineStr">
+      <c r="C142" s="32" t="inlineStr">
         <is>
           <t>苦情（相談）記録表へ記入
 内容・緊急度・対象利用者を整理
@@ -12491,7 +12641,7 @@
           <t>③ 緊急度判定</t>
         </is>
       </c>
-      <c r="C144" s="29" t="inlineStr">
+      <c r="C144" s="32" t="inlineStr">
         <is>
           <t>【高】生命・安全に係る／重大クレーム
 【中】早急に対応が必要
@@ -12512,7 +12662,7 @@
           <t>④ 初期対応の実施</t>
         </is>
       </c>
-      <c r="C146" s="29" t="inlineStr">
+      <c r="C146" s="32" t="inlineStr">
         <is>
           <t>担当交代、訪問調整、緊急措置
 必要に応じて主治医・ケアマネへ連絡</t>
@@ -12532,7 +12682,7 @@
           <t>⑤ 事実確認</t>
         </is>
       </c>
-      <c r="C148" s="29" t="inlineStr">
+      <c r="C148" s="32" t="inlineStr">
         <is>
           <t>関係職員への聞き取り
 訪問記録・ケア記録との照合
@@ -12553,7 +12703,7 @@
           <t>⑥ 分析・判断</t>
         </is>
       </c>
-      <c r="C150" s="29" t="inlineStr">
+      <c r="C150" s="32" t="inlineStr">
         <is>
           <t>原因の特定（ヒューマンエラー／体制要因など）
 事業所としての判断と改善方針決定</t>
@@ -12573,7 +12723,7 @@
           <t>⑦ 利用者・家族への説明</t>
         </is>
       </c>
-      <c r="C152" s="29" t="inlineStr">
+      <c r="C152" s="32" t="inlineStr">
         <is>
           <t>事実確認結果と改善策を説明
 理解状況と同意の有無を記録</t>
@@ -12593,7 +12743,7 @@
           <t>⑧ 是正措置・改善策の実行</t>
         </is>
       </c>
-      <c r="C154" s="29" t="inlineStr">
+      <c r="C154" s="32" t="inlineStr">
         <is>
           <t>担当者変更／介助方法改善／研修の実施
 再発防止策を組織として実行</t>
@@ -12613,7 +12763,7 @@
           <t>⑨ フォローアップ</t>
         </is>
       </c>
-      <c r="C156" s="29" t="inlineStr">
+      <c r="C156" s="32" t="inlineStr">
         <is>
           <t>後日、利用者へ確認の連絡
 収束状況を記録、必要に応じて再対応</t>
@@ -12633,7 +12783,7 @@
           <t>⑩ 終結・保存</t>
         </is>
       </c>
-      <c r="C158" s="29" t="inlineStr">
+      <c r="C158" s="32" t="inlineStr">
         <is>
           <t>管理者が最終確認
 苦情（相談）記録表を保存（5年）
@@ -12770,7 +12920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13601,7 +13751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13636,7 +13786,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>職場におけるハラスメントの
 防止に関する規定</t>
@@ -14107,7 +14257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14838,7 +14988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14873,7 +15023,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応規程</t>
@@ -15842,7 +15992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15877,7 +16027,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応マニュアル</t>
@@ -16729,7 +16879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17014,7 +17164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17774,599 +17924,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>苦情（相談）記録表</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="32" t="inlineStr">
-        <is>
-          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No.　　　　　</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
-        <is>
-          <t>受付日</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>受付方法（電話・対面・書面・代理等）</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
-        <is>
-          <t>苦情（相談）者氏名／続柄</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>対象利用者名</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>受付職員名</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>苦情（相談）区分
-（サービス内容・職員対応・安全衛生・事務手続・その他）</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>発生日時・場所</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>緊急度（高・中・低）</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>1．苦情（相談）内容の詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
-        <is>
-          <t>（事実関係、発生状況、当事者の言動、経緯などを可能な限り具体的に記録）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="23" t="n"/>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="23" t="n"/>
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="23" t="n"/>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="23" t="n"/>
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="23" t="n"/>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>2．利用者・家族の意向／感情の状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>（怒り・不安・困惑など、受け止め方を含めて明確に記述）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="23" t="n"/>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="23" t="n"/>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="23" t="n"/>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>3．初期対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>（受付時の対応、説明内容、緊急対応の要否、関係者（管理者・ケアマネジャー・主治医等）への連絡など）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="23" t="n"/>
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="23" t="n"/>
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="23" t="n"/>
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="34" t="inlineStr">
-        <is>
-          <t>4．関係職員への聞き取り記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>（事実確認内容、職員の説明、第三者の証言等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="23" t="n"/>
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="23" t="n"/>
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="23" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="23" t="n"/>
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="23" t="n"/>
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>5．事業所としての分析・判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="35" t="inlineStr">
-        <is>
-          <t>（原因分析、再発要因、責任区分の検討など）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="23" t="n"/>
-      <c r="B43" s="23" t="n"/>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="23" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="23" t="n"/>
-      <c r="B44" s="23" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="23" t="n"/>
-      <c r="B45" s="23" t="n"/>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="23" t="n"/>
-      <c r="E45" s="23" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>6．対応内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="35" t="inlineStr">
-        <is>
-          <t>（是正措置、改善策、訪問調整、担当変更、職員指導内容など）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="23" t="n"/>
-      <c r="B49" s="23" t="n"/>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="23" t="n"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="23" t="n"/>
-      <c r="B50" s="23" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="23" t="n"/>
-      <c r="E50" s="23" t="n"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="23" t="n"/>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>7．利用者・家族への説明／同意</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="35" t="inlineStr">
-        <is>
-          <t>（説明日、説明者、理解状況、同意の有無）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="23" t="n"/>
-      <c r="B55" s="23" t="n"/>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="23" t="n"/>
-      <c r="E55" s="23" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="23" t="n"/>
-      <c r="B56" s="23" t="n"/>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="23" t="n"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="23" t="n"/>
-      <c r="B57" s="23" t="n"/>
-      <c r="C57" s="23" t="n"/>
-      <c r="D57" s="23" t="n"/>
-      <c r="E57" s="23" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="34" t="inlineStr">
-        <is>
-          <t>8．再発防止策</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>（教育、マニュアル改訂、業務フロー改善等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="23" t="n"/>
-      <c r="B61" s="23" t="n"/>
-      <c r="C61" s="23" t="n"/>
-      <c r="D61" s="23" t="n"/>
-      <c r="E61" s="23" t="n"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="23" t="n"/>
-      <c r="B62" s="23" t="n"/>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="23" t="n"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="23" t="n"/>
-      <c r="B63" s="23" t="n"/>
-      <c r="C63" s="23" t="n"/>
-      <c r="D63" s="23" t="n"/>
-      <c r="E63" s="23" t="n"/>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="34" t="inlineStr">
-        <is>
-          <t>9．フォローアップ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="35" t="inlineStr">
-        <is>
-          <t>（後日の確認状況、苦情の収束状況、残課題、対応完了日など）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="23" t="n"/>
-      <c r="B67" s="23" t="n"/>
-      <c r="C67" s="23" t="n"/>
-      <c r="D67" s="23" t="n"/>
-      <c r="E67" s="23" t="n"/>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="23" t="n"/>
-      <c r="B68" s="23" t="n"/>
-      <c r="C68" s="23" t="n"/>
-      <c r="D68" s="23" t="n"/>
-      <c r="E68" s="23" t="n"/>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="23" t="n"/>
-      <c r="B69" s="23" t="n"/>
-      <c r="C69" s="23" t="n"/>
-      <c r="D69" s="23" t="n"/>
-      <c r="E69" s="23" t="n"/>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="34" t="inlineStr">
-        <is>
-          <t>10．管理者コメント</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="35" t="inlineStr">
-        <is>
-          <t>（総括、必要な追加措置、大阪市・国保連への報告の要否、虐待・事故に該当する場合の通報・報告など）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="23" t="n"/>
-      <c r="B73" s="23" t="n"/>
-      <c r="C73" s="23" t="n"/>
-      <c r="D73" s="23" t="n"/>
-      <c r="E73" s="23" t="n"/>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="23" t="n"/>
-      <c r="B74" s="23" t="n"/>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="23" t="n"/>
-      <c r="E74" s="23" t="n"/>
-    </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="23" t="n"/>
-      <c r="B75" s="23" t="n"/>
-      <c r="C75" s="23" t="n"/>
-      <c r="D75" s="23" t="n"/>
-      <c r="E75" s="23" t="n"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>【最終確認】</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="26" t="inlineStr">
-        <is>
-          <t>管理者署名：</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="9" t="n"/>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="26" t="inlineStr">
-        <is>
-          <t>確認日：　　　　年　　月　　日</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="n"/>
-      <c r="C79" s="9" t="n"/>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="35" t="inlineStr">
-        <is>
-          <t>※本記録表は対応完了日から5年間保存する。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A43:E45"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A67:E69"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A24:E26"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A49:E51"/>
-    <mergeCell ref="A30:E32"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A73:E75"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A61:E63"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A16:E20"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A55:E57"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A36:E39"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="B10:E10"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="33" min="0" max="16383" man="1"/>
-    <brk id="58" min="0" max="16383" man="1"/>
-  </rowBreaks>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19005,6 +18562,599 @@
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="25" min="0" max="16383" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>苦情（相談）記録表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>運営：株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No.　　　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>受付日</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>受付方法（電話・対面・書面・代理等）</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>苦情（相談）者氏名／続柄</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>対象利用者名</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>受付職員名</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>苦情（相談）区分
+（サービス内容・職員対応・安全衛生・事務手続・その他）</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>発生日時・場所</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>緊急度（高・中・低）</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>1．苦情（相談）内容の詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>（事実関係、発生状況、当事者の言動、経緯などを可能な限り具体的に記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>2．利用者・家族の意向／感情の状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>（怒り・不安・困惑など、受け止め方を含めて明確に記述）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="23" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>3．初期対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>（受付時の対応、説明内容、緊急対応の要否、関係者（管理者・ケアマネジャー・主治医等）への連絡など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="23" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="35" t="inlineStr">
+        <is>
+          <t>4．関係職員への聞き取り記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>（事実確認内容、職員の説明、第三者の証言等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="23" t="n"/>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="23" t="n"/>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="23" t="n"/>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>5．事業所としての分析・判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>（原因分析、再発要因、責任区分の検討など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="23" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="23" t="n"/>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="23" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="23" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>6．対応内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>（是正措置、改善策、訪問調整、担当変更、職員指導内容など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="23" t="n"/>
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="23" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="23" t="n"/>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="23" t="n"/>
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="35" t="inlineStr">
+        <is>
+          <t>7．利用者・家族への説明／同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>（説明日、説明者、理解状況、同意の有無）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="23" t="n"/>
+      <c r="B55" s="23" t="n"/>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="23" t="n"/>
+      <c r="E55" s="23" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="23" t="n"/>
+      <c r="B56" s="23" t="n"/>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="23" t="n"/>
+      <c r="B57" s="23" t="n"/>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="23" t="n"/>
+      <c r="E57" s="23" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="35" t="inlineStr">
+        <is>
+          <t>8．再発防止策</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>（教育、マニュアル改訂、業務フロー改善等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="23" t="n"/>
+      <c r="B61" s="23" t="n"/>
+      <c r="C61" s="23" t="n"/>
+      <c r="D61" s="23" t="n"/>
+      <c r="E61" s="23" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="23" t="n"/>
+      <c r="B62" s="23" t="n"/>
+      <c r="C62" s="23" t="n"/>
+      <c r="D62" s="23" t="n"/>
+      <c r="E62" s="23" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="23" t="n"/>
+      <c r="B63" s="23" t="n"/>
+      <c r="C63" s="23" t="n"/>
+      <c r="D63" s="23" t="n"/>
+      <c r="E63" s="23" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="35" t="inlineStr">
+        <is>
+          <t>9．フォローアップ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
+        <is>
+          <t>（後日の確認状況、苦情の収束状況、残課題、対応完了日など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="23" t="n"/>
+      <c r="B67" s="23" t="n"/>
+      <c r="C67" s="23" t="n"/>
+      <c r="D67" s="23" t="n"/>
+      <c r="E67" s="23" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="23" t="n"/>
+      <c r="B68" s="23" t="n"/>
+      <c r="C68" s="23" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="23" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="23" t="n"/>
+      <c r="B69" s="23" t="n"/>
+      <c r="C69" s="23" t="n"/>
+      <c r="D69" s="23" t="n"/>
+      <c r="E69" s="23" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="35" t="inlineStr">
+        <is>
+          <t>10．管理者コメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="36" t="inlineStr">
+        <is>
+          <t>（総括、必要な追加措置、大阪市・国保連への報告の要否、虐待・事故に該当する場合の通報・報告など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="23" t="n"/>
+      <c r="B73" s="23" t="n"/>
+      <c r="C73" s="23" t="n"/>
+      <c r="D73" s="23" t="n"/>
+      <c r="E73" s="23" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="23" t="n"/>
+      <c r="B74" s="23" t="n"/>
+      <c r="C74" s="23" t="n"/>
+      <c r="D74" s="23" t="n"/>
+      <c r="E74" s="23" t="n"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="23" t="n"/>
+      <c r="B75" s="23" t="n"/>
+      <c r="C75" s="23" t="n"/>
+      <c r="D75" s="23" t="n"/>
+      <c r="E75" s="23" t="n"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>【最終確認】</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="26" t="inlineStr">
+        <is>
+          <t>管理者署名：</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>確認日：　　　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="9" t="n"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="36" t="inlineStr">
+        <is>
+          <t>※本記録表は対応完了日から5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A43:E45"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A67:E69"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E26"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A49:E51"/>
+    <mergeCell ref="A30:E32"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A73:E75"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A61:E63"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A16:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A55:E57"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A36:E39"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="B10:E10"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="33" min="0" max="16383" man="1"/>
+    <brk id="58" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -139,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -156,11 +156,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -244,6 +272,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -7292,7 +7325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8186,124 +8219,104 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>感染症対策全体の統括・研修・教育担当を兼務</t>
+          <t>感染症対策全体の統括・最終判断・行政報告。研修・教育担当を兼務</t>
         </is>
       </c>
       <c r="E134" s="23" t="n"/>
     </row>
-    <row r="135" ht="20" customHeight="1">
+    <row r="135" ht="32" customHeight="1">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>副委員長（サービス提供責任者）</t>
+          <t>委員（代表取締役）</t>
         </is>
       </c>
       <c r="B135" s="21" t="n"/>
       <c r="C135" s="22" t="inlineStr">
         <is>
-          <t>岩谷</t>
+          <t>吉田 俊輔</t>
         </is>
       </c>
       <c r="D135" s="22" t="inlineStr">
         <is>
-          <t>現場調整・周知・実務統括</t>
+          <t>法人としての方針決定、BCPの承認、重大事案時の対外対応</t>
         </is>
       </c>
       <c r="E135" s="23" t="n"/>
     </row>
-    <row r="136" ht="20" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>看護職委員</t>
+          <t>委員（事務・総務）</t>
         </is>
       </c>
       <c r="B136" s="21" t="n"/>
       <c r="C136" s="22" t="inlineStr">
         <is>
-          <t>松本</t>
+          <t>吉田 麻美</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
         <is>
-          <t>医療的助言・PPE指導</t>
+          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
         </is>
       </c>
       <c r="E136" s="23" t="n"/>
     </row>
-    <row r="137" ht="20" customHeight="1">
+    <row r="137" ht="32" customHeight="1">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>ヘルパー代表</t>
+          <t>委員（ヘルパー代表）</t>
         </is>
       </c>
       <c r="B137" s="21" t="n"/>
       <c r="C137" s="22" t="inlineStr">
         <is>
-          <t>松川</t>
+          <t>WIN YADANAR AWNG</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>現場情報共有・フィードバック</t>
+          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
         </is>
       </c>
       <c r="E137" s="23" t="n"/>
     </row>
-    <row r="138" ht="20" customHeight="1">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>事務・総務</t>
+          <t>顧問（任意）</t>
         </is>
       </c>
       <c r="B138" s="21" t="n"/>
       <c r="C138" s="22" t="inlineStr">
         <is>
-          <t>鳥羽</t>
+          <t>主治医・外部専門家・保健所等</t>
         </is>
       </c>
       <c r="D138" s="22" t="inlineStr">
         <is>
-          <t>記録整備・行政書類確認</t>
+          <t>医療的助言・PPE指導（必要に応じて）</t>
         </is>
       </c>
       <c r="E138" s="23" t="n"/>
     </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="20" t="inlineStr">
-        <is>
-          <t>研修・教育担当</t>
-        </is>
-      </c>
-      <c r="B139" s="21" t="n"/>
-      <c r="C139" s="22" t="inlineStr">
-        <is>
-          <t>生田 友哉（兼務）</t>
-        </is>
-      </c>
-      <c r="D139" s="22" t="inlineStr">
-        <is>
-          <t>感染研修の企画・欠席者フォロー</t>
-        </is>
-      </c>
-      <c r="E139" s="23" t="n"/>
-    </row>
-    <row r="140" ht="8" customHeight="1"/>
+    <row r="139" ht="8" customHeight="1"/>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>＜附則＞</t>
+        </is>
+      </c>
+    </row>
     <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>＜附則＞</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>本資料は、令和8年2月1日から適用する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="107">
-    <mergeCell ref="A142:E142"/>
+  <mergeCells count="105">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A79:E79"/>
@@ -8342,7 +8355,6 @@
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="D53:E53"/>
-    <mergeCell ref="A139:B139"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
@@ -8359,7 +8371,6 @@
     <mergeCell ref="A110:E110"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D139:E139"/>
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="A25:E25"/>
@@ -8400,6 +8411,7 @@
     <mergeCell ref="D137:E137"/>
     <mergeCell ref="A135:B135"/>
     <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A134:B134"/>
@@ -10782,7 +10794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11071,489 +11083,503 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 駿成</t>
+          <t xml:space="preserve">　・管理者（委員長）　生田 友哉</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・管理者（委員長）　生田 友哉</t>
+          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 俊輔</t>
         </is>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・必要に応じて、サービス提供責任者・担当訪問介護員等の参加を求める</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="8" customHeight="1"/>
+          <t xml:space="preserve">　・事務・総務　吉田 麻美</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+        </is>
+      </c>
+    </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・必要に応じて、担当訪問介護員・ケアマネジャー・主治医等の参加を求める</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>③ 委員会の開催</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>年1回以上定期的に開催するほか、必要時に随時開催します。開催はテレビ電話装置等を活用して行うことができ、虐待防止委員会等と一体的に開催することを妨げません。結果は記録し、全職員に周知します。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="10" customHeight="1"/>
-    <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
+    <row r="75" ht="10" customHeight="1"/>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>4．やむを得ず身体拘束を行う場合の対応</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>本人又は他の利用者等の生命又は身体を保護するための措置として、緊急やむを得ず身体拘束を行わなければならない場合は、以下の手順に従って実施します。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="78" ht="6" customHeight="1"/>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>1）カンファレンスの実施</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>緊急やむを得ない状況になった場合、委員会の構成員が集まり、拘束による利用者の心身の損害や拘束をしない場合のリスクについて検討し、身体拘束を行う事を選択する前に①切迫性②非代替性③一時性の3要件全てを満たしているかどうかについて検討、確認します。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="64" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+    <row r="81" ht="64" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>要件を検討・確認した上で、身体拘束を行うことを選択した場合は、拘束の方法、場所、時間帯、期間等について検討し、本人・家族に対する説明書を作成します。また、廃止に向けた取り組み改善の検討会を早急に行い実施に努めます。居宅介護支援事業所（ケアマネジャー）にも報告し、ケアプランへの位置づけについて協議します。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="6" customHeight="1"/>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>2）利用者本人や家族に対しての説明</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>また、身体拘束の同意期限を越え、なお拘束を必要とする場合については、事前に契約者・家族等と行っている内容と方向性、利用者の状態などを確認説明し、同意を得たうえで実施します。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="6" customHeight="1"/>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
+    <row r="86" ht="6" customHeight="1"/>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>3）記録と再検討</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="64" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>法律上、身体拘束に関する記録は義務付けられており、専用の様式を用いてその態様及び時間・その際の利用者の心身の状況・やむを得なかった理由などを記録します。身体拘束の早期解除に向けて、拘束の必要性や方法を逐次検討します。その記録は5年間保存し、行政担当部局の運営指導等が行われる際に提示できるようにします。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="6" customHeight="1"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>4）拘束の解除</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="32" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>3）の記録と再検討の結果、身体拘束を継続する必要性がなくなった場合は、速やかに身体拘束を解除します。その場合には、契約者、家族、居宅介護支援事業所に報告します。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="10" customHeight="1"/>
-    <row r="91" ht="26" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
+    <row r="92" ht="10" customHeight="1"/>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
         <is>
           <t>5．身体的拘束等の報告方法等のための方策に関する基本方針</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　1）身体的拘束等を行う場合には、4．の手続きに基づき利用者家族に速やかに説明し、報告を行うこと。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="48" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　3）適切な手続きに依らない身体的拘束の事実が判明した場合は、利用者及び利用者家族への謝罪を行い、大阪市への報告を行うこと。高齢者虐待に該当するおそれがある場合は、高齢者虐待防止法に基づき通報すること。</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　4）訪問時に家族等による身体拘束を発見した場合は、管理者に報告し、居宅介護支援事業所と連携して対応すること。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="17" t="inlineStr">
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="17" t="inlineStr">
         <is>
           <t>介護保険指定基準において身体拘束禁止の対象となる具体的な行為</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（4）点滴・経管栄養等のチューブを抜かないように、四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="32" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　（6）車椅子・椅子からずり落ちたり、立ち上がったりしないように、Y字型拘束帯や腰ベルト・車椅子テーブルをつける</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（11）自分の意思で開けることのできない居室等に隔離する</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="8" customHeight="1"/>
-    <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="16" t="inlineStr">
+    <row r="111" ht="8" customHeight="1"/>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="16" t="inlineStr">
         <is>
           <t>6．身体拘束廃止に向けた各職種の役割</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>身体拘束の廃止のために、各職種の専門性に基づくアプローチから、チームケアを行うことを基本とし、それぞれの果たすべき役割に責任をもって対応します。</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="6" customHeight="1"/>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="114" ht="6" customHeight="1"/>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>（代表取締役）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）委員会総括責任者</t>
         </is>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2）委員会総括責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3）家族、医療、行政機関、その他関係機関への対応</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="8" customHeight="1"/>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="119" ht="8" customHeight="1"/>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>（身体拘束適正化委員会）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
         </is>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　5）身体拘束廃止に向けた職員教育</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="8" customHeight="1"/>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="126" ht="8" customHeight="1"/>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>（全従業者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
         </is>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
+          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
+          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
+          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
+          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
+          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
+          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　11）利用者宅の住環境（段差・家具配置等）や福祉用具の改善提案</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="26" customHeight="1">
-      <c r="A138" s="16" t="inlineStr">
+    <row r="139" ht="8" customHeight="1"/>
+    <row r="140" ht="26" customHeight="1">
+      <c r="A140" s="16" t="inlineStr">
         <is>
           <t>7．身体拘束廃止・改善のための職員教育・研修</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="32" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="141" ht="32" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>支援に携わる全ての職員（登録ヘルパーを含む）に対して、身体拘束廃止と人権を尊重したケアの励行を図り、事故防止と合わせてリスクマネジメントとしての職員教育を行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
         </is>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　③ その他必要な教育・研修の実施</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="8" customHeight="1"/>
-    <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="16" t="inlineStr">
+    <row r="145" ht="8" customHeight="1"/>
+    <row r="146" ht="26" customHeight="1">
+      <c r="A146" s="16" t="inlineStr">
         <is>
           <t>8．身体拘束廃止に関する指針の閲覧について</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="147" ht="32" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>この指針は、当事業所内に掲示するとともに、利用者・家族がいつでも自由に閲覧することができます。</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="10" customHeight="1"/>
-    <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="16" t="inlineStr">
+    <row r="148" ht="10" customHeight="1"/>
+    <row r="149" ht="26" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t>9．附則</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>この指針は令和8年2月1日より施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="104">
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
@@ -11561,15 +11587,15 @@
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A136:E136"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
-    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
@@ -11583,17 +11609,14 @@
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A148:E148"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A138:E138"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
-    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
@@ -11603,59 +11626,64 @@
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A81:E81"/>
     <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A147:E147"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A123:E123"/>
     <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A146:E146"/>
+    <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A149:E149"/>
     <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A150:E150"/>
     <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A127:E127"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A90:E90"/>
     <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A126:E126"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A143:E143"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11762,7 +11790,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>吉田 駿成</t>
+          <t>吉田 俊輔</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -11773,6 +11801,28 @@
       <c r="D7" s="22" t="inlineStr">
         <is>
           <t>身体拘束に関する諸課題の最高責任者、家族・医療・行政機関等への対応、指針の改廃の決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>吉田 麻美</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>事務・総務</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>議事録の作成・保存、記録様式の管理、委員会資料の準備</t>
         </is>
       </c>
     </row>
@@ -11782,23 +11832,26 @@
           <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="33" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
         </is>
@@ -12599,7 +12652,7 @@
           <t>① 苦情・相談の受付</t>
         </is>
       </c>
-      <c r="C140" s="32" t="inlineStr">
+      <c r="C140" s="35" t="inlineStr">
         <is>
           <t>電話／対面／書面／代理で受理
 傾聴し、感情を受け止める
@@ -12620,7 +12673,7 @@
           <t>② 初期情報の記録</t>
         </is>
       </c>
-      <c r="C142" s="32" t="inlineStr">
+      <c r="C142" s="35" t="inlineStr">
         <is>
           <t>苦情（相談）記録表へ記入
 内容・緊急度・対象利用者を整理
@@ -12641,7 +12694,7 @@
           <t>③ 緊急度判定</t>
         </is>
       </c>
-      <c r="C144" s="32" t="inlineStr">
+      <c r="C144" s="35" t="inlineStr">
         <is>
           <t>【高】生命・安全に係る／重大クレーム
 【中】早急に対応が必要
@@ -12662,7 +12715,7 @@
           <t>④ 初期対応の実施</t>
         </is>
       </c>
-      <c r="C146" s="32" t="inlineStr">
+      <c r="C146" s="35" t="inlineStr">
         <is>
           <t>担当交代、訪問調整、緊急措置
 必要に応じて主治医・ケアマネへ連絡</t>
@@ -12682,7 +12735,7 @@
           <t>⑤ 事実確認</t>
         </is>
       </c>
-      <c r="C148" s="32" t="inlineStr">
+      <c r="C148" s="35" t="inlineStr">
         <is>
           <t>関係職員への聞き取り
 訪問記録・ケア記録との照合
@@ -12703,7 +12756,7 @@
           <t>⑥ 分析・判断</t>
         </is>
       </c>
-      <c r="C150" s="32" t="inlineStr">
+      <c r="C150" s="35" t="inlineStr">
         <is>
           <t>原因の特定（ヒューマンエラー／体制要因など）
 事業所としての判断と改善方針決定</t>
@@ -12723,7 +12776,7 @@
           <t>⑦ 利用者・家族への説明</t>
         </is>
       </c>
-      <c r="C152" s="32" t="inlineStr">
+      <c r="C152" s="35" t="inlineStr">
         <is>
           <t>事実確認結果と改善策を説明
 理解状況と同意の有無を記録</t>
@@ -12743,7 +12796,7 @@
           <t>⑧ 是正措置・改善策の実行</t>
         </is>
       </c>
-      <c r="C154" s="32" t="inlineStr">
+      <c r="C154" s="35" t="inlineStr">
         <is>
           <t>担当者変更／介助方法改善／研修の実施
 再発防止策を組織として実行</t>
@@ -12763,7 +12816,7 @@
           <t>⑨ フォローアップ</t>
         </is>
       </c>
-      <c r="C156" s="32" t="inlineStr">
+      <c r="C156" s="35" t="inlineStr">
         <is>
           <t>後日、利用者へ確認の連絡
 収束状況を記録、必要に応じて再対応</t>
@@ -12783,7 +12836,7 @@
           <t>⑩ 終結・保存</t>
         </is>
       </c>
-      <c r="C158" s="32" t="inlineStr">
+      <c r="C158" s="35" t="inlineStr">
         <is>
           <t>管理者が最終確認
 苦情（相談）記録表を保存（5年）
@@ -13786,7 +13839,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>職場におけるハラスメントの
 防止に関する規定</t>
@@ -15023,7 +15076,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応規程</t>
@@ -16027,7 +16080,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応マニュアル</t>
@@ -18604,7 +18657,7 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>受付日</t>
         </is>
@@ -18615,7 +18668,7 @@
       <c r="E5" s="23" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>受付方法（電話・対面・書面・代理等）</t>
         </is>
@@ -18626,7 +18679,7 @@
       <c r="E6" s="23" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>苦情（相談）者氏名／続柄</t>
         </is>
@@ -18637,7 +18690,7 @@
       <c r="E7" s="23" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>対象利用者名</t>
         </is>
@@ -18648,7 +18701,7 @@
       <c r="E8" s="23" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>受付職員名</t>
         </is>
@@ -18659,7 +18712,7 @@
       <c r="E9" s="23" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>苦情（相談）区分
 （サービス内容・職員対応・安全衛生・事務手続・その他）</t>
@@ -18671,7 +18724,7 @@
       <c r="E10" s="23" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>発生日時・場所</t>
         </is>
@@ -18682,7 +18735,7 @@
       <c r="E11" s="23" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>緊急度（高・中・低）</t>
         </is>
@@ -18693,14 +18746,14 @@
       <c r="E12" s="23" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>1．苦情（相談）内容の詳細</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>（事実関係、発生状況、当事者の言動、経緯などを可能な限り具体的に記録）</t>
         </is>
@@ -18742,14 +18795,14 @@
       <c r="E20" s="23" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>2．利用者・家族の意向／感情の状況</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="36" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>（怒り・不安・困惑など、受け止め方を含めて明確に記述）</t>
         </is>
@@ -18777,14 +18830,14 @@
       <c r="E26" s="23" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>3．初期対応</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>（受付時の対応、説明内容、緊急対応の要否、関係者（管理者・ケアマネジャー・主治医等）への連絡など）</t>
         </is>
@@ -18812,14 +18865,14 @@
       <c r="E32" s="23" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="38" t="inlineStr">
         <is>
           <t>4．関係職員への聞き取り記録</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="36" t="inlineStr">
+      <c r="A35" s="39" t="inlineStr">
         <is>
           <t>（事実確認内容、職員の説明、第三者の証言等）</t>
         </is>
@@ -18854,14 +18907,14 @@
       <c r="E39" s="23" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>5．事業所としての分析・判断</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>（原因分析、再発要因、責任区分の検討など）</t>
         </is>
@@ -18889,14 +18942,14 @@
       <c r="E45" s="23" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="38" t="inlineStr">
         <is>
           <t>6．対応内容</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>（是正措置、改善策、訪問調整、担当変更、職員指導内容など）</t>
         </is>
@@ -18924,14 +18977,14 @@
       <c r="E51" s="23" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="38" t="inlineStr">
         <is>
           <t>7．利用者・家族への説明／同意</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="39" t="inlineStr">
         <is>
           <t>（説明日、説明者、理解状況、同意の有無）</t>
         </is>
@@ -18959,14 +19012,14 @@
       <c r="E57" s="23" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="38" t="inlineStr">
         <is>
           <t>8．再発防止策</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>（教育、マニュアル改訂、業務フロー改善等）</t>
         </is>
@@ -18994,14 +19047,14 @@
       <c r="E63" s="23" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="35" t="inlineStr">
+      <c r="A65" s="38" t="inlineStr">
         <is>
           <t>9．フォローアップ記録</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="36" t="inlineStr">
+      <c r="A66" s="39" t="inlineStr">
         <is>
           <t>（後日の確認状況、苦情の収束状況、残課題、対応完了日など）</t>
         </is>
@@ -19029,14 +19082,14 @@
       <c r="E69" s="23" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="35" t="inlineStr">
+      <c r="A71" s="38" t="inlineStr">
         <is>
           <t>10．管理者コメント</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="36" t="inlineStr">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>（総括、必要な追加措置、大阪市・国保連への報告の要否、虐待・事故に該当する場合の通報・報告など）</t>
         </is>
@@ -19089,7 +19142,7 @@
       <c r="C79" s="9" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="36" t="inlineStr">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>※本記録表は対応完了日から5年間保存する。</t>
         </is>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -139,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -156,39 +156,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -272,11 +244,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -11708,7 +11675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11826,32 +11793,51 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>WIN YADANAR AWNG</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>訪問介護員（ヘルパー代表）</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>現場での拘束・スピーチロックの有無の確認、困りごとの共有、決定事項の現場へのフィードバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="32" t="n"/>
-      <c r="D9" s="33" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
         </is>
@@ -11860,12 +11846,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12652,7 +12638,7 @@
           <t>① 苦情・相談の受付</t>
         </is>
       </c>
-      <c r="C140" s="35" t="inlineStr">
+      <c r="C140" s="32" t="inlineStr">
         <is>
           <t>電話／対面／書面／代理で受理
 傾聴し、感情を受け止める
@@ -12673,7 +12659,7 @@
           <t>② 初期情報の記録</t>
         </is>
       </c>
-      <c r="C142" s="35" t="inlineStr">
+      <c r="C142" s="32" t="inlineStr">
         <is>
           <t>苦情（相談）記録表へ記入
 内容・緊急度・対象利用者を整理
@@ -12694,7 +12680,7 @@
           <t>③ 緊急度判定</t>
         </is>
       </c>
-      <c r="C144" s="35" t="inlineStr">
+      <c r="C144" s="32" t="inlineStr">
         <is>
           <t>【高】生命・安全に係る／重大クレーム
 【中】早急に対応が必要
@@ -12715,7 +12701,7 @@
           <t>④ 初期対応の実施</t>
         </is>
       </c>
-      <c r="C146" s="35" t="inlineStr">
+      <c r="C146" s="32" t="inlineStr">
         <is>
           <t>担当交代、訪問調整、緊急措置
 必要に応じて主治医・ケアマネへ連絡</t>
@@ -12735,7 +12721,7 @@
           <t>⑤ 事実確認</t>
         </is>
       </c>
-      <c r="C148" s="35" t="inlineStr">
+      <c r="C148" s="32" t="inlineStr">
         <is>
           <t>関係職員への聞き取り
 訪問記録・ケア記録との照合
@@ -12756,7 +12742,7 @@
           <t>⑥ 分析・判断</t>
         </is>
       </c>
-      <c r="C150" s="35" t="inlineStr">
+      <c r="C150" s="32" t="inlineStr">
         <is>
           <t>原因の特定（ヒューマンエラー／体制要因など）
 事業所としての判断と改善方針決定</t>
@@ -12776,7 +12762,7 @@
           <t>⑦ 利用者・家族への説明</t>
         </is>
       </c>
-      <c r="C152" s="35" t="inlineStr">
+      <c r="C152" s="32" t="inlineStr">
         <is>
           <t>事実確認結果と改善策を説明
 理解状況と同意の有無を記録</t>
@@ -12796,7 +12782,7 @@
           <t>⑧ 是正措置・改善策の実行</t>
         </is>
       </c>
-      <c r="C154" s="35" t="inlineStr">
+      <c r="C154" s="32" t="inlineStr">
         <is>
           <t>担当者変更／介助方法改善／研修の実施
 再発防止策を組織として実行</t>
@@ -12816,7 +12802,7 @@
           <t>⑨ フォローアップ</t>
         </is>
       </c>
-      <c r="C156" s="35" t="inlineStr">
+      <c r="C156" s="32" t="inlineStr">
         <is>
           <t>後日、利用者へ確認の連絡
 収束状況を記録、必要に応じて再対応</t>
@@ -12836,7 +12822,7 @@
           <t>⑩ 終結・保存</t>
         </is>
       </c>
-      <c r="C158" s="35" t="inlineStr">
+      <c r="C158" s="32" t="inlineStr">
         <is>
           <t>管理者が最終確認
 苦情（相談）記録表を保存（5年）
@@ -13839,7 +13825,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>職場におけるハラスメントの
 防止に関する規定</t>
@@ -15076,7 +15062,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応規程</t>
@@ -16080,7 +16066,7 @@
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1"/>
     <row r="13" ht="80" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>利用者等からのハラスメント
 防止・対応マニュアル</t>
@@ -18657,7 +18643,7 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>受付日</t>
         </is>
@@ -18668,7 +18654,7 @@
       <c r="E5" s="23" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>受付方法（電話・対面・書面・代理等）</t>
         </is>
@@ -18679,7 +18665,7 @@
       <c r="E6" s="23" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>苦情（相談）者氏名／続柄</t>
         </is>
@@ -18690,7 +18676,7 @@
       <c r="E7" s="23" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>対象利用者名</t>
         </is>
@@ -18701,7 +18687,7 @@
       <c r="E8" s="23" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>受付職員名</t>
         </is>
@@ -18712,7 +18698,7 @@
       <c r="E9" s="23" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>苦情（相談）区分
 （サービス内容・職員対応・安全衛生・事務手続・その他）</t>
@@ -18724,7 +18710,7 @@
       <c r="E10" s="23" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>発生日時・場所</t>
         </is>
@@ -18735,7 +18721,7 @@
       <c r="E11" s="23" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>緊急度（高・中・低）</t>
         </is>
@@ -18746,14 +18732,14 @@
       <c r="E12" s="23" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>1．苦情（相談）内容の詳細</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>（事実関係、発生状況、当事者の言動、経緯などを可能な限り具体的に記録）</t>
         </is>
@@ -18795,14 +18781,14 @@
       <c r="E20" s="23" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>2．利用者・家族の意向／感情の状況</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>（怒り・不安・困惑など、受け止め方を含めて明確に記述）</t>
         </is>
@@ -18830,14 +18816,14 @@
       <c r="E26" s="23" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>3．初期対応</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>（受付時の対応、説明内容、緊急対応の要否、関係者（管理者・ケアマネジャー・主治医等）への連絡など）</t>
         </is>
@@ -18865,14 +18851,14 @@
       <c r="E32" s="23" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="38" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>4．関係職員への聞き取り記録</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>（事実確認内容、職員の説明、第三者の証言等）</t>
         </is>
@@ -18907,14 +18893,14 @@
       <c r="E39" s="23" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>5．事業所としての分析・判断</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>（原因分析、再発要因、責任区分の検討など）</t>
         </is>
@@ -18942,14 +18928,14 @@
       <c r="E45" s="23" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="38" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>6．対応内容</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>（是正措置、改善策、訪問調整、担当変更、職員指導内容など）</t>
         </is>
@@ -18977,14 +18963,14 @@
       <c r="E51" s="23" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="38" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>7．利用者・家族への説明／同意</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="39" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>（説明日、説明者、理解状況、同意の有無）</t>
         </is>
@@ -19012,14 +18998,14 @@
       <c r="E57" s="23" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="38" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>8．再発防止策</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="39" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>（教育、マニュアル改訂、業務フロー改善等）</t>
         </is>
@@ -19047,14 +19033,14 @@
       <c r="E63" s="23" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="38" t="inlineStr">
+      <c r="A65" s="35" t="inlineStr">
         <is>
           <t>9．フォローアップ記録</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="39" t="inlineStr">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>（後日の確認状況、苦情の収束状況、残課題、対応完了日など）</t>
         </is>
@@ -19082,14 +19068,14 @@
       <c r="E69" s="23" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="38" t="inlineStr">
+      <c r="A71" s="35" t="inlineStr">
         <is>
           <t>10．管理者コメント</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="39" t="inlineStr">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>（総括、必要な追加措置、大阪市・国保連への報告の要否、虐待・事故に該当する場合の通報・報告など）</t>
         </is>
@@ -19142,7 +19128,7 @@
       <c r="C79" s="9" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="39" t="inlineStr">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>※本記録表は対応完了日から5年間保存する。</t>
         </is>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -37,6 +37,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束委員会 議事録R8.6.25" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,7 +47,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,8 +126,41 @@
       <color rgb="001F4E79"/>
       <sz val="11.5"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -138,8 +172,20 @@
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -156,11 +202,69 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -261,6 +365,35 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -628,7 +761,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E132"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -1448,7 +1581,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -1912,7 +2045,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E146"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -2752,7 +2885,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E193"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -3923,7 +4056,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -4334,7 +4467,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E137"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -5095,7 +5228,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -5805,7 +5938,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E207"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -7293,7 +7426,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -8416,7 +8549,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E91"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -8972,7 +9105,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E174"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -10080,7 +10213,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E128"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -10761,8 +10894,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E151"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -11071,498 +11204,505 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+          <t xml:space="preserve">　・訪問介護員　松村 知恵</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・必要に応じて、担当訪問介護員・ケアマネジャー・主治医等の参加を求める</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="8" customHeight="1"/>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>③ 委員会の開催</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="75" ht="48" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>年1回以上定期的に開催するほか、必要時に随時開催します。開催はテレビ電話装置等を活用して行うことができ、虐待防止委員会等と一体的に開催することを妨げません。結果は記録し、全職員に周知します。</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="10" customHeight="1"/>
-    <row r="76" ht="26" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="76" ht="10" customHeight="1"/>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>4．やむを得ず身体拘束を行う場合の対応</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>本人又は他の利用者等の生命又は身体を保護するための措置として、緊急やむを得ず身体拘束を行わなければならない場合は、以下の手順に従って実施します。</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="6" customHeight="1"/>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="79" ht="6" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>1）カンファレンスの実施</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>緊急やむを得ない状況になった場合、委員会の構成員が集まり、拘束による利用者の心身の損害や拘束をしない場合のリスクについて検討し、身体拘束を行う事を選択する前に①切迫性②非代替性③一時性の3要件全てを満たしているかどうかについて検討、確認します。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="64" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>要件を検討・確認した上で、身体拘束を行うことを選択した場合は、拘束の方法、場所、時間帯、期間等について検討し、本人・家族に対する説明書を作成します。また、廃止に向けた取り組み改善の検討会を早急に行い実施に努めます。居宅介護支援事業所（ケアマネジャー）にも報告し、ケアプランへの位置づけについて協議します。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="6" customHeight="1"/>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="83" ht="6" customHeight="1"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>2）利用者本人や家族に対しての説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>身体拘束の内容・目的・理由・拘束時間又は時間帯・期間・場所・改善に向けた取り組み方法を詳細に説明し、充分理解が得られるように努めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>また、身体拘束の同意期限を越え、なお拘束を必要とする場合については、事前に契約者・家族等と行っている内容と方向性、利用者の状態などを確認説明し、同意を得たうえで実施します。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="6" customHeight="1"/>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+    <row r="87" ht="6" customHeight="1"/>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>3）記録と再検討</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="64" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>法律上、身体拘束に関する記録は義務付けられており、専用の様式を用いてその態様及び時間・その際の利用者の心身の状況・やむを得なかった理由などを記録します。身体拘束の早期解除に向けて、拘束の必要性や方法を逐次検討します。その記録は5年間保存し、行政担当部局の運営指導等が行われる際に提示できるようにします。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="6" customHeight="1"/>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="90" ht="6" customHeight="1"/>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>4）拘束の解除</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>3）の記録と再検討の結果、身体拘束を継続する必要性がなくなった場合は、速やかに身体拘束を解除します。その場合には、契約者、家族、居宅介護支援事業所に報告します。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="10" customHeight="1"/>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
+    <row r="93" ht="10" customHeight="1"/>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
         <is>
           <t>5．身体的拘束等の報告方法等のための方策に関する基本方針</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　1）身体的拘束等を行う場合には、4．の手続きに基づき利用者家族に速やかに説明し、報告を行うこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
         </is>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　2）訪問先等において他の職員等による適切な手続きに依らない身体的拘束等を視認等した場合、具体的な状況、時刻等を確認したうえで委員会への報告を行うこと。当該報告を受けた委員は、身体的拘束を実施したと思われる職員に聞き取りを行い実態の把握に努めること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3）適切な手続きに依らない身体的拘束の事実が判明した場合は、利用者及び利用者家族への謝罪を行い、大阪市への報告を行うこと。高齢者虐待に該当するおそれがある場合は、高齢者虐待防止法に基づき通報すること。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">　4）訪問時に家族等による身体拘束を発見した場合は、管理者に報告し、居宅介護支援事業所と連携して対応すること。</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="8" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="17" t="inlineStr">
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="17" t="inlineStr">
         <is>
           <t>介護保険指定基準において身体拘束禁止の対象となる具体的な行為</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
+          <t xml:space="preserve">　（1）徘徊しないように、車椅子や椅子・ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+          <t xml:space="preserve">　（2）転落しないように、ベッドに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（3）自分で降りられないように、ベッドを柵（サイドレール）で囲む</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（4）点滴・経管栄養等のチューブを抜かないように、四肢をひも等で縛る</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
         </is>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（5）点滴・経管栄養等のチューブを抜かないように、又は皮膚をかきむしらないように、手指の機能を制限するミトン型の手袋等をつける</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（6）車椅子・椅子からずり落ちたり、立ち上がったりしないように、Y字型拘束帯や腰ベルト・車椅子テーブルをつける</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
+          <t xml:space="preserve">　（7）立ち上がる能力のある人の立ち上がりを妨げるような椅子を使用する</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
+          <t xml:space="preserve">　（8）脱衣やオムツはずしを制限するために、介護衣（つなぎ服）を着せる</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+          <t xml:space="preserve">　（9）他人への迷惑行為を防ぐために、ベッドなどに体幹や四肢をひも等で縛る</t>
         </is>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　（10）行動を落ち着かせるために、向精神薬を過剰に服用させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　（11）自分の意思で開けることのできない居室等に隔離する</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="26" customHeight="1">
-      <c r="A112" s="16" t="inlineStr">
+    <row r="112" ht="8" customHeight="1"/>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="16" t="inlineStr">
         <is>
           <t>6．身体拘束廃止に向けた各職種の役割</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>身体拘束の廃止のために、各職種の専門性に基づくアプローチから、チームケアを行うことを基本とし、それぞれの果たすべき役割に責任をもって対応します。</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="6" customHeight="1"/>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
+    <row r="115" ht="6" customHeight="1"/>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>（代表取締役）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
         </is>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2）委員会総括責任者</t>
+          <t xml:space="preserve">　1）身体拘束における諸課題等の最高責任者</t>
         </is>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　2）委員会総括責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3）家族、医療、行政機関、その他関係機関への対応</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>（身体拘束適正化委員会）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
         </is>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
+          <t xml:space="preserve">　1）身体拘束廃止のための指針の周知徹底</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
+          <t xml:space="preserve">　2）身体拘束に関する説明書、システムの確立</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+          <t xml:space="preserve">　3）身体拘束に関する対応策及び防止策の検討</t>
         </is>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　4）検討内容の実践、結果確認及び再検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　5）身体拘束廃止に向けた職員教育</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="8" customHeight="1"/>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
+    <row r="127" ht="8" customHeight="1"/>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>（全従業者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
         </is>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
+          <t xml:space="preserve">　1）拘束がもたらす弊害を正確に認識する</t>
         </is>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
+          <t xml:space="preserve">　2）利用者の尊厳を理解する</t>
         </is>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
+          <t xml:space="preserve">　3）利用者の疾病、障害等による行動特性の理解</t>
         </is>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
+          <t xml:space="preserve">　4）利用者個々の心身の状態を把握し、基本的ケアに努める</t>
         </is>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
+          <t xml:space="preserve">　5）利用者とのコミュニケーションを充分にとる</t>
         </is>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
+          <t xml:space="preserve">　6）記録は正確かつ丁寧に記録する</t>
         </is>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
+          <t xml:space="preserve">　7）医療機関、家族、居宅介護支援事業所等の関係機関との連絡調整</t>
         </is>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
+          <t xml:space="preserve">　8）訪問介護員が行える医療的ケアの範囲の確認</t>
         </is>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+          <t xml:space="preserve">　9）重度化する利用者の状態観察</t>
         </is>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　10）家族の意向に添ったケアの確立</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　11）利用者宅の住環境（段差・家具配置等）や福祉用具の改善提案</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="8" customHeight="1"/>
-    <row r="140" ht="26" customHeight="1">
-      <c r="A140" s="16" t="inlineStr">
+    <row r="140" ht="8" customHeight="1"/>
+    <row r="141" ht="26" customHeight="1">
+      <c r="A141" s="16" t="inlineStr">
         <is>
           <t>7．身体拘束廃止・改善のための職員教育・研修</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="32" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>支援に携わる全ての職員（登録ヘルパーを含む）に対して、身体拘束廃止と人権を尊重したケアの励行を図り、事故防止と合わせてリスクマネジメントとしての職員教育を行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
         </is>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+          <t xml:space="preserve">　① 定期的な教育・研修（年2回）の実施</t>
         </is>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">　② 新任者に対する身体拘束廃止・改善のための研修の実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">　③ その他必要な教育・研修の実施</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="8" customHeight="1"/>
-    <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="16" t="inlineStr">
+    <row r="146" ht="8" customHeight="1"/>
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
         <is>
           <t>8．身体拘束廃止に関する指針の閲覧について</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="32" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="148" ht="32" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>この指針は、当事業所内に掲示するとともに、利用者・家族がいつでも自由に閲覧することができます。</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="10" customHeight="1"/>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="16" t="inlineStr">
+    <row r="149" ht="10" customHeight="1"/>
+    <row r="150" ht="26" customHeight="1">
+      <c r="A150" s="16" t="inlineStr">
         <is>
           <t>9．附則</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>この指針は令和8年2月1日より施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="105">
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A128:E128"/>
     <mergeCell ref="A137:E137"/>
     <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A136:E136"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
@@ -11570,21 +11710,21 @@
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A148:E148"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A138:E138"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A120:E120"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
@@ -11598,33 +11738,34 @@
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A123:E123"/>
     <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A146:E146"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A84:E84"/>
     <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A149:E149"/>
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A141:E141"/>
     <mergeCell ref="A135:E135"/>
     <mergeCell ref="A150:E150"/>
     <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A127:E127"/>
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
@@ -11632,17 +11773,15 @@
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A99:E99"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
     <mergeCell ref="A116:E116"/>
-    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A126:E126"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
@@ -11650,7 +11789,9 @@
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
     <mergeCell ref="A143:E143"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11675,8 +11816,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -11801,43 +11942,65 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
+          <t>松村 知恵</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>訪問介護員</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>現場での拘束・スピーチロックの有無の確認、事例の共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
           <t>WIN YADANAR AWNG</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>訪問介護員（ヘルパー代表）</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>現場での拘束・スピーチロックの有無の確認、困りごとの共有、決定事項の現場へのフィードバック</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
+          <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
+          <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
         </is>
@@ -11848,8 +12011,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
@@ -11866,7 +12029,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E158"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -12966,7 +13129,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E144"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -13797,7 +13960,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -14303,7 +14466,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E111"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -15034,7 +15197,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E169"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -16038,7 +16201,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E138"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -16925,7 +17088,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -17210,7 +17373,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -17970,7 +18133,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E116"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -18612,7 +18775,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -19198,6 +19361,384 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>令和8年度　身体拘束廃止・適正化委員会　議事録</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>（株式会社dhpケアマネジメント）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>1．開催日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>日時</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>令和8年6月25日　14時00分～15時00分</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>2．開催場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント 本社事務所 会議室</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>3．委員会構成員</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>委員長</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>生田友哉</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>4．議題</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>1. 身体拘束（身体拘束に該当する行為）の報告状況確認</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="42" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>2. 身体拘束廃止・適正化に向けた職員周知・研修状況について</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="n"/>
+      <c r="D17" s="42" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>3. 身体拘束に該当する可能性のある事例共有および予防策の検討</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="42" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>4. 今後の課題および記録・マニュアル整備について</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="42" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>5．議事内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>議題</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>内容・協議結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>【議題1】
+身体拘束の報告状況確認</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>・委員長より身体拘束に該当する行為の再確認を実施。
+・現場からは、現在身体拘束に該当する対応は行っていないとの報告。
+・ベッド柵や車いすベルトなどの使用状況も確認したが、身体拘束には該当しない運用であることを確認。</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>【議題2】
+職員周知・研修状況</t>
+        </is>
+      </c>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>・今年度前期研修での身体拘束廃止の理念の周知状況を報告。
+・新入職員研修に必須項目として組み込み、フォローアップ研修も実施中。
+・動画教材等の導入も検討し、理解度の底上げを図る方針。</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="B25" s="45" t="inlineStr">
+        <is>
+          <t>【議題3】
+身体拘束に該当する可能性のある事例検討</t>
+        </is>
+      </c>
+      <c r="C25" s="46" t="inlineStr">
+        <is>
+          <t>・認知症進行による夜間不穏がある利用者について事例共有。
+・徘徊・転倒リスクに対し、環境整備や巡視頻度見直しなど拘束に頼らない予防策を検討。
+・本人の生活リズム再評価、観察記録強化、家族との連携強化を決定。</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>【議題4】
+課題・マニュアル整備</t>
+        </is>
+      </c>
+      <c r="C26" s="46" t="inlineStr">
+        <is>
+          <t>・身体拘束チェックリストを整備し判断のばらつきを縮小する案を共有。
+・ガイドライン準拠の記録様式の統一化を進めることを決定。
+・万が一拘束が必要な場合の医師意見書手順や解除基準については次回協議。</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>6．その他・次回予定</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>・必要に応じて臨時開催を行うことを確認。</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="n"/>
+      <c r="D29" s="42" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>・次回開催は令和8年11月25日頃を予定。</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="n"/>
+      <c r="D30" s="42" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="24" customHeight="1">
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>7．確認欄（委員確認印）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="47" t="inlineStr">
+        <is>
+          <t>本議事録の内容について相違ないことを確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>生田友哉（委員長）</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>松村知恵（委員）</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>win yadanar aung（委員）</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>吉田俊輔（委員）</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="inlineStr">
+        <is>
+          <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>吉田麻美（委員）</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19205,7 +19746,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E97"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -19723,7 +20264,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -20245,7 +20786,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E119"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -21011,7 +21552,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -21630,7 +22171,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E119"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -22317,7 +22858,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E116"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -19380,7 +19380,7 @@
     <row r="2">
       <c r="B2" s="37" t="inlineStr">
         <is>
-          <t>令和8年度　身体拘束廃止・適正化委員会　議事録</t>
+          <t>令和8年度　身体拘束適正化委員会　議事録</t>
         </is>
       </c>
     </row>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -19387,7 +19387,7 @@
     <row r="3">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>（株式会社dhpケアマネジメント）</t>
+          <t>（株式会社dhpケアマネジメント　いいかいご）</t>
         </is>
       </c>
     </row>
@@ -19573,7 +19573,7 @@
       <c r="C25" s="46" t="inlineStr">
         <is>
           <t>・認知症進行による夜間不穏がある利用者について事例共有。
-・徘徊・転倒リスクに対し、環境整備や巡視頻度見直しなど拘束に頼らない予防策を検討。
+・徘徊・転倒リスクに対し、環境整備や、訪問時の見守り強化・訪問回数や時間帯の見直し（ケアマネジャーと相談）など拘束に頼らない予防策を検討。
 ・本人の生活リズム再評価、観察記録強化、家族との連携強化を決定。</t>
         </is>
       </c>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -37,7 +37,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セクシャルハラスメント防止指針" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止に関する指針" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束委員会 議事録R8.6.25" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症研修報告R8.6.20" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束委員会 議事録R8.6.25" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47,7 +48,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -129,14 +130,14 @@
     <font>
       <name val="Yu Gothic"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
       <b val="1"/>
-      <color rgb="00333333"/>
-      <sz val="12"/>
+      <color rgb="001F4E79"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -158,6 +159,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="5">
@@ -235,17 +242,6 @@
       <top style="thin">
         <color rgb="00D9D9D9"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -260,11 +256,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -375,18 +382,27 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7425,7 +7441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8343,21 +8359,21 @@
       </c>
       <c r="E135" s="23" t="n"/>
     </row>
-    <row r="136" ht="32" customHeight="1">
+    <row r="136" ht="48" customHeight="1">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>委員（事務・総務）</t>
+          <t>看護職委員</t>
         </is>
       </c>
       <c r="B136" s="21" t="n"/>
       <c r="C136" s="22" t="inlineStr">
         <is>
-          <t>吉田 麻美</t>
+          <t>松村 知恵</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
         <is>
-          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
+          <t>医療的助言・トリアージ・PPE指導、BCPレベル判断の承認（委員長と2名承認）</t>
         </is>
       </c>
       <c r="E136" s="23" t="n"/>
@@ -8365,18 +8381,18 @@
     <row r="137" ht="32" customHeight="1">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>委員（ヘルパー代表）</t>
+          <t>委員（事務・総務）</t>
         </is>
       </c>
       <c r="B137" s="21" t="n"/>
       <c r="C137" s="22" t="inlineStr">
         <is>
-          <t>WIN YADANAR AWNG</t>
+          <t>吉田 麻美</t>
         </is>
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
+          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
         </is>
       </c>
       <c r="E137" s="23" t="n"/>
@@ -8384,39 +8400,59 @@
     <row r="138" ht="32" customHeight="1">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>顧問（任意）</t>
+          <t>委員（ヘルパー代表）</t>
         </is>
       </c>
       <c r="B138" s="21" t="n"/>
       <c r="C138" s="22" t="inlineStr">
         <is>
+          <t>WIN YADANAR AWNG</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
+        </is>
+      </c>
+      <c r="E138" s="23" t="n"/>
+    </row>
+    <row r="139" ht="32" customHeight="1">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>顧問（任意）</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="n"/>
+      <c r="C139" s="22" t="inlineStr">
+        <is>
           <t>主治医・外部専門家・保健所等</t>
         </is>
       </c>
-      <c r="D138" s="22" t="inlineStr">
-        <is>
-          <t>医療的助言・PPE指導（必要に応じて）</t>
-        </is>
-      </c>
-      <c r="E138" s="23" t="n"/>
-    </row>
-    <row r="139" ht="8" customHeight="1"/>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="D139" s="22" t="inlineStr">
+        <is>
+          <t>専門的助言（必要に応じて）</t>
+        </is>
+      </c>
+      <c r="E139" s="23" t="n"/>
+    </row>
+    <row r="140" ht="8" customHeight="1"/>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>＜附則＞</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>本資料は、令和8年2月1日から適用する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="107">
+    <mergeCell ref="A142:E142"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A79:E79"/>
@@ -8455,6 +8491,7 @@
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="D53:E53"/>
+    <mergeCell ref="A139:B139"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A97:E97"/>
@@ -8471,6 +8508,7 @@
     <mergeCell ref="A110:E110"/>
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D139:E139"/>
     <mergeCell ref="D52:E52"/>
     <mergeCell ref="D49:E49"/>
     <mergeCell ref="A25:E25"/>
@@ -8511,7 +8549,6 @@
     <mergeCell ref="D137:E137"/>
     <mergeCell ref="A135:B135"/>
     <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A134:B134"/>
@@ -11204,7 +11241,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・訪問介護員　松村 知恵</t>
+          <t xml:space="preserve">　・看護職　松村 知恵</t>
         </is>
       </c>
     </row>
@@ -11947,12 +11984,12 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>訪問介護員</t>
+          <t>看護職</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>現場での拘束・スピーチロックの有無の確認、事例の共有</t>
+          <t>医療的な視点からの助言、利用者の心身状況の評価、事例の共有</t>
         </is>
       </c>
     </row>
@@ -19367,6 +19404,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>感染症対策委員会 研修実施報告書（統合版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>1．研修実施報告書</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修日時</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>令和8年6月20日　14時00分～16時00分</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修内容</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>感染症・食中毒の予防および発生時対応、BCP運用手順、委員会連携強化</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修場所</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント 本社会議スペース（オンライン併用）</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修講師</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>研修・教育担当：生田
+医療的助言：松村（看護職委員）</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修参加者</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>委員長：生田友哉
+委員：松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="152" customHeight="1">
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>■ 欠席者の対応</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>※今回の研修は全員参加。
+【欠席が出た場合の標準対応】
+・資料配布
+・録画視聴による確認
+・別日補講（生田が担当）
+・理解度チェックシートの提出</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="152" customHeight="1">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>■ 委員長コメント・総括</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>今回の夏季感染対策研修では、委員会メンバー全員が一丸となり、初動対応・ゾーンニング・BCP運用の要点を明確に整理できたことが大きな成果でした。特に、想定訓練において動線遮断やPPE装着といった具体的オペレーションを確認したことにより、実際の発生時に迷いが生じにくい体制が構築できています。
+課題として浮き彫りになったPPE配置の分かりづらさや、判断基準の統一については、委員として責任を持って改善し、現場にとってより安全で実務的な仕組みへ進化させていきます。今後も“早期把握・早期遮断・正確な対応”を軸に、利用者とスタッフ双方の安全を守り抜く体制づくりを進めていきます。</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>■ 本書作成日</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>令和8年6月20日</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>■ 本書作成者</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>生田友哉</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>2．研修内容 詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>実施内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>① 感染経路と季節リスクの再確認</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>・夏季増加の食中毒（ノロ・サルモネラ等）と高温多湿環境での菌増殖リスク
+・季節性ウイルスと新規感染症の混在期への備え</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="98" customHeight="1">
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>② 初動30分行動指針訓練</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>・生田：統括
+・松村：トリアージ・医療的助言
+・吉田（俊）：導線遮断・ゾーニング
+・吉田（麻）：行政報告ルート確認
+・win yadanar aung：研修体系化と欠席フォロー</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>③ BCP手順の再確認</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>・行動レベル1～3の基準
+・応援要員・在宅勤務切替の判断
+・PPE緊急調達ルート
+・クラスター発生時の業務継続判断</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>④ PPE装着・脱衣実演</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>・グローブ二重装着
+・ガウン着脱の注意点
+・廃棄物処理とゾーニング</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>⑤ 食中毒リスク管理</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>・温度管理
+・搬入物検品
+・嘔吐物処理手順</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>⑥ 委員会としての改善点</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>・巡回チェック表簡素化
+・月次ミニ研修
+・行政書類テンプレ改善</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>3．課題と改善方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="70" customHeight="1">
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>■ 課題</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>・導線遮断に3分の遅れ
+・PPE在庫の把握に差
+・嘔吐物処理セットの補充漏れ
+・BCPレベル判断の迷い</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="70" customHeight="1">
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>■ 改善方法</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>・初動カードを電話横へ配置
+・PPE棚の色分け・写真表示
+・嘔吐物処理セットの月2回点検
+・BCP基準は生田・松村の2名承認制</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>4．参加者・責任者・作成者</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>4. 参加者</t>
+        </is>
+      </c>
+      <c r="C30" s="46" t="inlineStr">
+        <is>
+          <t>委員会メンバー全員（5名）</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="45" t="inlineStr">
+        <is>
+          <t>5. 訓練実施責任者</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>委員長：生田友哉</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>6. 訓練記録作成者</t>
+        </is>
+      </c>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>生田友哉</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -19378,14 +19812,14 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="47" t="inlineStr">
         <is>
           <t>令和8年度　身体拘束適正化委員会　議事録</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>（株式会社dhpケアマネジメント　いいかいご）</t>
         </is>
@@ -19400,12 +19834,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>日時</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>令和8年6月25日　14時00分～15時00分</t>
         </is>
@@ -19421,12 +19855,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>場所</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>株式会社dhpケアマネジメント 本社事務所 会議室</t>
         </is>
@@ -19442,12 +19876,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="45" t="inlineStr">
         <is>
           <t>委員長</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="46" t="inlineStr">
         <is>
           <t>生田友哉</t>
         </is>
@@ -19455,12 +19889,12 @@
       <c r="D12" s="42" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>委員</t>
         </is>
       </c>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="C13" s="46" t="inlineStr">
         <is>
           <t>松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
         </is>
@@ -19476,39 +19910,39 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>1. 身体拘束（身体拘束に該当する行為）の報告状況確認</t>
         </is>
       </c>
-      <c r="C16" s="43" t="n"/>
+      <c r="C16" s="48" t="n"/>
       <c r="D16" s="42" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>2. 身体拘束廃止・適正化に向けた職員周知・研修状況について</t>
         </is>
       </c>
-      <c r="C17" s="43" t="n"/>
+      <c r="C17" s="48" t="n"/>
       <c r="D17" s="42" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>3. 身体拘束に該当する可能性のある事例共有および予防策の検討</t>
         </is>
       </c>
-      <c r="C18" s="43" t="n"/>
+      <c r="C18" s="48" t="n"/>
       <c r="D18" s="42" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>4. 今後の課題および記録・マニュアル整備について</t>
         </is>
       </c>
-      <c r="C19" s="43" t="n"/>
+      <c r="C19" s="48" t="n"/>
       <c r="D19" s="42" t="n"/>
     </row>
     <row r="20"/>
@@ -19520,25 +19954,25 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>議題</t>
         </is>
       </c>
-      <c r="C22" s="44" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>内容・協議結果</t>
         </is>
       </c>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="B23" s="45" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>【議題1】
 身体拘束の報告状況確認</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>・委員長より身体拘束に該当する行為の再確認を実施。
 ・現場からは、現在身体拘束に該当する対応は行っていないとの報告。
@@ -19548,13 +19982,13 @@
       <c r="D23" s="42" t="n"/>
     </row>
     <row r="24" ht="64" customHeight="1">
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>【議題2】
 職員周知・研修状況</t>
         </is>
       </c>
-      <c r="C24" s="46" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>・今年度前期研修での身体拘束廃止の理念の周知状況を報告。
 ・新入職員研修に必須項目として組み込み、フォローアップ研修も実施中。
@@ -19564,13 +19998,13 @@
       <c r="D24" s="42" t="n"/>
     </row>
     <row r="25" ht="64" customHeight="1">
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>【議題3】
 身体拘束に該当する可能性のある事例検討</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" s="41" t="inlineStr">
         <is>
           <t>・認知症進行による夜間不穏がある利用者について事例共有。
 ・徘徊・転倒リスクに対し、環境整備や、訪問時の見守り強化・訪問回数や時間帯の見直し（ケアマネジャーと相談）など拘束に頼らない予防策を検討。
@@ -19580,13 +20014,13 @@
       <c r="D25" s="42" t="n"/>
     </row>
     <row r="26" ht="64" customHeight="1">
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>【議題4】
 課題・マニュアル整備</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
         <is>
           <t>・身体拘束チェックリストを整備し判断のばらつきを縮小する案を共有。
 ・ガイドライン準拠の記録様式の統一化を進めることを決定。
@@ -19604,21 +20038,21 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>・必要に応じて臨時開催を行うことを確認。</t>
         </is>
       </c>
-      <c r="C29" s="43" t="n"/>
+      <c r="C29" s="48" t="n"/>
       <c r="D29" s="42" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="46" t="inlineStr">
         <is>
           <t>・次回開催は令和8年11月25日頃を予定。</t>
         </is>
       </c>
-      <c r="C30" s="43" t="n"/>
+      <c r="C30" s="48" t="n"/>
       <c r="D30" s="42" t="n"/>
     </row>
     <row r="31"/>
@@ -19630,19 +20064,19 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="47" t="inlineStr">
+      <c r="B33" s="50" t="inlineStr">
         <is>
           <t>本議事録の内容について相違ないことを確認します。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="B34" s="48" t="inlineStr">
+      <c r="B34" s="51" t="inlineStr">
         <is>
           <t>生田友哉（委員長）</t>
         </is>
       </c>
-      <c r="C34" s="49" t="inlineStr">
+      <c r="C34" s="52" t="inlineStr">
         <is>
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
@@ -19650,12 +20084,12 @@
       <c r="D34" s="42" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="B35" s="48" t="inlineStr">
+      <c r="B35" s="51" t="inlineStr">
         <is>
           <t>松村知恵（委員）</t>
         </is>
       </c>
-      <c r="C35" s="49" t="inlineStr">
+      <c r="C35" s="52" t="inlineStr">
         <is>
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
@@ -19663,12 +20097,12 @@
       <c r="D35" s="42" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="B36" s="48" t="inlineStr">
+      <c r="B36" s="51" t="inlineStr">
         <is>
           <t>win yadanar aung（委員）</t>
         </is>
       </c>
-      <c r="C36" s="49" t="inlineStr">
+      <c r="C36" s="52" t="inlineStr">
         <is>
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
@@ -19676,12 +20110,12 @@
       <c r="D36" s="42" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="B37" s="48" t="inlineStr">
+      <c r="B37" s="51" t="inlineStr">
         <is>
           <t>吉田俊輔（委員）</t>
         </is>
       </c>
-      <c r="C37" s="49" t="inlineStr">
+      <c r="C37" s="52" t="inlineStr">
         <is>
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>
@@ -19689,12 +20123,12 @@
       <c r="D37" s="42" t="n"/>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="B38" s="48" t="inlineStr">
+      <c r="B38" s="51" t="inlineStr">
         <is>
           <t>吉田麻美（委員）</t>
         </is>
       </c>
-      <c r="C38" s="49" t="inlineStr">
+      <c r="C38" s="52" t="inlineStr">
         <is>
           <t>確認印： [　　　　　　　　]　　確認日：令和　　年　　月　　日</t>
         </is>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -8335,45 +8335,45 @@
       </c>
       <c r="D134" s="22" t="inlineStr">
         <is>
-          <t>感染症対策全体の統括・最終判断・行政報告。研修・教育担当を兼務</t>
+          <t>感染症対策全体の統括・最終判断・行政報告、研修講師・欠席者の補講</t>
         </is>
       </c>
       <c r="E134" s="23" t="n"/>
     </row>
-    <row r="135" ht="32" customHeight="1">
+    <row r="135" ht="48" customHeight="1">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>委員（代表取締役）</t>
+          <t>看護職委員</t>
         </is>
       </c>
       <c r="B135" s="21" t="n"/>
       <c r="C135" s="22" t="inlineStr">
         <is>
-          <t>吉田 俊輔</t>
+          <t>松村 知恵</t>
         </is>
       </c>
       <c r="D135" s="22" t="inlineStr">
         <is>
-          <t>法人としての方針決定、BCPの承認、重大事案時の対外対応</t>
+          <t>トリアージ・医療的助言・PPE指導、BCPレベル判断の承認（委員長と2名承認）</t>
         </is>
       </c>
       <c r="E135" s="23" t="n"/>
     </row>
-    <row r="136" ht="48" customHeight="1">
+    <row r="136" ht="32" customHeight="1">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>看護職委員</t>
+          <t>委員（代表取締役）</t>
         </is>
       </c>
       <c r="B136" s="21" t="n"/>
       <c r="C136" s="22" t="inlineStr">
         <is>
-          <t>松村 知恵</t>
+          <t>吉田 俊輔</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
         <is>
-          <t>医療的助言・トリアージ・PPE指導、BCPレベル判断の承認（委員長と2名承認）</t>
+          <t>感染疑い時の訪問調整（担当者限定・訪問順の変更）、BCPの承認</t>
         </is>
       </c>
       <c r="E136" s="23" t="n"/>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>議事録作成、記録整備・行政書類確認、衛生用品の在庫管理</t>
+          <t>行政報告ルートの確認、議事録・記録整備、衛生用品の在庫管理</t>
         </is>
       </c>
       <c r="E137" s="23" t="n"/>
@@ -8400,7 +8400,7 @@
     <row r="138" ht="32" customHeight="1">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>委員（ヘルパー代表）</t>
+          <t>委員（研修・教育担当）</t>
         </is>
       </c>
       <c r="B138" s="21" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="D138" s="22" t="inlineStr">
         <is>
-          <t>現場情報共有・フィードバック、標準予防策の実施状況の確認</t>
+          <t>研修の体系化、欠席者へのフォロー、現場情報の共有</t>
         </is>
       </c>
       <c r="E138" s="23" t="n"/>
@@ -19417,14 +19417,14 @@
     <row r="2">
       <c r="B2" s="37" t="inlineStr">
         <is>
-          <t>株式会社dhpケアマネジメント</t>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="38" t="inlineStr">
         <is>
-          <t>感染症対策委員会 研修実施報告書（統合版）</t>
+          <t>感染症対策委員会 研修・訓練実施報告書（統合版）</t>
         </is>
       </c>
     </row>
@@ -19432,14 +19432,14 @@
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>1．研修実施報告書</t>
+          <t>1．研修・訓練実施報告書</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>■ 研修日時</t>
+          <t>■ 研修・訓練日時</t>
         </is>
       </c>
       <c r="C6" s="41" t="inlineStr">
@@ -19452,7 +19452,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>■ 研修内容</t>
+          <t>■ 研修・訓練内容</t>
         </is>
       </c>
       <c r="C7" s="41" t="inlineStr">
@@ -19465,7 +19465,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>■ 研修場所</t>
+          <t>■ 実施場所</t>
         </is>
       </c>
       <c r="C8" s="41" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="10" ht="44" customHeight="1">
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>■ 研修参加者</t>
+          <t>■ 参加者</t>
         </is>
       </c>
       <c r="C10" s="41" t="inlineStr">
@@ -19529,8 +19529,8 @@
       </c>
       <c r="C12" s="41" t="inlineStr">
         <is>
-          <t>今回の夏季感染対策研修では、委員会メンバー全員が一丸となり、初動対応・ゾーンニング・BCP運用の要点を明確に整理できたことが大きな成果でした。特に、想定訓練において動線遮断やPPE装着といった具体的オペレーションを確認したことにより、実際の発生時に迷いが生じにくい体制が構築できています。
-課題として浮き彫りになったPPE配置の分かりづらさや、判断基準の統一については、委員として責任を持って改善し、現場にとってより安全で実務的な仕組みへ進化させていきます。今後も“早期把握・早期遮断・正確な対応”を軸に、利用者とスタッフ双方の安全を守り抜く体制づくりを進めていきます。</t>
+          <t>今回の夏季感染対策研修では、委員会メンバー全員が一丸となり、初動対応・感染疑い時の訪問調整・BCP運用の要点を明確に整理できたことが大きな成果でした。特に、想定訓練において感染疑い利用者宅への訪問調整（担当者限定・訪問順の変更）やPPE装着といった具体的オペレーションを確認したことにより、実際の発生時に迷いが生じにくい体制が構築できています。
+課題として浮き彫りになった訪問用衛生用品セットの内容・在庫の分かりづらさや、判断基準の統一については、委員として責任を持って改善し、現場にとってより安全で実務的な仕組みへ進化させていきます。今後も“早期把握・早期遮断・正確な対応”を軸に、利用者とスタッフ双方の安全を守り抜く体制づくりを進めていきます。</t>
         </is>
       </c>
       <c r="D12" s="42" t="n"/>
@@ -19605,7 +19605,7 @@
         <is>
           <t>・生田：統括
 ・松村：トリアージ・医療的助言
-・吉田（俊）：導線遮断・ゾーニング
+・吉田（俊）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
 ・吉田（麻）：行政報告ルート確認
 ・win yadanar aung：研修体系化と欠席フォロー</t>
         </is>
@@ -19637,8 +19637,8 @@
       <c r="C21" s="41" t="inlineStr">
         <is>
           <t>・グローブ二重装着
-・ガウン着脱の注意点
-・廃棄物処理とゾーニング</t>
+・ガウン着脱の注意点（利用者宅の玄関等での着脱手順）
+・使用済みPPE・廃棄物の密閉処理（利用者宅のごみ出しルールに従う）</t>
         </is>
       </c>
       <c r="D21" s="42" t="n"/>
@@ -19651,8 +19651,8 @@
       </c>
       <c r="C22" s="41" t="inlineStr">
         <is>
-          <t>・温度管理
-・搬入物検品
+          <t>・調理援助時の温度管理
+・購入食品・冷蔵庫内食品の消費期限確認
 ・嘔吐物処理手順</t>
         </is>
       </c>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="C23" s="41" t="inlineStr">
         <is>
-          <t>・巡回チェック表簡素化
+          <t>・訪問時の体調確認チェック表の簡素化
 ・月次ミニ研修
 ・行政書類テンプレ改善</t>
         </is>
@@ -19689,8 +19689,8 @@
       </c>
       <c r="C26" s="41" t="inlineStr">
         <is>
-          <t>・導線遮断に3分の遅れ
-・PPE在庫の把握に差
+          <t>・感染疑い時の訪問調整（担当者限定・訪問順の変更）の判断に3分の遅れ
+・訪問用PPE・衛生用品の在庫把握に差
 ・嘔吐物処理セットの補充漏れ
 ・BCPレベル判断の迷い</t>
         </is>
@@ -19705,8 +19705,8 @@
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>・初動カードを電話横へ配置
-・PPE棚の色分け・写真表示
+          <t>・初動カードを事業所の電話横へ配置し、訪問用バッグにも携行
+・訪問用衛生用品セットの中身を写真付きで一覧表示
 ・嘔吐物処理セットの月2回点検
 ・BCP基準は生田・松村の2名承認制</t>
         </is>
@@ -19737,7 +19737,7 @@
     <row r="31" ht="24" customHeight="1">
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>5. 訓練実施責任者</t>
+          <t>5. 研修・訓練実施責任者</t>
         </is>
       </c>
       <c r="C31" s="46" t="inlineStr">
@@ -19750,7 +19750,7 @@
     <row r="32" ht="24" customHeight="1">
       <c r="B32" s="45" t="inlineStr">
         <is>
-          <t>6. 訓練記録作成者</t>
+          <t>6. 研修・訓練記録作成者</t>
         </is>
       </c>
       <c r="C32" s="46" t="inlineStr">

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -8406,7 +8406,7 @@
       <c r="B138" s="21" t="n"/>
       <c r="C138" s="22" t="inlineStr">
         <is>
-          <t>WIN YADANAR AWNG</t>
+          <t>WIN YADANAR AUNG</t>
         </is>
       </c>
       <c r="D138" s="22" t="inlineStr">
@@ -11248,7 +11248,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AWNG</t>
+          <t xml:space="preserve">　・訪問介護員（ヘルパー代表）　WIN YADANAR AUNG</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>WIN YADANAR AWNG</t>
+          <t>WIN YADANAR AUNG</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -19498,7 +19498,7 @@
       <c r="C10" s="41" t="inlineStr">
         <is>
           <t>委員長：生田友哉
-委員：松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
+委員：松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
         </is>
       </c>
       <c r="D10" s="42" t="n"/>
@@ -19607,7 +19607,7 @@
 ・松村：トリアージ・医療的助言
 ・吉田（俊）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
 ・吉田（麻）：行政報告ルート確認
-・win yadanar aung：研修体系化と欠席フォロー</t>
+・WIN YADANAR AUNG：研修体系化と欠席フォロー</t>
         </is>
       </c>
       <c r="D19" s="42" t="n"/>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="C13" s="46" t="inlineStr">
         <is>
-          <t>松村知恵、win yadanar aung、吉田俊輔、吉田麻美</t>
+          <t>松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
         </is>
       </c>
       <c r="D13" s="42" t="n"/>
@@ -20099,7 +20099,7 @@
     <row r="36" ht="28" customHeight="1">
       <c r="B36" s="51" t="inlineStr">
         <is>
-          <t>win yadanar aung（委員）</t>
+          <t>WIN YADANAR AUNG（委員）</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -39,6 +39,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症研修報告R8.6.20" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束委員会 議事録R8.6.25" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止研修報告R8.8.20" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20173,6 +20174,188 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>虐待防止委員会 研修実施報告書</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>1．研修基本情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修日時</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>令和8年8月20日　14時00分～16時00分</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="152" customHeight="1">
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修内容</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>虐待防止に関する基礎知識の再確認および事例検討
+・高齢者虐待防止法の再整理
+・事業所内におけるリスク兆候の早期発見ポイント
+・過去事例を用いたグループディスカッション
+・利用者対応時の言動チェックリスト共有
+・緊急時対応プロトコルの統一化</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修場所</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント 本社研修室（内）</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修講師</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>虐待防止委員会 委員長：生田友哉</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修参加者</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>委員長：生田友哉
+委員：WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>■ 欠席者の対応</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>欠席者なし（全4名参加）</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>■ 委員長総括コメント</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>本日の研修では、虐待防止における「気づきの質」を全員で共有し、現場レベルで即時改善につながるディスカッションが行われました。特に、利用者の小さな変化を丁寧に観察する姿勢が、虐待防止の基盤となります。今後も事業所全体で統一的な対応ができるよう、マニュアル整備とケースレビューを定例化し、より安全で信頼される支援体制を構築していきます。</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>■ 本書作成日</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>令和8年8月20日</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>■ 本書作成者</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご
+生田友哉</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -8369,7 +8369,7 @@
       <c r="B136" s="21" t="n"/>
       <c r="C136" s="22" t="inlineStr">
         <is>
-          <t>吉田 俊輔</t>
+          <t>吉田 駿成</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 俊輔</t>
+          <t xml:space="preserve">　・代表取締役（法人代表者）　吉田 駿成</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>吉田 俊輔</t>
+          <t>吉田 駿成</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -19499,7 +19499,7 @@
       <c r="C10" s="41" t="inlineStr">
         <is>
           <t>委員長：生田友哉
-委員：松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+委員：松村知恵、WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
         </is>
       </c>
       <c r="D10" s="42" t="n"/>
@@ -19606,7 +19606,7 @@
         <is>
           <t>・生田：統括
 ・松村：トリアージ・医療的助言
-・吉田（俊）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
+・吉田（駿）：感染疑い時の訪問調整（担当者限定・訪問順の変更）
 ・吉田（麻）：行政報告ルート確認
 ・WIN YADANAR AUNG：研修体系化と欠席フォロー</t>
         </is>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="C13" s="46" t="inlineStr">
         <is>
-          <t>松村知恵、WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+          <t>松村知恵、WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
         </is>
       </c>
       <c r="D13" s="42" t="n"/>
@@ -20113,7 +20113,7 @@
     <row r="37" ht="28" customHeight="1">
       <c r="B37" s="51" t="inlineStr">
         <is>
-          <t>吉田俊輔（委員）</t>
+          <t>吉田駿成（委員）</t>
         </is>
       </c>
       <c r="C37" s="52" t="inlineStr">
@@ -20278,7 +20278,7 @@
       <c r="C10" s="41" t="inlineStr">
         <is>
           <t>委員長：生田友哉
-委員：WIN YADANAR AUNG、吉田俊輔、吉田麻美</t>
+委員：WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
         </is>
       </c>
       <c r="D10" s="42" t="n"/>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症研修報告R8.6.20" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束委員会 議事録R8.6.25" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止研修報告R8.8.20" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束研修報告R8.8.20" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20356,6 +20357,333 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>身体拘束廃止研修 実施報告書</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>1．研修概要</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>■ 研修名</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>身体拘束廃止研修（虐待防止および権利擁護研修を含む）</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>■ 開催日時</t>
+        </is>
+      </c>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>令和8年8月20日　14:00～16:30</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>■ 開催場所</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント 本社研修室</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>■ 講師</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="inlineStr">
+        <is>
+          <t>生田友哉（身体拘束適正化委員会・虐待防止委員会 委員長・介護福祉士）</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>2．研修の目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>利用者の尊厳を守り、身体拘束ゼロを継続するための理解と判断基準の統一。
+グレーゾーンの排除、緊急やむを得ない場合の3要件の正確な適用など。</t>
+        </is>
+      </c>
+      <c r="C12" s="48" t="n"/>
+      <c r="D12" s="42" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>3．研修内容（詳細）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>項目・時間</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>研修内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="82" customHeight="1">
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>(1) 身体拘束の定義と法的根拠
+(45分)</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>・身体拘束に該当する11の具体的行為（国の手引き）の再整理
+・グレーゾーン事例の分析
+・環境固定化と自由制限のリスク
+・意思決定支援の重要性</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>(2) 緊急やむを得ない場合の3要件
+(30分)</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>・切迫性、非代替性、一時性の3点を具体例をもとに検討。</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="82" customHeight="1">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>(3) ケーススタディ
+(40分)</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>ケース1：夜間センサーマットの判断
+ケース2：徘徊傾向利用者の玄関施錠
+ケース3：医療後の安静保持と抑制
+ケース4：介助拒否時の複数人介助</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>(4) 記録・報告体制の強化
+(20分)</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>・ヒヤリ報告書の改訂ポイント
+・報告ライン（訪問介護員 → サービス提供責任者 → 管理者（委員長）→ 委員会）</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>(5) いいかいごの
+身体拘束ゼロ方針 (15分)</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>・尊厳最優先の原則
+・訪問時の見守り方法・住環境の工夫・声掛け技術の統一ルール</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>4．体制・講評・アクションプラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>4. 研修参加者</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>生田友哉（委員長）、WIN YADANAR AUNG、吉田駿成、吉田麻美（全4名）</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>5. 欠席者対応</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>欠席者なし（全員出席）</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>6. 講師総括</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>身体拘束は「やらない」ではなく「やらなくて済む環境づくり」が重要であることを強調。</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>7. 研修後のアクションプラン</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>・担当利用者宅ごとの拘束リスク点検（家族による拘束を含む）
+・夜間・早朝訪問時の対応改善案提出
+・新人教育/OJTに組み込み
+・委員会でのモニタリング強化</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>8. 本書作成日</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>令和8年8月20日</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>9. 本書作成者</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご
+身体拘束適正化委員会（委員長 生田友哉）</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -39,8 +39,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="苦情（相談）記録表" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="感染症研修報告R8.6.20" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束委員会 議事録R8.6.25" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止研修報告R8.8.20" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束研修報告R8.8.20" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="身体拘束研修報告R8.7.25" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="虐待防止研修報告R8.8.20" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20181,188 +20181,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1"/>
-    <row r="2">
-      <c r="B2" s="37" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t>虐待防止委員会 研修実施報告書</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>1．研修基本情報</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>■ 研修日時</t>
-        </is>
-      </c>
-      <c r="C6" s="41" t="inlineStr">
-        <is>
-          <t>令和8年8月20日　14時00分～16時00分</t>
-        </is>
-      </c>
-      <c r="D6" s="42" t="n"/>
-    </row>
-    <row r="7" ht="152" customHeight="1">
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>■ 研修内容</t>
-        </is>
-      </c>
-      <c r="C7" s="41" t="inlineStr">
-        <is>
-          <t>虐待防止に関する基礎知識の再確認および事例検討
-・高齢者虐待防止法の再整理
-・事業所内におけるリスク兆候の早期発見ポイント
-・過去事例を用いたグループディスカッション
-・利用者対応時の言動チェックリスト共有
-・緊急時対応プロトコルの統一化</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>■ 研修場所</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント 本社研修室（内）</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>■ 研修講師</t>
-        </is>
-      </c>
-      <c r="C9" s="41" t="inlineStr">
-        <is>
-          <t>虐待防止委員会 委員長：生田友哉</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="n"/>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>■ 研修参加者</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="inlineStr">
-        <is>
-          <t>委員長：生田友哉
-委員：WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>■ 欠席者の対応</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="inlineStr">
-        <is>
-          <t>欠席者なし（全4名参加）</t>
-        </is>
-      </c>
-      <c r="D11" s="42" t="n"/>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="B12" s="40" t="inlineStr">
-        <is>
-          <t>■ 委員長総括コメント</t>
-        </is>
-      </c>
-      <c r="C12" s="41" t="inlineStr">
-        <is>
-          <t>本日の研修では、虐待防止における「気づきの質」を全員で共有し、現場レベルで即時改善につながるディスカッションが行われました。特に、利用者の小さな変化を丁寧に観察する姿勢が、虐待防止の基盤となります。今後も事業所全体で統一的な対応ができるよう、マニュアル整備とケースレビューを定例化し、より安全で信頼される支援体制を構築していきます。</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="n"/>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>■ 本書作成日</t>
-        </is>
-      </c>
-      <c r="C13" s="41" t="inlineStr">
-        <is>
-          <t>令和8年8月20日</t>
-        </is>
-      </c>
-      <c r="D13" s="42" t="n"/>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>■ 本書作成者</t>
-        </is>
-      </c>
-      <c r="C14" s="41" t="inlineStr">
-        <is>
-          <t>株式会社dhpケアマネジメント　いいかいご
-生田友哉</t>
-        </is>
-      </c>
-      <c r="D14" s="42" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C8:D8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20416,7 +20234,7 @@
       </c>
       <c r="C7" s="46" t="inlineStr">
         <is>
-          <t>令和8年8月20日　14:00～16:30</t>
+          <t>令和8年7月25日　14:00～16:30</t>
         </is>
       </c>
       <c r="D7" s="42" t="n"/>
@@ -20634,7 +20452,7 @@
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>令和8年8月20日</t>
+          <t>令和8年7月25日</t>
         </is>
       </c>
       <c r="D27" s="42" t="n"/>
@@ -20678,6 +20496,188 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>虐待防止委員会 研修実施報告書</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>1．研修基本情報</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修日時</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>令和8年8月20日　14時00分～16時00分</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="152" customHeight="1">
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修内容</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>虐待防止に関する基礎知識の再確認および事例検討
+・高齢者虐待防止法の再整理
+・事業所内におけるリスク兆候の早期発見ポイント
+・過去事例を用いたグループディスカッション
+・利用者対応時の言動チェックリスト共有
+・緊急時対応プロトコルの統一化</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修場所</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント 本社研修室（内）</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修講師</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>虐待防止委員会 委員長：生田友哉</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>■ 研修参加者</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>委員長：生田友哉
+委員：WIN YADANAR AUNG、吉田駿成、吉田麻美</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>■ 欠席者の対応</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>欠席者なし（全4名参加）</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>■ 委員長総括コメント</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>本日の研修では、虐待防止における「気づきの質」を全員で共有し、現場レベルで即時改善につながるディスカッションが行われました。特に、利用者の小さな変化を丁寧に観察する姿勢が、虐待防止の基盤となります。今後も事業所全体で統一的な対応ができるよう、マニュアル整備とケースレビューを定例化し、より安全で信頼される支援体制を構築していきます。</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>■ 本書作成日</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>令和8年8月20日</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>■ 本書作成者</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>株式会社dhpケアマネジメント　いいかいご
+生田友哉</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/output/いいかいご_社内規程一式.xlsx
+++ b/output/いいかいご_社内規程一式.xlsx
@@ -19792,6 +19792,7 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -20170,6 +20171,7 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -20497,6 +20499,7 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -20679,6 +20682,7 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C8:D8"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
